--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.67</v>
+        <v>4.07</v>
       </c>
       <c r="F14" t="n">
-        <v>14.28</v>
+        <v>14.27</v>
       </c>
       <c r="G14" t="n">
-        <v>298.5</v>
+        <v>303.3</v>
       </c>
       <c r="H14" t="n">
-        <v>30.3</v>
+        <v>31</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>28.31</v>
+        <v>-90.86</v>
       </c>
       <c r="K14" t="n">
-        <v>78.28</v>
+        <v>-305.56</v>
       </c>
       <c r="L14" t="n">
-        <v>83.23999999999999</v>
+        <v>318.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:30:08</t>
+          <t>04:30:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="F15" t="n">
-        <v>14.56</v>
+        <v>13.96</v>
       </c>
       <c r="G15" t="n">
-        <v>306</v>
+        <v>290.7</v>
       </c>
       <c r="H15" t="n">
-        <v>30.3</v>
+        <v>23.2</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>15.73</v>
+        <v>56.15</v>
       </c>
       <c r="K15" t="n">
-        <v>186.1</v>
+        <v>-45.56</v>
       </c>
       <c r="L15" t="n">
-        <v>186.77</v>
+        <v>72.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:31:31</t>
+          <t>04:31:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.64</v>
+        <v>3.86</v>
       </c>
       <c r="F16" t="n">
-        <v>14.35</v>
+        <v>14.18</v>
       </c>
       <c r="G16" t="n">
-        <v>285.3</v>
+        <v>302.4</v>
       </c>
       <c r="H16" t="n">
-        <v>37.4</v>
+        <v>29.2</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-80.95999999999999</v>
+        <v>-10.84</v>
       </c>
       <c r="K16" t="n">
-        <v>-29.2</v>
+        <v>-114.59</v>
       </c>
       <c r="L16" t="n">
-        <v>86.06999999999999</v>
+        <v>115.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:36:56</t>
+          <t>04:36:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="F17" t="n">
-        <v>14.26</v>
+        <v>14.14</v>
       </c>
       <c r="G17" t="n">
-        <v>304.3</v>
+        <v>298.7</v>
       </c>
       <c r="H17" t="n">
-        <v>25.1</v>
+        <v>22.7</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>63.05</v>
+        <v>143.89</v>
       </c>
       <c r="K17" t="n">
-        <v>105.46</v>
+        <v>-39.83</v>
       </c>
       <c r="L17" t="n">
-        <v>122.87</v>
+        <v>149.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:38:29</t>
+          <t>04:38:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.42</v>
+        <v>4.07</v>
       </c>
       <c r="F18" t="n">
-        <v>15.34</v>
+        <v>14.05</v>
       </c>
       <c r="G18" t="n">
-        <v>323.5</v>
+        <v>313.4</v>
       </c>
       <c r="H18" t="n">
-        <v>32.1</v>
+        <v>35.3</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>59.31</v>
+        <v>2.62</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.16</v>
+        <v>45.99</v>
       </c>
       <c r="L18" t="n">
-        <v>60.35</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:40:16</t>
+          <t>04:41:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.49</v>
+        <v>3.8</v>
       </c>
       <c r="F19" t="n">
-        <v>14.44</v>
+        <v>14.12</v>
       </c>
       <c r="G19" t="n">
-        <v>300.5</v>
+        <v>291.9</v>
       </c>
       <c r="H19" t="n">
-        <v>25.9</v>
+        <v>27.9</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-35.86</v>
+        <v>-89.92</v>
       </c>
       <c r="K19" t="n">
-        <v>190.74</v>
+        <v>-78.5</v>
       </c>
       <c r="L19" t="n">
-        <v>194.09</v>
+        <v>119.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:45:15</t>
+          <t>04:45:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="F20" t="n">
-        <v>13.75</v>
+        <v>14.36</v>
       </c>
       <c r="G20" t="n">
-        <v>305.3</v>
+        <v>313.7</v>
       </c>
       <c r="H20" t="n">
-        <v>29.3</v>
+        <v>30.4</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>277.94</v>
+        <v>373.43</v>
       </c>
       <c r="K20" t="n">
-        <v>-424.12</v>
+        <v>-138.08</v>
       </c>
       <c r="L20" t="n">
-        <v>507.08</v>
+        <v>398.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:46:40</t>
+          <t>04:47:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.69</v>
+        <v>3.85</v>
       </c>
       <c r="F21" t="n">
-        <v>13.78</v>
+        <v>13.86</v>
       </c>
       <c r="G21" t="n">
-        <v>301.6</v>
+        <v>300.1</v>
       </c>
       <c r="H21" t="n">
-        <v>24.3</v>
+        <v>29</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>441.49</v>
+        <v>-211.1</v>
       </c>
       <c r="K21" t="n">
-        <v>-78.09</v>
+        <v>131.09</v>
       </c>
       <c r="L21" t="n">
-        <v>448.34</v>
+        <v>248.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:48:34</t>
+          <t>04:48:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.88</v>
+        <v>4.45</v>
       </c>
       <c r="F22" t="n">
-        <v>14.72</v>
+        <v>14.33</v>
       </c>
       <c r="G22" t="n">
-        <v>297.8</v>
+        <v>296.8</v>
       </c>
       <c r="H22" t="n">
-        <v>27</v>
+        <v>24.8</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-253.62</v>
+        <v>-40.31</v>
       </c>
       <c r="K22" t="n">
-        <v>196.98</v>
+        <v>-309.62</v>
       </c>
       <c r="L22" t="n">
-        <v>321.13</v>
+        <v>312.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:54:35</t>
+          <t>04:53:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.6</v>
+        <v>5.28</v>
       </c>
       <c r="F23" t="n">
-        <v>14.28</v>
+        <v>14.87</v>
       </c>
       <c r="G23" t="n">
-        <v>293.1</v>
+        <v>296.9</v>
       </c>
       <c r="H23" t="n">
-        <v>31</v>
+        <v>25.9</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>27.15</v>
+        <v>36.47</v>
       </c>
       <c r="K23" t="n">
-        <v>166.91</v>
+        <v>-391</v>
       </c>
       <c r="L23" t="n">
-        <v>169.1</v>
+        <v>392.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:56:23</t>
+          <t>04:55:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.64</v>
+        <v>4.06</v>
       </c>
       <c r="F24" t="n">
-        <v>14.34</v>
+        <v>13.07</v>
       </c>
       <c r="G24" t="n">
-        <v>304.7</v>
+        <v>302.4</v>
       </c>
       <c r="H24" t="n">
-        <v>32.2</v>
+        <v>24.2</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>247.49</v>
+        <v>-54.36</v>
       </c>
       <c r="K24" t="n">
-        <v>18.37</v>
+        <v>-320.6</v>
       </c>
       <c r="L24" t="n">
-        <v>248.17</v>
+        <v>325.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:58:05</t>
+          <t>04:57:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.73</v>
+        <v>4.93</v>
       </c>
       <c r="F25" t="n">
-        <v>13.92</v>
+        <v>14.62</v>
       </c>
       <c r="G25" t="n">
-        <v>299</v>
+        <v>301.4</v>
       </c>
       <c r="H25" t="n">
-        <v>29.2</v>
+        <v>25.7</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>4.54</v>
+        <v>174.78</v>
       </c>
       <c r="K25" t="n">
-        <v>-152.62</v>
+        <v>350.24</v>
       </c>
       <c r="L25" t="n">
-        <v>152.68</v>
+        <v>391.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:02:20</t>
+          <t>05:02:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.56</v>
+        <v>5.04</v>
       </c>
       <c r="F26" t="n">
-        <v>14.33</v>
+        <v>14.16</v>
       </c>
       <c r="G26" t="n">
-        <v>313.3</v>
+        <v>308.4</v>
       </c>
       <c r="H26" t="n">
-        <v>33.8</v>
+        <v>34.4</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>409.87</v>
+        <v>-716.23</v>
       </c>
       <c r="K26" t="n">
-        <v>148.19</v>
+        <v>158.55</v>
       </c>
       <c r="L26" t="n">
-        <v>435.84</v>
+        <v>733.5700000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:04:13</t>
+          <t>05:04:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.72</v>
+        <v>3.58</v>
       </c>
       <c r="F27" t="n">
-        <v>14.35</v>
+        <v>14.16</v>
       </c>
       <c r="G27" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="H27" t="n">
-        <v>26.9</v>
+        <v>23.6</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>1.17</v>
+        <v>-309.88</v>
       </c>
       <c r="K27" t="n">
-        <v>-69.16</v>
+        <v>291.79</v>
       </c>
       <c r="L27" t="n">
-        <v>69.17</v>
+        <v>425.64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:05:50</t>
+          <t>05:05:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.91</v>
+        <v>4.24</v>
       </c>
       <c r="F28" t="n">
-        <v>14.39</v>
+        <v>14.54</v>
       </c>
       <c r="G28" t="n">
-        <v>312.1</v>
+        <v>300.7</v>
       </c>
       <c r="H28" t="n">
-        <v>33.3</v>
+        <v>23.3</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-39.9</v>
+        <v>-359.96</v>
       </c>
       <c r="K28" t="n">
-        <v>-186.72</v>
+        <v>-161.78</v>
       </c>
       <c r="L28" t="n">
-        <v>190.94</v>
+        <v>394.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:16:24</t>
+          <t>05:15:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.31</v>
+        <v>3.88</v>
       </c>
       <c r="F29" t="n">
-        <v>13.72</v>
+        <v>13.79</v>
       </c>
       <c r="G29" t="n">
-        <v>322.8</v>
+        <v>307.2</v>
       </c>
       <c r="H29" t="n">
-        <v>28.3</v>
+        <v>27.5</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>112.7</v>
+        <v>-27.93</v>
       </c>
       <c r="K29" t="n">
-        <v>-69.41</v>
+        <v>123.1</v>
       </c>
       <c r="L29" t="n">
-        <v>132.35</v>
+        <v>126.23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:42</t>
+          <t>05:17:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="F30" t="n">
-        <v>14.08</v>
+        <v>14.31</v>
       </c>
       <c r="G30" t="n">
-        <v>313.4</v>
+        <v>293</v>
       </c>
       <c r="H30" t="n">
-        <v>29.5</v>
+        <v>24.7</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.91</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-91.51000000000001</v>
+        <v>146.32</v>
       </c>
       <c r="L30" t="n">
-        <v>92.04000000000001</v>
+        <v>146.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:20:03</t>
+          <t>05:17:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.56</v>
+        <v>4.93</v>
       </c>
       <c r="F31" t="n">
-        <v>14.72</v>
+        <v>14.23</v>
       </c>
       <c r="G31" t="n">
-        <v>301.1</v>
+        <v>298.4</v>
       </c>
       <c r="H31" t="n">
-        <v>30.8</v>
+        <v>29</v>
       </c>
       <c r="I31" t="n">
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.24</v>
+        <v>201.22</v>
       </c>
       <c r="K31" t="n">
-        <v>41.17</v>
+        <v>74.86</v>
       </c>
       <c r="L31" t="n">
-        <v>41.5</v>
+        <v>214.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:24:35</t>
+          <t>05:21:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.71</v>
+        <v>3.96</v>
       </c>
       <c r="F32" t="n">
-        <v>14.06</v>
+        <v>13.91</v>
       </c>
       <c r="G32" t="n">
-        <v>291.7</v>
+        <v>299.6</v>
       </c>
       <c r="H32" t="n">
-        <v>23.6</v>
+        <v>21.3</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-23.95</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>167.25</v>
+        <v>160.59</v>
       </c>
       <c r="L32" t="n">
-        <v>168.95</v>
+        <v>184.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:25:49</t>
+          <t>05:23:24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.27</v>
+        <v>4.34</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>13.84</v>
       </c>
       <c r="G33" t="n">
-        <v>302.2</v>
+        <v>293.4</v>
       </c>
       <c r="H33" t="n">
-        <v>30.7</v>
+        <v>28</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>132.9</v>
+        <v>47.02</v>
       </c>
       <c r="K33" t="n">
-        <v>86.03</v>
+        <v>7.21</v>
       </c>
       <c r="L33" t="n">
-        <v>158.32</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:27:37</t>
+          <t>05:24:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.66</v>
+        <v>4.45</v>
       </c>
       <c r="F34" t="n">
-        <v>13.87</v>
+        <v>15.12</v>
       </c>
       <c r="G34" t="n">
-        <v>293.8</v>
+        <v>302.1</v>
       </c>
       <c r="H34" t="n">
-        <v>26.9</v>
+        <v>30.8</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>235.46</v>
+        <v>35.28</v>
       </c>
       <c r="K34" t="n">
-        <v>51.16</v>
+        <v>364.01</v>
       </c>
       <c r="L34" t="n">
-        <v>240.95</v>
+        <v>365.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:33:21</t>
+          <t>05:27:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.22</v>
+        <v>4.46</v>
       </c>
       <c r="F35" t="n">
-        <v>14.05</v>
+        <v>14.27</v>
       </c>
       <c r="G35" t="n">
-        <v>312.3</v>
+        <v>292.8</v>
       </c>
       <c r="H35" t="n">
-        <v>29.2</v>
+        <v>34.2</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>41.98</v>
+        <v>-57.32</v>
       </c>
       <c r="K35" t="n">
-        <v>-241.94</v>
+        <v>-272.51</v>
       </c>
       <c r="L35" t="n">
-        <v>245.56</v>
+        <v>278.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:35:30</t>
+          <t>05:29:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.47</v>
+        <v>4.98</v>
       </c>
       <c r="F36" t="n">
-        <v>13.69</v>
+        <v>13.9</v>
       </c>
       <c r="G36" t="n">
-        <v>293.8</v>
+        <v>312.1</v>
       </c>
       <c r="H36" t="n">
-        <v>27.1</v>
+        <v>23.2</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-75.73</v>
+        <v>188.1</v>
       </c>
       <c r="K36" t="n">
-        <v>-198.98</v>
+        <v>139.41</v>
       </c>
       <c r="L36" t="n">
-        <v>212.91</v>
+        <v>234.13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:37:46</t>
+          <t>05:31:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.63</v>
+        <v>3.39</v>
       </c>
       <c r="F37" t="n">
-        <v>14.14</v>
+        <v>13.46</v>
       </c>
       <c r="G37" t="n">
         <v>301.2</v>
       </c>
       <c r="H37" t="n">
-        <v>29.2</v>
+        <v>26.8</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>50.78</v>
+        <v>-220.67</v>
       </c>
       <c r="K37" t="n">
-        <v>23.67</v>
+        <v>-37.29</v>
       </c>
       <c r="L37" t="n">
-        <v>56.02</v>
+        <v>223.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:41:48</t>
+          <t>05:36:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="F38" t="n">
-        <v>13.93</v>
+        <v>14.48</v>
       </c>
       <c r="G38" t="n">
-        <v>305.6</v>
+        <v>313.7</v>
       </c>
       <c r="H38" t="n">
-        <v>31.2</v>
+        <v>24.8</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>108.07</v>
+        <v>-323.14</v>
       </c>
       <c r="K38" t="n">
-        <v>59.16</v>
+        <v>-349.76</v>
       </c>
       <c r="L38" t="n">
-        <v>123.2</v>
+        <v>476.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:43:46</t>
+          <t>05:38:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.87</v>
+        <v>4.53</v>
       </c>
       <c r="F39" t="n">
-        <v>14.25</v>
+        <v>14.19</v>
       </c>
       <c r="G39" t="n">
-        <v>302.1</v>
+        <v>294.9</v>
       </c>
       <c r="H39" t="n">
-        <v>26.2</v>
+        <v>25.4</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>312.3</v>
+        <v>-41.44</v>
       </c>
       <c r="K39" t="n">
-        <v>-209.57</v>
+        <v>305.77</v>
       </c>
       <c r="L39" t="n">
-        <v>376.1</v>
+        <v>308.57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:46:11</t>
+          <t>05:40:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.56</v>
+        <v>4.47</v>
       </c>
       <c r="F40" t="n">
-        <v>14.41</v>
+        <v>14.26</v>
       </c>
       <c r="G40" t="n">
-        <v>303.6</v>
+        <v>288.6</v>
       </c>
       <c r="H40" t="n">
-        <v>23.6</v>
+        <v>28.9</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>158.36</v>
+        <v>218.77</v>
       </c>
       <c r="K40" t="n">
-        <v>-616.61</v>
+        <v>195.6</v>
       </c>
       <c r="L40" t="n">
-        <v>636.62</v>
+        <v>293.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:51:46</t>
+          <t>05:45:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.81</v>
+        <v>4.35</v>
       </c>
       <c r="F41" t="n">
-        <v>13.51</v>
+        <v>14.28</v>
       </c>
       <c r="G41" t="n">
-        <v>298.1</v>
+        <v>299.6</v>
       </c>
       <c r="H41" t="n">
-        <v>25.3</v>
+        <v>29.1</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>112.96</v>
+        <v>514.72</v>
       </c>
       <c r="K41" t="n">
-        <v>-105</v>
+        <v>747.8200000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>154.22</v>
+        <v>907.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:53:59</t>
+          <t>05:46:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.15</v>
+        <v>4.84</v>
       </c>
       <c r="F42" t="n">
-        <v>13.89</v>
+        <v>13.97</v>
       </c>
       <c r="G42" t="n">
-        <v>302.7</v>
+        <v>290.7</v>
       </c>
       <c r="H42" t="n">
-        <v>29.6</v>
+        <v>21.9</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>34.73</v>
+        <v>-156.78</v>
       </c>
       <c r="K42" t="n">
-        <v>611.0700000000001</v>
+        <v>-580.02</v>
       </c>
       <c r="L42" t="n">
-        <v>612.05</v>
+        <v>600.84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:55:53</t>
+          <t>05:48:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.8</v>
+        <v>4.97</v>
       </c>
       <c r="F43" t="n">
-        <v>14.62</v>
+        <v>13.76</v>
       </c>
       <c r="G43" t="n">
-        <v>302.5</v>
+        <v>303.9</v>
       </c>
       <c r="H43" t="n">
-        <v>28.3</v>
+        <v>32.4</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>114.19</v>
+        <v>768.26</v>
       </c>
       <c r="K43" t="n">
-        <v>-114.55</v>
+        <v>-87.03</v>
       </c>
       <c r="L43" t="n">
-        <v>161.74</v>
+        <v>773.1799999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:18</t>
+          <t>05:57:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.75</v>
+        <v>4.28</v>
       </c>
       <c r="F44" t="n">
-        <v>13.87</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
-        <v>304.6</v>
+        <v>295.3</v>
       </c>
       <c r="H44" t="n">
-        <v>36.4</v>
+        <v>32.8</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-90.95</v>
+        <v>5.38</v>
       </c>
       <c r="K44" t="n">
-        <v>-131.18</v>
+        <v>146.13</v>
       </c>
       <c r="L44" t="n">
-        <v>159.62</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:07:55</t>
+          <t>05:59:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.58</v>
+        <v>4.13</v>
       </c>
       <c r="F45" t="n">
-        <v>13.71</v>
+        <v>14.06</v>
       </c>
       <c r="G45" t="n">
-        <v>310.3</v>
+        <v>304.7</v>
       </c>
       <c r="H45" t="n">
-        <v>27.1</v>
+        <v>37.4</v>
       </c>
       <c r="I45" t="n">
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-21.32</v>
+        <v>-47.09</v>
       </c>
       <c r="K45" t="n">
-        <v>11.43</v>
+        <v>-231.13</v>
       </c>
       <c r="L45" t="n">
-        <v>24.2</v>
+        <v>235.88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:10:10</t>
+          <t>06:00:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="F46" t="n">
-        <v>13.24</v>
+        <v>13.27</v>
       </c>
       <c r="G46" t="n">
-        <v>313.7</v>
+        <v>301.5</v>
       </c>
       <c r="H46" t="n">
-        <v>35.6</v>
+        <v>21.7</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-192.8</v>
+        <v>41.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-191.67</v>
+        <v>21.87</v>
       </c>
       <c r="L46" t="n">
-        <v>271.86</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:16:50</t>
+          <t>06:06:20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="F47" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="G47" t="n">
-        <v>305.2</v>
+        <v>302.6</v>
       </c>
       <c r="H47" t="n">
-        <v>23.7</v>
+        <v>28.1</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>245.81</v>
+        <v>48.12</v>
       </c>
       <c r="K47" t="n">
-        <v>55.97</v>
+        <v>-30.56</v>
       </c>
       <c r="L47" t="n">
-        <v>252.1</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:18:21</t>
+          <t>06:08:06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.42</v>
+        <v>5.62</v>
       </c>
       <c r="F48" t="n">
-        <v>14.56</v>
+        <v>13.93</v>
       </c>
       <c r="G48" t="n">
-        <v>306.8</v>
+        <v>299.9</v>
       </c>
       <c r="H48" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-72.59999999999999</v>
+        <v>119.1</v>
       </c>
       <c r="K48" t="n">
-        <v>-9.69</v>
+        <v>-124.02</v>
       </c>
       <c r="L48" t="n">
-        <v>73.25</v>
+        <v>171.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:20:45</t>
+          <t>06:09:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="F49" t="n">
-        <v>14.02</v>
+        <v>14.45</v>
       </c>
       <c r="G49" t="n">
-        <v>304.6</v>
+        <v>298.4</v>
       </c>
       <c r="H49" t="n">
-        <v>30.4</v>
+        <v>21.1</v>
       </c>
       <c r="I49" t="n">
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>59.86</v>
+        <v>219.8</v>
       </c>
       <c r="K49" t="n">
-        <v>63.67</v>
+        <v>112.64</v>
       </c>
       <c r="L49" t="n">
-        <v>87.39</v>
+        <v>246.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:25:38</t>
+          <t>06:14:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.36</v>
+        <v>4.79</v>
       </c>
       <c r="F50" t="n">
-        <v>14.71</v>
+        <v>14.1</v>
       </c>
       <c r="G50" t="n">
-        <v>297.7</v>
+        <v>302.6</v>
       </c>
       <c r="H50" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>124.9</v>
+        <v>-25.53</v>
       </c>
       <c r="K50" t="n">
-        <v>-111.43</v>
+        <v>-154.21</v>
       </c>
       <c r="L50" t="n">
-        <v>167.38</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:28:32</t>
+          <t>06:17:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.31</v>
+        <v>4.83</v>
       </c>
       <c r="F51" t="n">
-        <v>14.15</v>
+        <v>14.33</v>
       </c>
       <c r="G51" t="n">
-        <v>300.8</v>
+        <v>300.6</v>
       </c>
       <c r="H51" t="n">
-        <v>18.1</v>
+        <v>29.8</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-478.07</v>
+        <v>17.73</v>
       </c>
       <c r="K51" t="n">
-        <v>-179.8</v>
+        <v>-117.65</v>
       </c>
       <c r="L51" t="n">
-        <v>510.77</v>
+        <v>118.98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:29:40</t>
+          <t>06:19:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.74</v>
+        <v>5.86</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>14.62</v>
       </c>
       <c r="G52" t="n">
-        <v>286.7</v>
+        <v>291.1</v>
       </c>
       <c r="H52" t="n">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>153.12</v>
+        <v>-231.18</v>
       </c>
       <c r="K52" t="n">
-        <v>3.23</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>153.16</v>
+        <v>250.68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:33:26</t>
+          <t>06:22:28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.52</v>
+        <v>4.87</v>
       </c>
       <c r="F53" t="n">
-        <v>13.96</v>
+        <v>14.23</v>
       </c>
       <c r="G53" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H53" t="n">
-        <v>29.3</v>
+        <v>28.7</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>-343.29</v>
+        <v>284.83</v>
       </c>
       <c r="K53" t="n">
-        <v>481.54</v>
+        <v>47.29</v>
       </c>
       <c r="L53" t="n">
-        <v>591.38</v>
+        <v>288.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:34:51</t>
+          <t>06:24:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.84</v>
+        <v>4.22</v>
       </c>
       <c r="F54" t="n">
-        <v>14.11</v>
+        <v>13.39</v>
       </c>
       <c r="G54" t="n">
-        <v>296.9</v>
+        <v>287.8</v>
       </c>
       <c r="H54" t="n">
-        <v>30.1</v>
+        <v>31.1</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>140.93</v>
+        <v>398.09</v>
       </c>
       <c r="K54" t="n">
-        <v>-298.96</v>
+        <v>-353.34</v>
       </c>
       <c r="L54" t="n">
-        <v>330.52</v>
+        <v>532.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:36:15</t>
+          <t>06:26:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.15</v>
+        <v>4.64</v>
       </c>
       <c r="F55" t="n">
-        <v>14.43</v>
+        <v>13.66</v>
       </c>
       <c r="G55" t="n">
-        <v>314.8</v>
+        <v>291.8</v>
       </c>
       <c r="H55" t="n">
-        <v>25.4</v>
+        <v>29.3</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-114.45</v>
+        <v>-96.25</v>
       </c>
       <c r="K55" t="n">
-        <v>385.06</v>
+        <v>-335.84</v>
       </c>
       <c r="L55" t="n">
-        <v>401.71</v>
+        <v>349.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:40:29</t>
+          <t>06:31:20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.09</v>
+        <v>4.97</v>
       </c>
       <c r="F56" t="n">
-        <v>14.12</v>
+        <v>14.05</v>
       </c>
       <c r="G56" t="n">
-        <v>308.7</v>
+        <v>304.4</v>
       </c>
       <c r="H56" t="n">
-        <v>30.8</v>
+        <v>26.4</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-298.51</v>
+        <v>-484.83</v>
       </c>
       <c r="K56" t="n">
-        <v>-257.69</v>
+        <v>-537.72</v>
       </c>
       <c r="L56" t="n">
-        <v>394.36</v>
+        <v>724.01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:42:33</t>
+          <t>06:32:21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="F57" t="n">
-        <v>13.56</v>
+        <v>13.8</v>
       </c>
       <c r="G57" t="n">
-        <v>304.9</v>
+        <v>303.6</v>
       </c>
       <c r="H57" t="n">
-        <v>30.8</v>
+        <v>22.5</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-416.03</v>
+        <v>325.92</v>
       </c>
       <c r="K57" t="n">
-        <v>-509.92</v>
+        <v>-212.55</v>
       </c>
       <c r="L57" t="n">
-        <v>658.1</v>
+        <v>389.11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:43:28</t>
+          <t>06:33:16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.89</v>
+        <v>5.14</v>
       </c>
       <c r="F58" t="n">
-        <v>14.05</v>
+        <v>13.04</v>
       </c>
       <c r="G58" t="n">
-        <v>299.5</v>
+        <v>300.4</v>
       </c>
       <c r="H58" t="n">
-        <v>27.2</v>
+        <v>29.3</v>
       </c>
       <c r="I58" t="n">
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>362.4</v>
+        <v>-170.06</v>
       </c>
       <c r="K58" t="n">
-        <v>-985.74</v>
+        <v>244.75</v>
       </c>
       <c r="L58" t="n">
-        <v>1050.25</v>
+        <v>298.03</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:57:48</t>
+          <t>06:43:05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.34</v>
+        <v>3.85</v>
       </c>
       <c r="F59" t="n">
-        <v>14.53</v>
+        <v>14.4</v>
       </c>
       <c r="G59" t="n">
-        <v>312.4</v>
+        <v>301.9</v>
       </c>
       <c r="H59" t="n">
-        <v>26.5</v>
+        <v>29</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>115.91</v>
+        <v>52.71</v>
       </c>
       <c r="K59" t="n">
-        <v>-70.03</v>
+        <v>106.11</v>
       </c>
       <c r="L59" t="n">
-        <v>135.43</v>
+        <v>118.49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:59:40</t>
+          <t>06:45:29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.35</v>
+        <v>4.51</v>
       </c>
       <c r="F60" t="n">
-        <v>14.14</v>
+        <v>13.89</v>
       </c>
       <c r="G60" t="n">
-        <v>299.5</v>
+        <v>292.3</v>
       </c>
       <c r="H60" t="n">
-        <v>24.5</v>
+        <v>30.3</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-25.52</v>
+        <v>105.33</v>
       </c>
       <c r="K60" t="n">
-        <v>-31.15</v>
+        <v>72.95</v>
       </c>
       <c r="L60" t="n">
-        <v>40.27</v>
+        <v>128.13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:01:11</t>
+          <t>06:47:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.64</v>
+        <v>4.98</v>
       </c>
       <c r="F61" t="n">
-        <v>13.38</v>
+        <v>13.29</v>
       </c>
       <c r="G61" t="n">
-        <v>304.1</v>
+        <v>312.1</v>
       </c>
       <c r="H61" t="n">
-        <v>29.8</v>
+        <v>27.3</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-103.7</v>
+        <v>-94.98</v>
       </c>
       <c r="K61" t="n">
-        <v>18.7</v>
+        <v>95.95</v>
       </c>
       <c r="L61" t="n">
-        <v>105.38</v>
+        <v>135.01</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:07:01</t>
+          <t>06:52:42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.1</v>
+        <v>4.83</v>
       </c>
       <c r="F62" t="n">
-        <v>13.77</v>
+        <v>14.03</v>
       </c>
       <c r="G62" t="n">
-        <v>315.1</v>
+        <v>301.6</v>
       </c>
       <c r="H62" t="n">
-        <v>26.2</v>
+        <v>23.9</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>63.97</v>
+        <v>168.17</v>
       </c>
       <c r="K62" t="n">
-        <v>206.51</v>
+        <v>32.54</v>
       </c>
       <c r="L62" t="n">
-        <v>216.19</v>
+        <v>171.29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:08:25</t>
+          <t>06:54:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.5</v>
+        <v>4.12</v>
       </c>
       <c r="F63" t="n">
-        <v>14.52</v>
+        <v>14.13</v>
       </c>
       <c r="G63" t="n">
-        <v>305.2</v>
+        <v>278.3</v>
       </c>
       <c r="H63" t="n">
-        <v>30.4</v>
+        <v>34.7</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>387.9</v>
+        <v>-38.39</v>
       </c>
       <c r="K63" t="n">
-        <v>57.09</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>392.08</v>
+        <v>84.04000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:10:08</t>
+          <t>06:56:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.81</v>
+        <v>4.58</v>
       </c>
       <c r="F64" t="n">
-        <v>14.8</v>
+        <v>14.08</v>
       </c>
       <c r="G64" t="n">
-        <v>295.7</v>
+        <v>311.6</v>
       </c>
       <c r="H64" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>-82.27</v>
+        <v>161.53</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.46</v>
+        <v>-225.04</v>
       </c>
       <c r="L64" t="n">
-        <v>99.20999999999999</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:14:35</t>
+          <t>07:00:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.69</v>
+        <v>4.47</v>
       </c>
       <c r="F65" t="n">
-        <v>13.59</v>
+        <v>13.87</v>
       </c>
       <c r="G65" t="n">
-        <v>304.2</v>
+        <v>284.9</v>
       </c>
       <c r="H65" t="n">
-        <v>27.9</v>
+        <v>25.4</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-198.32</v>
+        <v>152.79</v>
       </c>
       <c r="K65" t="n">
-        <v>-139.21</v>
+        <v>519.6</v>
       </c>
       <c r="L65" t="n">
-        <v>242.3</v>
+        <v>541.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:15:58</t>
+          <t>07:01:53</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.02</v>
+        <v>5.36</v>
       </c>
       <c r="F66" t="n">
-        <v>14.88</v>
+        <v>13.95</v>
       </c>
       <c r="G66" t="n">
-        <v>294.9</v>
+        <v>315.1</v>
       </c>
       <c r="H66" t="n">
-        <v>29.3</v>
+        <v>24.5</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-223.11</v>
+        <v>-135.89</v>
       </c>
       <c r="K66" t="n">
-        <v>307.83</v>
+        <v>-308.64</v>
       </c>
       <c r="L66" t="n">
-        <v>380.19</v>
+        <v>337.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:17:24</t>
+          <t>07:03:16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
       <c r="F67" t="n">
-        <v>14.24</v>
+        <v>14.18</v>
       </c>
       <c r="G67" t="n">
-        <v>292.1</v>
+        <v>289.3</v>
       </c>
       <c r="H67" t="n">
-        <v>27.3</v>
+        <v>23</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-30.4</v>
+        <v>-180.76</v>
       </c>
       <c r="K67" t="n">
-        <v>301.45</v>
+        <v>-115.19</v>
       </c>
       <c r="L67" t="n">
-        <v>302.98</v>
+        <v>214.34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:23:01</t>
+          <t>07:08:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.08</v>
+        <v>4.92</v>
       </c>
       <c r="F68" t="n">
-        <v>14.45</v>
+        <v>14.48</v>
       </c>
       <c r="G68" t="n">
-        <v>307.8</v>
+        <v>302.8</v>
       </c>
       <c r="H68" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-211.39</v>
+        <v>-100.07</v>
       </c>
       <c r="K68" t="n">
-        <v>-205.15</v>
+        <v>35.91</v>
       </c>
       <c r="L68" t="n">
-        <v>294.57</v>
+        <v>106.32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:24:29</t>
+          <t>07:09:21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.82</v>
+        <v>4.16</v>
       </c>
       <c r="F69" t="n">
-        <v>14.38</v>
+        <v>14.1</v>
       </c>
       <c r="G69" t="n">
-        <v>313.2</v>
+        <v>292.6</v>
       </c>
       <c r="H69" t="n">
-        <v>25.3</v>
+        <v>30.3</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-178.78</v>
+        <v>531.26</v>
       </c>
       <c r="K69" t="n">
-        <v>57.34</v>
+        <v>367.54</v>
       </c>
       <c r="L69" t="n">
-        <v>187.75</v>
+        <v>646</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:25:36</t>
+          <t>07:11:13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.31</v>
+        <v>4.22</v>
       </c>
       <c r="F70" t="n">
-        <v>13.9</v>
+        <v>13.79</v>
       </c>
       <c r="G70" t="n">
-        <v>309</v>
+        <v>304.4</v>
       </c>
       <c r="H70" t="n">
-        <v>33.9</v>
+        <v>26.2</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>468.05</v>
+        <v>-133.41</v>
       </c>
       <c r="K70" t="n">
-        <v>-341.1</v>
+        <v>228.6</v>
       </c>
       <c r="L70" t="n">
-        <v>579.16</v>
+        <v>264.68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:31:00</t>
+          <t>07:17:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.96</v>
+        <v>4.91</v>
       </c>
       <c r="F71" t="n">
-        <v>14.42</v>
+        <v>13.99</v>
       </c>
       <c r="G71" t="n">
-        <v>301.5</v>
+        <v>306.3</v>
       </c>
       <c r="H71" t="n">
-        <v>25.9</v>
+        <v>29.7</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>136.58</v>
+        <v>593.4</v>
       </c>
       <c r="K71" t="n">
-        <v>426.98</v>
+        <v>109.27</v>
       </c>
       <c r="L71" t="n">
-        <v>448.29</v>
+        <v>603.38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:32:18</t>
+          <t>07:19:43</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.17</v>
+        <v>4.8</v>
       </c>
       <c r="F72" t="n">
-        <v>14.29</v>
+        <v>14.18</v>
       </c>
       <c r="G72" t="n">
-        <v>296.3</v>
+        <v>298.6</v>
       </c>
       <c r="H72" t="n">
-        <v>32.6</v>
+        <v>27.2</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-121.92</v>
+        <v>-151.21</v>
       </c>
       <c r="K72" t="n">
-        <v>185.36</v>
+        <v>-290.18</v>
       </c>
       <c r="L72" t="n">
-        <v>221.87</v>
+        <v>327.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:33:31</t>
+          <t>07:21:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.8</v>
+        <v>4.84</v>
       </c>
       <c r="F73" t="n">
-        <v>13.77</v>
+        <v>14.15</v>
       </c>
       <c r="G73" t="n">
-        <v>304.7</v>
+        <v>306.8</v>
       </c>
       <c r="H73" t="n">
-        <v>36.5</v>
+        <v>20.1</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-1060.75</v>
+        <v>249.57</v>
       </c>
       <c r="K73" t="n">
-        <v>1062.52</v>
+        <v>-538.03</v>
       </c>
       <c r="L73" t="n">
-        <v>1501.38</v>
+        <v>593.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:46:40</t>
+          <t>07:30:11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.04</v>
+        <v>5.29</v>
       </c>
       <c r="F74" t="n">
-        <v>14.21</v>
+        <v>13.94</v>
       </c>
       <c r="G74" t="n">
-        <v>296.2</v>
+        <v>303.5</v>
       </c>
       <c r="H74" t="n">
-        <v>23.6</v>
+        <v>19</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-71.55</v>
+        <v>-120.86</v>
       </c>
       <c r="K74" t="n">
-        <v>-112.05</v>
+        <v>-16.58</v>
       </c>
       <c r="L74" t="n">
-        <v>132.94</v>
+        <v>121.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:48:03</t>
+          <t>07:32:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.81</v>
+        <v>4.61</v>
       </c>
       <c r="F75" t="n">
-        <v>14.34</v>
+        <v>13.65</v>
       </c>
       <c r="G75" t="n">
-        <v>306.3</v>
+        <v>296.2</v>
       </c>
       <c r="H75" t="n">
-        <v>23.3</v>
+        <v>27.1</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-115.63</v>
+        <v>-200.11</v>
       </c>
       <c r="K75" t="n">
-        <v>21.34</v>
+        <v>22.44</v>
       </c>
       <c r="L75" t="n">
-        <v>117.58</v>
+        <v>201.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:50:10</t>
+          <t>07:33:06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.55</v>
+        <v>4.57</v>
       </c>
       <c r="F76" t="n">
-        <v>14.03</v>
+        <v>14.1</v>
       </c>
       <c r="G76" t="n">
-        <v>305.2</v>
+        <v>297.1</v>
       </c>
       <c r="H76" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>8.039999999999999</v>
+        <v>73</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.47</v>
+        <v>-111.92</v>
       </c>
       <c r="L76" t="n">
-        <v>8.75</v>
+        <v>133.62</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:53:53</t>
+          <t>07:37:55</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.83</v>
+        <v>4.8</v>
       </c>
       <c r="F77" t="n">
-        <v>14.55</v>
+        <v>13.68</v>
       </c>
       <c r="G77" t="n">
-        <v>294.1</v>
+        <v>294.5</v>
       </c>
       <c r="H77" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-169.06</v>
+        <v>-95.75</v>
       </c>
       <c r="K77" t="n">
-        <v>177.26</v>
+        <v>-190.59</v>
       </c>
       <c r="L77" t="n">
-        <v>244.95</v>
+        <v>213.29</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:56:18</t>
+          <t>07:39:07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.21</v>
+        <v>5.45</v>
       </c>
       <c r="F78" t="n">
-        <v>13.25</v>
+        <v>14.34</v>
       </c>
       <c r="G78" t="n">
-        <v>296.7</v>
+        <v>290.3</v>
       </c>
       <c r="H78" t="n">
-        <v>27.9</v>
+        <v>20.4</v>
       </c>
       <c r="I78" t="n">
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>38.82</v>
+        <v>274.76</v>
       </c>
       <c r="K78" t="n">
-        <v>119.67</v>
+        <v>122.24</v>
       </c>
       <c r="L78" t="n">
-        <v>125.81</v>
+        <v>300.72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:57:24</t>
+          <t>07:41:03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.85</v>
+        <v>4.99</v>
       </c>
       <c r="F79" t="n">
-        <v>14.54</v>
+        <v>14.27</v>
       </c>
       <c r="G79" t="n">
-        <v>301.7</v>
+        <v>312.5</v>
       </c>
       <c r="H79" t="n">
-        <v>27.6</v>
+        <v>23</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>-146.84</v>
+        <v>119.6</v>
       </c>
       <c r="K79" t="n">
-        <v>166.35</v>
+        <v>359.55</v>
       </c>
       <c r="L79" t="n">
-        <v>221.89</v>
+        <v>378.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:01:53</t>
+          <t>07:46:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.98</v>
+        <v>4.77</v>
       </c>
       <c r="F80" t="n">
-        <v>13.77</v>
+        <v>13.5</v>
       </c>
       <c r="G80" t="n">
-        <v>296.1</v>
+        <v>302.8</v>
       </c>
       <c r="H80" t="n">
-        <v>30.1</v>
+        <v>26.4</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>39.77</v>
+        <v>-13.98</v>
       </c>
       <c r="K80" t="n">
-        <v>-128.33</v>
+        <v>472.57</v>
       </c>
       <c r="L80" t="n">
-        <v>134.35</v>
+        <v>472.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:02:55</t>
+          <t>07:48:20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.98</v>
+        <v>4.07</v>
       </c>
       <c r="F81" t="n">
-        <v>13.68</v>
+        <v>13.77</v>
       </c>
       <c r="G81" t="n">
-        <v>301.3</v>
+        <v>300.7</v>
       </c>
       <c r="H81" t="n">
-        <v>35.3</v>
+        <v>27.1</v>
       </c>
       <c r="I81" t="n">
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>55.34</v>
+        <v>-405.25</v>
       </c>
       <c r="K81" t="n">
-        <v>-367.67</v>
+        <v>-122.52</v>
       </c>
       <c r="L81" t="n">
-        <v>371.82</v>
+        <v>423.37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:04:23</t>
+          <t>07:49:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.24</v>
+        <v>4.43</v>
       </c>
       <c r="F82" t="n">
-        <v>14.79</v>
+        <v>13.92</v>
       </c>
       <c r="G82" t="n">
-        <v>299.4</v>
+        <v>298.3</v>
       </c>
       <c r="H82" t="n">
-        <v>28.3</v>
+        <v>24.9</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>380.26</v>
+        <v>-125.9</v>
       </c>
       <c r="K82" t="n">
-        <v>-44.73</v>
+        <v>-203.62</v>
       </c>
       <c r="L82" t="n">
-        <v>382.88</v>
+        <v>239.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:08:39</t>
+          <t>07:52:45</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.1</v>
+        <v>4.93</v>
       </c>
       <c r="F83" t="n">
-        <v>14.04</v>
+        <v>13.28</v>
       </c>
       <c r="G83" t="n">
-        <v>299.5</v>
+        <v>301.1</v>
       </c>
       <c r="H83" t="n">
-        <v>30.2</v>
+        <v>25.7</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-213.28</v>
+        <v>-186.36</v>
       </c>
       <c r="K83" t="n">
-        <v>-291.82</v>
+        <v>-281.25</v>
       </c>
       <c r="L83" t="n">
-        <v>361.46</v>
+        <v>337.4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:11:10</t>
+          <t>07:54:55</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.32</v>
+        <v>4.56</v>
       </c>
       <c r="F84" t="n">
-        <v>13.88</v>
+        <v>13.73</v>
       </c>
       <c r="G84" t="n">
-        <v>306.5</v>
+        <v>310.8</v>
       </c>
       <c r="H84" t="n">
-        <v>31.4</v>
+        <v>32.1</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>73</v>
+        <v>-201.66</v>
       </c>
       <c r="K84" t="n">
-        <v>-600.7</v>
+        <v>299.07</v>
       </c>
       <c r="L84" t="n">
-        <v>605.12</v>
+        <v>360.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:13:04</t>
+          <t>07:55:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.67</v>
+        <v>4.97</v>
       </c>
       <c r="F85" t="n">
-        <v>15.07</v>
+        <v>14.1</v>
       </c>
       <c r="G85" t="n">
-        <v>289.5</v>
+        <v>313</v>
       </c>
       <c r="H85" t="n">
-        <v>24.2</v>
+        <v>25.7</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-549.88</v>
+        <v>-111.38</v>
       </c>
       <c r="K85" t="n">
-        <v>-311.48</v>
+        <v>415.43</v>
       </c>
       <c r="L85" t="n">
-        <v>631.97</v>
+        <v>430.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:18:21</t>
+          <t>07:59:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.42</v>
+        <v>4.72</v>
       </c>
       <c r="F86" t="n">
-        <v>13.92</v>
+        <v>14.36</v>
       </c>
       <c r="G86" t="n">
-        <v>302.2</v>
+        <v>296</v>
       </c>
       <c r="H86" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-266.87</v>
+        <v>279.18</v>
       </c>
       <c r="K86" t="n">
-        <v>-307.23</v>
+        <v>206.3</v>
       </c>
       <c r="L86" t="n">
-        <v>406.95</v>
+        <v>347.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:20:07</t>
+          <t>08:01:47</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.44</v>
+        <v>4.52</v>
       </c>
       <c r="F87" t="n">
-        <v>14.96</v>
+        <v>13.95</v>
       </c>
       <c r="G87" t="n">
-        <v>300.8</v>
+        <v>317.2</v>
       </c>
       <c r="H87" t="n">
-        <v>23.3</v>
+        <v>29.5</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-48.7</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-180.96</v>
+        <v>112.64</v>
       </c>
       <c r="L87" t="n">
-        <v>187.4</v>
+        <v>136</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:21:31</t>
+          <t>08:03:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="F88" t="n">
-        <v>14.46</v>
+        <v>13.74</v>
       </c>
       <c r="G88" t="n">
-        <v>306.8</v>
+        <v>299.8</v>
       </c>
       <c r="H88" t="n">
-        <v>31.5</v>
+        <v>29.4</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>511.01</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>-219.63</v>
+        <v>-78.48999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>556.21</v>
+        <v>110.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-90.86</v>
+        <v>-70.61</v>
       </c>
       <c r="K14" t="n">
-        <v>-305.56</v>
+        <v>-237.46</v>
       </c>
       <c r="L14" t="n">
-        <v>318.78</v>
+        <v>247.74</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>56.15</v>
+        <v>63.23</v>
       </c>
       <c r="K15" t="n">
-        <v>-45.56</v>
+        <v>-51.29</v>
       </c>
       <c r="L15" t="n">
-        <v>72.31</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.84</v>
+        <v>-10.93</v>
       </c>
       <c r="K16" t="n">
-        <v>-114.59</v>
+        <v>-115.57</v>
       </c>
       <c r="L16" t="n">
-        <v>115.11</v>
+        <v>116.08</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>143.89</v>
+        <v>162.76</v>
       </c>
       <c r="K17" t="n">
-        <v>-39.83</v>
+        <v>-45.06</v>
       </c>
       <c r="L17" t="n">
-        <v>149.3</v>
+        <v>168.88</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>2.62</v>
+        <v>6.14</v>
       </c>
       <c r="K18" t="n">
-        <v>45.99</v>
+        <v>107.92</v>
       </c>
       <c r="L18" t="n">
-        <v>46.06</v>
+        <v>108.09</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-89.92</v>
+        <v>-110.79</v>
       </c>
       <c r="K19" t="n">
-        <v>-78.5</v>
+        <v>-96.72</v>
       </c>
       <c r="L19" t="n">
-        <v>119.36</v>
+        <v>147.07</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>373.43</v>
+        <v>408.35</v>
       </c>
       <c r="K20" t="n">
-        <v>-138.08</v>
+        <v>-150.99</v>
       </c>
       <c r="L20" t="n">
-        <v>398.14</v>
+        <v>435.37</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-211.1</v>
+        <v>-213.21</v>
       </c>
       <c r="K21" t="n">
-        <v>131.09</v>
+        <v>132.4</v>
       </c>
       <c r="L21" t="n">
-        <v>248.49</v>
+        <v>250.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-40.31</v>
+        <v>-48.07</v>
       </c>
       <c r="K22" t="n">
-        <v>-309.62</v>
+        <v>-369.19</v>
       </c>
       <c r="L22" t="n">
-        <v>312.23</v>
+        <v>372.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>36.47</v>
+        <v>50.79</v>
       </c>
       <c r="K23" t="n">
-        <v>-391</v>
+        <v>-544.41</v>
       </c>
       <c r="L23" t="n">
-        <v>392.7</v>
+        <v>546.77</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-54.36</v>
+        <v>-61.4</v>
       </c>
       <c r="K24" t="n">
-        <v>-320.6</v>
+        <v>-362.1</v>
       </c>
       <c r="L24" t="n">
-        <v>325.17</v>
+        <v>367.27</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>174.78</v>
+        <v>206.36</v>
       </c>
       <c r="K25" t="n">
-        <v>350.24</v>
+        <v>413.52</v>
       </c>
       <c r="L25" t="n">
-        <v>391.43</v>
+        <v>462.15</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-716.23</v>
+        <v>-763.3099999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>158.55</v>
+        <v>168.97</v>
       </c>
       <c r="L26" t="n">
-        <v>733.5700000000001</v>
+        <v>781.79</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-309.88</v>
+        <v>-323.99</v>
       </c>
       <c r="K27" t="n">
-        <v>291.79</v>
+        <v>305.08</v>
       </c>
       <c r="L27" t="n">
-        <v>425.64</v>
+        <v>445.02</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-359.96</v>
+        <v>-481.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-161.78</v>
+        <v>-216.4</v>
       </c>
       <c r="L28" t="n">
-        <v>394.65</v>
+        <v>527.89</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.93</v>
+        <v>-29.73</v>
       </c>
       <c r="K29" t="n">
-        <v>123.1</v>
+        <v>131.05</v>
       </c>
       <c r="L29" t="n">
-        <v>126.23</v>
+        <v>134.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="K30" t="n">
-        <v>146.32</v>
+        <v>145.69</v>
       </c>
       <c r="L30" t="n">
-        <v>146.35</v>
+        <v>145.73</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>201.22</v>
+        <v>216.97</v>
       </c>
       <c r="K31" t="n">
-        <v>74.86</v>
+        <v>80.72</v>
       </c>
       <c r="L31" t="n">
-        <v>214.69</v>
+        <v>231.5</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>90.65000000000001</v>
+        <v>85.45</v>
       </c>
       <c r="K32" t="n">
-        <v>160.59</v>
+        <v>151.37</v>
       </c>
       <c r="L32" t="n">
-        <v>184.41</v>
+        <v>173.82</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>47.02</v>
+        <v>103.33</v>
       </c>
       <c r="K33" t="n">
-        <v>7.21</v>
+        <v>15.85</v>
       </c>
       <c r="L33" t="n">
-        <v>47.57</v>
+        <v>104.54</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>35.28</v>
+        <v>28.56</v>
       </c>
       <c r="K34" t="n">
-        <v>364.01</v>
+        <v>294.59</v>
       </c>
       <c r="L34" t="n">
-        <v>365.71</v>
+        <v>295.97</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-57.32</v>
+        <v>-62.92</v>
       </c>
       <c r="K35" t="n">
-        <v>-272.51</v>
+        <v>-299.17</v>
       </c>
       <c r="L35" t="n">
-        <v>278.47</v>
+        <v>305.71</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>188.1</v>
+        <v>273.84</v>
       </c>
       <c r="K36" t="n">
-        <v>139.41</v>
+        <v>202.96</v>
       </c>
       <c r="L36" t="n">
-        <v>234.13</v>
+        <v>340.85</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-220.67</v>
+        <v>-203.91</v>
       </c>
       <c r="K37" t="n">
-        <v>-37.29</v>
+        <v>-34.46</v>
       </c>
       <c r="L37" t="n">
-        <v>223.8</v>
+        <v>206.8</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-323.14</v>
+        <v>-357.7</v>
       </c>
       <c r="K38" t="n">
-        <v>-349.76</v>
+        <v>-387.17</v>
       </c>
       <c r="L38" t="n">
-        <v>476.19</v>
+        <v>527.12</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-41.44</v>
+        <v>-55.57</v>
       </c>
       <c r="K39" t="n">
-        <v>305.77</v>
+        <v>410.04</v>
       </c>
       <c r="L39" t="n">
-        <v>308.57</v>
+        <v>413.79</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>218.77</v>
+        <v>309.43</v>
       </c>
       <c r="K40" t="n">
-        <v>195.6</v>
+        <v>276.65</v>
       </c>
       <c r="L40" t="n">
-        <v>293.46</v>
+        <v>415.07</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>514.72</v>
+        <v>583.91</v>
       </c>
       <c r="K41" t="n">
-        <v>747.8200000000001</v>
+        <v>848.34</v>
       </c>
       <c r="L41" t="n">
-        <v>907.84</v>
+        <v>1029.87</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-156.78</v>
+        <v>-196.25</v>
       </c>
       <c r="K42" t="n">
-        <v>-580.02</v>
+        <v>-726.0599999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>600.84</v>
+        <v>752.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>768.26</v>
+        <v>1013.06</v>
       </c>
       <c r="K43" t="n">
-        <v>-87.03</v>
+        <v>-114.76</v>
       </c>
       <c r="L43" t="n">
-        <v>773.1799999999999</v>
+        <v>1019.54</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>5.38</v>
+        <v>5.84</v>
       </c>
       <c r="K44" t="n">
-        <v>146.13</v>
+        <v>158.79</v>
       </c>
       <c r="L44" t="n">
-        <v>146.23</v>
+        <v>158.9</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.09</v>
+        <v>-47.75</v>
       </c>
       <c r="K45" t="n">
-        <v>-231.13</v>
+        <v>-234.36</v>
       </c>
       <c r="L45" t="n">
-        <v>235.88</v>
+        <v>239.18</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>41.46</v>
+        <v>78.69</v>
       </c>
       <c r="K46" t="n">
-        <v>21.87</v>
+        <v>41.52</v>
       </c>
       <c r="L46" t="n">
-        <v>46.87</v>
+        <v>88.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>48.12</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-30.56</v>
+        <v>-60.66</v>
       </c>
       <c r="L47" t="n">
-        <v>57.01</v>
+        <v>113.17</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>119.1</v>
+        <v>142.75</v>
       </c>
       <c r="K48" t="n">
-        <v>-124.02</v>
+        <v>-148.64</v>
       </c>
       <c r="L48" t="n">
-        <v>171.95</v>
+        <v>206.08</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>219.8</v>
+        <v>218.45</v>
       </c>
       <c r="K49" t="n">
-        <v>112.64</v>
+        <v>111.95</v>
       </c>
       <c r="L49" t="n">
-        <v>246.98</v>
+        <v>245.46</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-25.53</v>
+        <v>-40.84</v>
       </c>
       <c r="K50" t="n">
-        <v>-154.21</v>
+        <v>-246.68</v>
       </c>
       <c r="L50" t="n">
-        <v>156.31</v>
+        <v>250.04</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>17.73</v>
+        <v>33.04</v>
       </c>
       <c r="K51" t="n">
-        <v>-117.65</v>
+        <v>-219.21</v>
       </c>
       <c r="L51" t="n">
-        <v>118.98</v>
+        <v>221.68</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-231.18</v>
+        <v>-278.9</v>
       </c>
       <c r="K52" t="n">
-        <v>96.93000000000001</v>
+        <v>116.94</v>
       </c>
       <c r="L52" t="n">
-        <v>250.68</v>
+        <v>302.42</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>284.83</v>
+        <v>356.63</v>
       </c>
       <c r="K53" t="n">
-        <v>47.29</v>
+        <v>59.21</v>
       </c>
       <c r="L53" t="n">
-        <v>288.73</v>
+        <v>361.51</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>398.09</v>
+        <v>480.46</v>
       </c>
       <c r="K54" t="n">
-        <v>-353.34</v>
+        <v>-426.45</v>
       </c>
       <c r="L54" t="n">
-        <v>532.29</v>
+        <v>642.41</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-96.25</v>
+        <v>-130.85</v>
       </c>
       <c r="K55" t="n">
-        <v>-335.84</v>
+        <v>-456.58</v>
       </c>
       <c r="L55" t="n">
-        <v>349.36</v>
+        <v>474.96</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-484.83</v>
+        <v>-653.12</v>
       </c>
       <c r="K56" t="n">
-        <v>-537.72</v>
+        <v>-724.37</v>
       </c>
       <c r="L56" t="n">
-        <v>724.01</v>
+        <v>975.34</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>325.92</v>
+        <v>489.99</v>
       </c>
       <c r="K57" t="n">
-        <v>-212.55</v>
+        <v>-319.54</v>
       </c>
       <c r="L57" t="n">
-        <v>389.11</v>
+        <v>584.97</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-170.06</v>
+        <v>-321.27</v>
       </c>
       <c r="K58" t="n">
-        <v>244.75</v>
+        <v>462.36</v>
       </c>
       <c r="L58" t="n">
-        <v>298.03</v>
+        <v>563.02</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>52.71</v>
+        <v>55.43</v>
       </c>
       <c r="K59" t="n">
-        <v>106.11</v>
+        <v>111.58</v>
       </c>
       <c r="L59" t="n">
-        <v>118.49</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>105.33</v>
+        <v>125.78</v>
       </c>
       <c r="K60" t="n">
-        <v>72.95</v>
+        <v>87.12</v>
       </c>
       <c r="L60" t="n">
-        <v>128.13</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-94.98</v>
+        <v>-118.99</v>
       </c>
       <c r="K61" t="n">
-        <v>95.95</v>
+        <v>120.2</v>
       </c>
       <c r="L61" t="n">
-        <v>135.01</v>
+        <v>169.13</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>168.17</v>
+        <v>203.83</v>
       </c>
       <c r="K62" t="n">
-        <v>32.54</v>
+        <v>39.44</v>
       </c>
       <c r="L62" t="n">
-        <v>171.29</v>
+        <v>207.61</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-38.39</v>
+        <v>-52.81</v>
       </c>
       <c r="K63" t="n">
-        <v>-74.76000000000001</v>
+        <v>-102.84</v>
       </c>
       <c r="L63" t="n">
-        <v>84.04000000000001</v>
+        <v>115.61</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>161.53</v>
+        <v>148.33</v>
       </c>
       <c r="K64" t="n">
-        <v>-225.04</v>
+        <v>-206.66</v>
       </c>
       <c r="L64" t="n">
-        <v>277</v>
+        <v>254.38</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>152.79</v>
+        <v>162.38</v>
       </c>
       <c r="K65" t="n">
-        <v>519.6</v>
+        <v>552.21</v>
       </c>
       <c r="L65" t="n">
-        <v>541.6</v>
+        <v>575.59</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-135.89</v>
+        <v>-175.04</v>
       </c>
       <c r="K66" t="n">
-        <v>-308.64</v>
+        <v>-397.57</v>
       </c>
       <c r="L66" t="n">
-        <v>337.23</v>
+        <v>434.4</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-180.76</v>
+        <v>-267.48</v>
       </c>
       <c r="K67" t="n">
-        <v>-115.19</v>
+        <v>-170.44</v>
       </c>
       <c r="L67" t="n">
-        <v>214.34</v>
+        <v>317.17</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-100.07</v>
+        <v>-281.62</v>
       </c>
       <c r="K68" t="n">
-        <v>35.91</v>
+        <v>101.07</v>
       </c>
       <c r="L68" t="n">
-        <v>106.32</v>
+        <v>299.21</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>531.26</v>
+        <v>566.76</v>
       </c>
       <c r="K69" t="n">
-        <v>367.54</v>
+        <v>392.1</v>
       </c>
       <c r="L69" t="n">
-        <v>646</v>
+        <v>689.17</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-133.41</v>
+        <v>-168.1</v>
       </c>
       <c r="K70" t="n">
-        <v>228.6</v>
+        <v>288.03</v>
       </c>
       <c r="L70" t="n">
-        <v>264.68</v>
+        <v>333.5</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>593.4</v>
+        <v>691.3099999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>109.27</v>
+        <v>127.3</v>
       </c>
       <c r="L71" t="n">
-        <v>603.38</v>
+        <v>702.9400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-151.21</v>
+        <v>-228.98</v>
       </c>
       <c r="K72" t="n">
-        <v>-290.18</v>
+        <v>-439.42</v>
       </c>
       <c r="L72" t="n">
-        <v>327.22</v>
+        <v>495.5</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>249.57</v>
+        <v>340.69</v>
       </c>
       <c r="K73" t="n">
-        <v>-538.03</v>
+        <v>-734.46</v>
       </c>
       <c r="L73" t="n">
-        <v>593.1</v>
+        <v>809.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-120.86</v>
+        <v>-142.26</v>
       </c>
       <c r="K74" t="n">
-        <v>-16.58</v>
+        <v>-19.51</v>
       </c>
       <c r="L74" t="n">
-        <v>121.99</v>
+        <v>143.6</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-200.11</v>
+        <v>-228.52</v>
       </c>
       <c r="K75" t="n">
-        <v>22.44</v>
+        <v>25.62</v>
       </c>
       <c r="L75" t="n">
-        <v>201.37</v>
+        <v>229.95</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>73</v>
+        <v>86.31</v>
       </c>
       <c r="K76" t="n">
-        <v>-111.92</v>
+        <v>-132.32</v>
       </c>
       <c r="L76" t="n">
-        <v>133.62</v>
+        <v>157.98</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-95.75</v>
+        <v>-97.26000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-190.59</v>
+        <v>-193.59</v>
       </c>
       <c r="L77" t="n">
-        <v>213.29</v>
+        <v>216.64</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>274.76</v>
+        <v>301.88</v>
       </c>
       <c r="K78" t="n">
-        <v>122.24</v>
+        <v>134.3</v>
       </c>
       <c r="L78" t="n">
-        <v>300.72</v>
+        <v>330.4</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>119.6</v>
+        <v>104.93</v>
       </c>
       <c r="K79" t="n">
-        <v>359.55</v>
+        <v>315.47</v>
       </c>
       <c r="L79" t="n">
-        <v>378.92</v>
+        <v>332.46</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.98</v>
+        <v>-12.73</v>
       </c>
       <c r="K80" t="n">
-        <v>472.57</v>
+        <v>430.23</v>
       </c>
       <c r="L80" t="n">
-        <v>472.78</v>
+        <v>430.42</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-405.25</v>
+        <v>-437.75</v>
       </c>
       <c r="K81" t="n">
-        <v>-122.52</v>
+        <v>-132.35</v>
       </c>
       <c r="L81" t="n">
-        <v>423.37</v>
+        <v>457.32</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-125.9</v>
+        <v>-132.88</v>
       </c>
       <c r="K82" t="n">
-        <v>-203.62</v>
+        <v>-214.91</v>
       </c>
       <c r="L82" t="n">
-        <v>239.4</v>
+        <v>252.67</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-186.36</v>
+        <v>-255.63</v>
       </c>
       <c r="K83" t="n">
-        <v>-281.25</v>
+        <v>-385.78</v>
       </c>
       <c r="L83" t="n">
-        <v>337.4</v>
+        <v>462.79</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-201.66</v>
+        <v>-279.53</v>
       </c>
       <c r="K84" t="n">
-        <v>299.07</v>
+        <v>414.56</v>
       </c>
       <c r="L84" t="n">
-        <v>360.71</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-111.38</v>
+        <v>-128.43</v>
       </c>
       <c r="K85" t="n">
-        <v>415.43</v>
+        <v>479.03</v>
       </c>
       <c r="L85" t="n">
-        <v>430.1</v>
+        <v>495.95</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>279.18</v>
+        <v>460.81</v>
       </c>
       <c r="K86" t="n">
-        <v>206.3</v>
+        <v>340.52</v>
       </c>
       <c r="L86" t="n">
-        <v>347.14</v>
+        <v>572.98</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-76.20999999999999</v>
+        <v>-187.46</v>
       </c>
       <c r="K87" t="n">
-        <v>112.64</v>
+        <v>277.05</v>
       </c>
       <c r="L87" t="n">
-        <v>136</v>
+        <v>334.51</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-77.59999999999999</v>
+        <v>-211.13</v>
       </c>
       <c r="K88" t="n">
-        <v>-78.48999999999999</v>
+        <v>-213.57</v>
       </c>
       <c r="L88" t="n">
-        <v>110.38</v>
+        <v>300.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-70.61</v>
+        <v>-66.26000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-237.46</v>
+        <v>-222.82</v>
       </c>
       <c r="L14" t="n">
-        <v>247.74</v>
+        <v>232.46</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>63.23</v>
+        <v>63.91</v>
       </c>
       <c r="K15" t="n">
-        <v>-51.29</v>
+        <v>-51.85</v>
       </c>
       <c r="L15" t="n">
-        <v>81.42</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.93</v>
+        <v>-10.36</v>
       </c>
       <c r="K16" t="n">
-        <v>-115.57</v>
+        <v>-109.58</v>
       </c>
       <c r="L16" t="n">
-        <v>116.08</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>162.76</v>
+        <v>128.62</v>
       </c>
       <c r="K17" t="n">
-        <v>-45.06</v>
+        <v>-35.61</v>
       </c>
       <c r="L17" t="n">
-        <v>168.88</v>
+        <v>133.46</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>6.14</v>
+        <v>4.61</v>
       </c>
       <c r="K18" t="n">
-        <v>107.92</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>108.09</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-110.79</v>
+        <v>-87.7</v>
       </c>
       <c r="K19" t="n">
-        <v>-96.72</v>
+        <v>-76.56</v>
       </c>
       <c r="L19" t="n">
-        <v>147.07</v>
+        <v>116.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>408.35</v>
+        <v>265.85</v>
       </c>
       <c r="K20" t="n">
-        <v>-150.99</v>
+        <v>-98.3</v>
       </c>
       <c r="L20" t="n">
-        <v>435.37</v>
+        <v>283.44</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-213.21</v>
+        <v>-168.27</v>
       </c>
       <c r="K21" t="n">
-        <v>132.4</v>
+        <v>104.49</v>
       </c>
       <c r="L21" t="n">
-        <v>250.97</v>
+        <v>198.07</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-48.07</v>
+        <v>-31.17</v>
       </c>
       <c r="K22" t="n">
-        <v>-369.19</v>
+        <v>-239.36</v>
       </c>
       <c r="L22" t="n">
-        <v>372.3</v>
+        <v>241.38</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>50.79</v>
+        <v>29.65</v>
       </c>
       <c r="K23" t="n">
-        <v>-544.41</v>
+        <v>-317.82</v>
       </c>
       <c r="L23" t="n">
-        <v>546.77</v>
+        <v>319.2</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-61.4</v>
+        <v>-42.42</v>
       </c>
       <c r="K24" t="n">
-        <v>-362.1</v>
+        <v>-250.2</v>
       </c>
       <c r="L24" t="n">
-        <v>367.27</v>
+        <v>253.77</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>206.36</v>
+        <v>139.11</v>
       </c>
       <c r="K25" t="n">
-        <v>413.52</v>
+        <v>278.76</v>
       </c>
       <c r="L25" t="n">
-        <v>462.15</v>
+        <v>311.54</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-763.3099999999999</v>
+        <v>-491.14</v>
       </c>
       <c r="K26" t="n">
-        <v>168.97</v>
+        <v>108.72</v>
       </c>
       <c r="L26" t="n">
-        <v>781.79</v>
+        <v>503.03</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-323.99</v>
+        <v>-221.53</v>
       </c>
       <c r="K27" t="n">
-        <v>305.08</v>
+        <v>208.6</v>
       </c>
       <c r="L27" t="n">
-        <v>445.02</v>
+        <v>304.28</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-481.5</v>
+        <v>-278.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-216.4</v>
+        <v>-124.96</v>
       </c>
       <c r="L28" t="n">
-        <v>527.89</v>
+        <v>304.84</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.73</v>
+        <v>-25.66</v>
       </c>
       <c r="K29" t="n">
-        <v>131.05</v>
+        <v>113.08</v>
       </c>
       <c r="L29" t="n">
-        <v>134.38</v>
+        <v>115.95</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>3.09</v>
+        <v>2.76</v>
       </c>
       <c r="K30" t="n">
-        <v>145.69</v>
+        <v>130.36</v>
       </c>
       <c r="L30" t="n">
-        <v>145.73</v>
+        <v>130.39</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>216.97</v>
+        <v>172.08</v>
       </c>
       <c r="K31" t="n">
-        <v>80.72</v>
+        <v>64.02</v>
       </c>
       <c r="L31" t="n">
-        <v>231.5</v>
+        <v>183.61</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>85.45</v>
+        <v>76.73</v>
       </c>
       <c r="K32" t="n">
-        <v>151.37</v>
+        <v>135.92</v>
       </c>
       <c r="L32" t="n">
-        <v>173.82</v>
+        <v>156.08</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>103.33</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>15.85</v>
+        <v>12.74</v>
       </c>
       <c r="L33" t="n">
-        <v>104.54</v>
+        <v>84.01000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>28.56</v>
+        <v>26.43</v>
       </c>
       <c r="K34" t="n">
-        <v>294.59</v>
+        <v>272.7</v>
       </c>
       <c r="L34" t="n">
-        <v>295.97</v>
+        <v>273.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-62.92</v>
+        <v>-46.22</v>
       </c>
       <c r="K35" t="n">
-        <v>-299.17</v>
+        <v>-219.73</v>
       </c>
       <c r="L35" t="n">
-        <v>305.71</v>
+        <v>224.54</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>273.84</v>
+        <v>168.38</v>
       </c>
       <c r="K36" t="n">
-        <v>202.96</v>
+        <v>124.8</v>
       </c>
       <c r="L36" t="n">
-        <v>340.85</v>
+        <v>209.58</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-203.91</v>
+        <v>-173.53</v>
       </c>
       <c r="K37" t="n">
-        <v>-34.46</v>
+        <v>-29.32</v>
       </c>
       <c r="L37" t="n">
-        <v>206.8</v>
+        <v>175.99</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-357.7</v>
+        <v>-231.81</v>
       </c>
       <c r="K38" t="n">
-        <v>-387.17</v>
+        <v>-250.91</v>
       </c>
       <c r="L38" t="n">
-        <v>527.12</v>
+        <v>341.6</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-55.57</v>
+        <v>-34.41</v>
       </c>
       <c r="K39" t="n">
-        <v>410.04</v>
+        <v>253.89</v>
       </c>
       <c r="L39" t="n">
-        <v>413.79</v>
+        <v>256.21</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>309.43</v>
+        <v>183.96</v>
       </c>
       <c r="K40" t="n">
-        <v>276.65</v>
+        <v>164.48</v>
       </c>
       <c r="L40" t="n">
-        <v>415.07</v>
+        <v>246.77</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>583.91</v>
+        <v>310.13</v>
       </c>
       <c r="K41" t="n">
-        <v>848.34</v>
+        <v>450.58</v>
       </c>
       <c r="L41" t="n">
-        <v>1029.87</v>
+        <v>547</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-196.25</v>
+        <v>-109.75</v>
       </c>
       <c r="K42" t="n">
-        <v>-726.0599999999999</v>
+        <v>-406.05</v>
       </c>
       <c r="L42" t="n">
-        <v>752.11</v>
+        <v>420.62</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>1013.06</v>
+        <v>502.39</v>
       </c>
       <c r="K43" t="n">
-        <v>-114.76</v>
+        <v>-56.91</v>
       </c>
       <c r="L43" t="n">
-        <v>1019.54</v>
+        <v>505.6</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>5.84</v>
+        <v>4.95</v>
       </c>
       <c r="K44" t="n">
-        <v>158.79</v>
+        <v>134.48</v>
       </c>
       <c r="L44" t="n">
-        <v>158.9</v>
+        <v>134.57</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.75</v>
+        <v>-36.23</v>
       </c>
       <c r="K45" t="n">
-        <v>-234.36</v>
+        <v>-177.81</v>
       </c>
       <c r="L45" t="n">
-        <v>239.18</v>
+        <v>181.46</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>78.69</v>
+        <v>69.38</v>
       </c>
       <c r="K46" t="n">
-        <v>41.52</v>
+        <v>36.61</v>
       </c>
       <c r="L46" t="n">
-        <v>88.97</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>95.54000000000001</v>
+        <v>76.81</v>
       </c>
       <c r="K47" t="n">
-        <v>-60.66</v>
+        <v>-48.77</v>
       </c>
       <c r="L47" t="n">
-        <v>113.17</v>
+        <v>90.98</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>142.75</v>
+        <v>122.44</v>
       </c>
       <c r="K48" t="n">
-        <v>-148.64</v>
+        <v>-127.49</v>
       </c>
       <c r="L48" t="n">
-        <v>206.08</v>
+        <v>176.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>218.45</v>
+        <v>176</v>
       </c>
       <c r="K49" t="n">
-        <v>111.95</v>
+        <v>90.19</v>
       </c>
       <c r="L49" t="n">
-        <v>245.46</v>
+        <v>197.76</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-40.84</v>
+        <v>-27.21</v>
       </c>
       <c r="K50" t="n">
-        <v>-246.68</v>
+        <v>-164.36</v>
       </c>
       <c r="L50" t="n">
-        <v>250.04</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>33.04</v>
+        <v>21.99</v>
       </c>
       <c r="K51" t="n">
-        <v>-219.21</v>
+        <v>-145.88</v>
       </c>
       <c r="L51" t="n">
-        <v>221.68</v>
+        <v>147.53</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-278.9</v>
+        <v>-218.37</v>
       </c>
       <c r="K52" t="n">
-        <v>116.94</v>
+        <v>91.56</v>
       </c>
       <c r="L52" t="n">
-        <v>302.42</v>
+        <v>236.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>356.63</v>
+        <v>253.83</v>
       </c>
       <c r="K53" t="n">
-        <v>59.21</v>
+        <v>42.14</v>
       </c>
       <c r="L53" t="n">
-        <v>361.51</v>
+        <v>257.31</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>480.46</v>
+        <v>267.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-426.45</v>
+        <v>-237.37</v>
       </c>
       <c r="L54" t="n">
-        <v>642.41</v>
+        <v>357.58</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-130.85</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-456.58</v>
+        <v>-270.77</v>
       </c>
       <c r="L55" t="n">
-        <v>474.96</v>
+        <v>281.67</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-653.12</v>
+        <v>-323.89</v>
       </c>
       <c r="K56" t="n">
-        <v>-724.37</v>
+        <v>-359.22</v>
       </c>
       <c r="L56" t="n">
-        <v>975.34</v>
+        <v>483.68</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>489.99</v>
+        <v>258.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-319.54</v>
+        <v>-168.89</v>
       </c>
       <c r="L57" t="n">
-        <v>584.97</v>
+        <v>309.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-321.27</v>
+        <v>-164.43</v>
       </c>
       <c r="K58" t="n">
-        <v>462.36</v>
+        <v>236.64</v>
       </c>
       <c r="L58" t="n">
-        <v>563.02</v>
+        <v>288.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>55.43</v>
+        <v>50.1</v>
       </c>
       <c r="K59" t="n">
-        <v>111.58</v>
+        <v>100.85</v>
       </c>
       <c r="L59" t="n">
-        <v>124.59</v>
+        <v>112.61</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>125.78</v>
+        <v>105.54</v>
       </c>
       <c r="K60" t="n">
-        <v>87.12</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>153</v>
+        <v>128.39</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-118.99</v>
+        <v>-98.23</v>
       </c>
       <c r="K61" t="n">
-        <v>120.2</v>
+        <v>99.23</v>
       </c>
       <c r="L61" t="n">
-        <v>169.13</v>
+        <v>139.63</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>203.83</v>
+        <v>162.58</v>
       </c>
       <c r="K62" t="n">
-        <v>39.44</v>
+        <v>31.46</v>
       </c>
       <c r="L62" t="n">
-        <v>207.61</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-52.81</v>
+        <v>-47.04</v>
       </c>
       <c r="K63" t="n">
-        <v>-102.84</v>
+        <v>-91.61</v>
       </c>
       <c r="L63" t="n">
-        <v>115.61</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>148.33</v>
+        <v>130.21</v>
       </c>
       <c r="K64" t="n">
-        <v>-206.66</v>
+        <v>-181.41</v>
       </c>
       <c r="L64" t="n">
-        <v>254.38</v>
+        <v>223.3</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>162.38</v>
+        <v>101.47</v>
       </c>
       <c r="K65" t="n">
-        <v>552.21</v>
+        <v>345.06</v>
       </c>
       <c r="L65" t="n">
-        <v>575.59</v>
+        <v>359.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-175.04</v>
+        <v>-110.51</v>
       </c>
       <c r="K66" t="n">
-        <v>-397.57</v>
+        <v>-251.01</v>
       </c>
       <c r="L66" t="n">
-        <v>434.4</v>
+        <v>274.26</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-267.48</v>
+        <v>-170.52</v>
       </c>
       <c r="K67" t="n">
-        <v>-170.44</v>
+        <v>-108.66</v>
       </c>
       <c r="L67" t="n">
-        <v>317.17</v>
+        <v>202.2</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-281.62</v>
+        <v>-159.64</v>
       </c>
       <c r="K68" t="n">
-        <v>101.07</v>
+        <v>57.29</v>
       </c>
       <c r="L68" t="n">
-        <v>299.21</v>
+        <v>169.61</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>566.76</v>
+        <v>340.81</v>
       </c>
       <c r="K69" t="n">
-        <v>392.1</v>
+        <v>235.78</v>
       </c>
       <c r="L69" t="n">
-        <v>689.17</v>
+        <v>414.43</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-168.1</v>
+        <v>-115.4</v>
       </c>
       <c r="K70" t="n">
-        <v>288.03</v>
+        <v>197.73</v>
       </c>
       <c r="L70" t="n">
-        <v>333.5</v>
+        <v>228.94</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>691.3099999999999</v>
+        <v>423.54</v>
       </c>
       <c r="K71" t="n">
-        <v>127.3</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>702.9400000000001</v>
+        <v>430.66</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-228.98</v>
+        <v>-134.08</v>
       </c>
       <c r="K72" t="n">
-        <v>-439.42</v>
+        <v>-257.31</v>
       </c>
       <c r="L72" t="n">
-        <v>495.5</v>
+        <v>290.15</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>340.69</v>
+        <v>175.83</v>
       </c>
       <c r="K73" t="n">
-        <v>-734.46</v>
+        <v>-379.05</v>
       </c>
       <c r="L73" t="n">
-        <v>809.63</v>
+        <v>417.85</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-142.26</v>
+        <v>-134.73</v>
       </c>
       <c r="K74" t="n">
-        <v>-19.51</v>
+        <v>-18.48</v>
       </c>
       <c r="L74" t="n">
-        <v>143.6</v>
+        <v>135.99</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-228.52</v>
+        <v>-170</v>
       </c>
       <c r="K75" t="n">
-        <v>25.62</v>
+        <v>19.06</v>
       </c>
       <c r="L75" t="n">
-        <v>229.95</v>
+        <v>171.07</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>86.31</v>
+        <v>72.25</v>
       </c>
       <c r="K76" t="n">
-        <v>-132.32</v>
+        <v>-110.77</v>
       </c>
       <c r="L76" t="n">
-        <v>157.98</v>
+        <v>132.25</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-97.26000000000001</v>
+        <v>-85.23</v>
       </c>
       <c r="K77" t="n">
-        <v>-193.59</v>
+        <v>-169.65</v>
       </c>
       <c r="L77" t="n">
-        <v>216.64</v>
+        <v>189.86</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>301.88</v>
+        <v>227.16</v>
       </c>
       <c r="K78" t="n">
-        <v>134.3</v>
+        <v>101.06</v>
       </c>
       <c r="L78" t="n">
-        <v>330.4</v>
+        <v>248.63</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>104.93</v>
+        <v>91.45</v>
       </c>
       <c r="K79" t="n">
-        <v>315.47</v>
+        <v>274.92</v>
       </c>
       <c r="L79" t="n">
-        <v>332.46</v>
+        <v>289.73</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.73</v>
+        <v>-10.24</v>
       </c>
       <c r="K80" t="n">
-        <v>430.23</v>
+        <v>345.97</v>
       </c>
       <c r="L80" t="n">
-        <v>430.42</v>
+        <v>346.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-437.75</v>
+        <v>-277.55</v>
       </c>
       <c r="K81" t="n">
-        <v>-132.35</v>
+        <v>-83.91</v>
       </c>
       <c r="L81" t="n">
-        <v>457.32</v>
+        <v>289.96</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-132.88</v>
+        <v>-108.09</v>
       </c>
       <c r="K82" t="n">
-        <v>-214.91</v>
+        <v>-174.82</v>
       </c>
       <c r="L82" t="n">
-        <v>252.67</v>
+        <v>205.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-255.63</v>
+        <v>-156.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-385.78</v>
+        <v>-236.91</v>
       </c>
       <c r="L83" t="n">
-        <v>462.79</v>
+        <v>284.2</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-279.53</v>
+        <v>-159.66</v>
       </c>
       <c r="K84" t="n">
-        <v>414.56</v>
+        <v>236.78</v>
       </c>
       <c r="L84" t="n">
-        <v>500</v>
+        <v>285.58</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-128.43</v>
+        <v>-86.48</v>
       </c>
       <c r="K85" t="n">
-        <v>479.03</v>
+        <v>322.57</v>
       </c>
       <c r="L85" t="n">
-        <v>495.95</v>
+        <v>333.96</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>460.81</v>
+        <v>239</v>
       </c>
       <c r="K86" t="n">
-        <v>340.52</v>
+        <v>176.61</v>
       </c>
       <c r="L86" t="n">
-        <v>572.98</v>
+        <v>297.18</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-187.46</v>
+        <v>-107.01</v>
       </c>
       <c r="K87" t="n">
-        <v>277.05</v>
+        <v>158.16</v>
       </c>
       <c r="L87" t="n">
-        <v>334.51</v>
+        <v>190.96</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-211.13</v>
+        <v>-129.57</v>
       </c>
       <c r="K88" t="n">
-        <v>-213.57</v>
+        <v>-131.07</v>
       </c>
       <c r="L88" t="n">
-        <v>300.31</v>
+        <v>184.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-66.26000000000001</v>
+        <v>-63.04</v>
       </c>
       <c r="K14" t="n">
-        <v>-222.82</v>
+        <v>-212</v>
       </c>
       <c r="L14" t="n">
-        <v>232.46</v>
+        <v>221.17</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>63.91</v>
+        <v>59.26</v>
       </c>
       <c r="K15" t="n">
-        <v>-51.85</v>
+        <v>-48.08</v>
       </c>
       <c r="L15" t="n">
-        <v>82.3</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.36</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-109.58</v>
+        <v>-103.57</v>
       </c>
       <c r="L16" t="n">
-        <v>110.07</v>
+        <v>104.03</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>128.62</v>
+        <v>125.43</v>
       </c>
       <c r="K17" t="n">
-        <v>-35.61</v>
+        <v>-34.72</v>
       </c>
       <c r="L17" t="n">
-        <v>133.46</v>
+        <v>130.14</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="K18" t="n">
-        <v>81.01000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>81.14</v>
+        <v>80.84</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-87.7</v>
+        <v>-86.19</v>
       </c>
       <c r="K19" t="n">
-        <v>-76.56</v>
+        <v>-75.23999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>116.42</v>
+        <v>114.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>265.85</v>
+        <v>272.85</v>
       </c>
       <c r="K20" t="n">
-        <v>-98.3</v>
+        <v>-100.89</v>
       </c>
       <c r="L20" t="n">
-        <v>283.44</v>
+        <v>290.9</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-168.27</v>
+        <v>-168.55</v>
       </c>
       <c r="K21" t="n">
-        <v>104.49</v>
+        <v>104.67</v>
       </c>
       <c r="L21" t="n">
-        <v>198.07</v>
+        <v>198.4</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-31.17</v>
+        <v>-31.73</v>
       </c>
       <c r="K22" t="n">
-        <v>-239.36</v>
+        <v>-243.7</v>
       </c>
       <c r="L22" t="n">
-        <v>241.38</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>29.65</v>
+        <v>30.91</v>
       </c>
       <c r="K23" t="n">
-        <v>-317.82</v>
+        <v>-331.35</v>
       </c>
       <c r="L23" t="n">
-        <v>319.2</v>
+        <v>332.79</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-42.42</v>
+        <v>-43.34</v>
       </c>
       <c r="K24" t="n">
-        <v>-250.2</v>
+        <v>-255.57</v>
       </c>
       <c r="L24" t="n">
-        <v>253.77</v>
+        <v>259.22</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>139.11</v>
+        <v>142.86</v>
       </c>
       <c r="K25" t="n">
-        <v>278.76</v>
+        <v>286.27</v>
       </c>
       <c r="L25" t="n">
-        <v>311.54</v>
+        <v>319.94</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-491.14</v>
+        <v>-520.4400000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>108.72</v>
+        <v>115.21</v>
       </c>
       <c r="L26" t="n">
-        <v>503.03</v>
+        <v>533.04</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-221.53</v>
+        <v>-227.51</v>
       </c>
       <c r="K27" t="n">
-        <v>208.6</v>
+        <v>214.23</v>
       </c>
       <c r="L27" t="n">
-        <v>304.28</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-278.05</v>
+        <v>-294.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-124.96</v>
+        <v>-132.16</v>
       </c>
       <c r="L28" t="n">
-        <v>304.84</v>
+        <v>322.39</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.66</v>
+        <v>-24.48</v>
       </c>
       <c r="K29" t="n">
-        <v>113.08</v>
+        <v>107.9</v>
       </c>
       <c r="L29" t="n">
-        <v>115.95</v>
+        <v>110.64</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="K30" t="n">
-        <v>130.36</v>
+        <v>123.6</v>
       </c>
       <c r="L30" t="n">
-        <v>130.39</v>
+        <v>123.62</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>172.08</v>
+        <v>168.2</v>
       </c>
       <c r="K31" t="n">
-        <v>64.02</v>
+        <v>62.58</v>
       </c>
       <c r="L31" t="n">
-        <v>183.61</v>
+        <v>179.47</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>76.73</v>
+        <v>73.33</v>
       </c>
       <c r="K32" t="n">
-        <v>135.92</v>
+        <v>129.91</v>
       </c>
       <c r="L32" t="n">
-        <v>156.08</v>
+        <v>149.18</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>83.04000000000001</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>12.74</v>
+        <v>12.4</v>
       </c>
       <c r="L33" t="n">
-        <v>84.01000000000001</v>
+        <v>81.79000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>26.43</v>
+        <v>25.37</v>
       </c>
       <c r="K34" t="n">
-        <v>272.7</v>
+        <v>261.72</v>
       </c>
       <c r="L34" t="n">
-        <v>273.98</v>
+        <v>262.95</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-46.22</v>
+        <v>-46.91</v>
       </c>
       <c r="K35" t="n">
-        <v>-219.73</v>
+        <v>-223.05</v>
       </c>
       <c r="L35" t="n">
-        <v>224.54</v>
+        <v>227.93</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>168.38</v>
+        <v>171.9</v>
       </c>
       <c r="K36" t="n">
-        <v>124.8</v>
+        <v>127.41</v>
       </c>
       <c r="L36" t="n">
-        <v>209.58</v>
+        <v>213.97</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-173.53</v>
+        <v>-172.21</v>
       </c>
       <c r="K37" t="n">
-        <v>-29.32</v>
+        <v>-29.1</v>
       </c>
       <c r="L37" t="n">
-        <v>175.99</v>
+        <v>174.65</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-231.81</v>
+        <v>-239.07</v>
       </c>
       <c r="K38" t="n">
-        <v>-250.91</v>
+        <v>-258.77</v>
       </c>
       <c r="L38" t="n">
-        <v>341.6</v>
+        <v>352.3</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-34.41</v>
+        <v>-35.73</v>
       </c>
       <c r="K39" t="n">
-        <v>253.89</v>
+        <v>263.65</v>
       </c>
       <c r="L39" t="n">
-        <v>256.21</v>
+        <v>266.06</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>183.96</v>
+        <v>192.97</v>
       </c>
       <c r="K40" t="n">
-        <v>164.48</v>
+        <v>172.53</v>
       </c>
       <c r="L40" t="n">
-        <v>246.77</v>
+        <v>258.86</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>310.13</v>
+        <v>334.89</v>
       </c>
       <c r="K41" t="n">
-        <v>450.58</v>
+        <v>486.56</v>
       </c>
       <c r="L41" t="n">
-        <v>547</v>
+        <v>590.67</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-109.75</v>
+        <v>-116.58</v>
       </c>
       <c r="K42" t="n">
-        <v>-406.05</v>
+        <v>-431.3</v>
       </c>
       <c r="L42" t="n">
-        <v>420.62</v>
+        <v>446.78</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>502.39</v>
+        <v>549.4400000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-56.91</v>
+        <v>-62.24</v>
       </c>
       <c r="L43" t="n">
-        <v>505.6</v>
+        <v>552.95</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="K44" t="n">
-        <v>134.48</v>
+        <v>130.24</v>
       </c>
       <c r="L44" t="n">
-        <v>134.57</v>
+        <v>130.33</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.23</v>
+        <v>-35.79</v>
       </c>
       <c r="K45" t="n">
-        <v>-177.81</v>
+        <v>-175.65</v>
       </c>
       <c r="L45" t="n">
-        <v>181.46</v>
+        <v>179.26</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>69.38</v>
+        <v>65.88</v>
       </c>
       <c r="K46" t="n">
-        <v>36.61</v>
+        <v>34.75</v>
       </c>
       <c r="L46" t="n">
-        <v>78.45</v>
+        <v>74.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>76.81</v>
+        <v>74.8</v>
       </c>
       <c r="K47" t="n">
-        <v>-48.77</v>
+        <v>-47.49</v>
       </c>
       <c r="L47" t="n">
-        <v>90.98</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>122.44</v>
+        <v>118.31</v>
       </c>
       <c r="K48" t="n">
-        <v>-127.49</v>
+        <v>-123.2</v>
       </c>
       <c r="L48" t="n">
-        <v>176.76</v>
+        <v>170.81</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>176</v>
+        <v>169.72</v>
       </c>
       <c r="K49" t="n">
-        <v>90.19</v>
+        <v>86.98</v>
       </c>
       <c r="L49" t="n">
-        <v>197.76</v>
+        <v>190.71</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-27.21</v>
+        <v>-27.68</v>
       </c>
       <c r="K50" t="n">
-        <v>-164.36</v>
+        <v>-167.15</v>
       </c>
       <c r="L50" t="n">
-        <v>166.6</v>
+        <v>169.43</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>21.99</v>
+        <v>22.43</v>
       </c>
       <c r="K51" t="n">
-        <v>-145.88</v>
+        <v>-148.81</v>
       </c>
       <c r="L51" t="n">
-        <v>147.53</v>
+        <v>150.49</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-218.37</v>
+        <v>-216.38</v>
       </c>
       <c r="K52" t="n">
-        <v>91.56</v>
+        <v>90.72</v>
       </c>
       <c r="L52" t="n">
-        <v>236.79</v>
+        <v>234.63</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>253.83</v>
+        <v>260.3</v>
       </c>
       <c r="K53" t="n">
-        <v>42.14</v>
+        <v>43.22</v>
       </c>
       <c r="L53" t="n">
-        <v>257.31</v>
+        <v>263.87</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>267.43</v>
+        <v>283.88</v>
       </c>
       <c r="K54" t="n">
-        <v>-237.37</v>
+        <v>-251.97</v>
       </c>
       <c r="L54" t="n">
-        <v>357.58</v>
+        <v>379.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-77.59999999999999</v>
+        <v>-81.53</v>
       </c>
       <c r="K55" t="n">
-        <v>-270.77</v>
+        <v>-284.48</v>
       </c>
       <c r="L55" t="n">
-        <v>281.67</v>
+        <v>295.93</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-323.89</v>
+        <v>-351.19</v>
       </c>
       <c r="K56" t="n">
-        <v>-359.22</v>
+        <v>-389.5</v>
       </c>
       <c r="L56" t="n">
-        <v>483.68</v>
+        <v>524.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>258.98</v>
+        <v>277.57</v>
       </c>
       <c r="K57" t="n">
-        <v>-168.89</v>
+        <v>-181.01</v>
       </c>
       <c r="L57" t="n">
-        <v>309.19</v>
+        <v>331.38</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-164.43</v>
+        <v>-177.75</v>
       </c>
       <c r="K58" t="n">
-        <v>236.64</v>
+        <v>255.8</v>
       </c>
       <c r="L58" t="n">
-        <v>288.16</v>
+        <v>311.49</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>50.1</v>
+        <v>47.6</v>
       </c>
       <c r="K59" t="n">
-        <v>100.85</v>
+        <v>95.83</v>
       </c>
       <c r="L59" t="n">
-        <v>112.61</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>105.54</v>
+        <v>102.22</v>
       </c>
       <c r="K60" t="n">
-        <v>73.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="L60" t="n">
-        <v>128.39</v>
+        <v>124.34</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-98.23</v>
+        <v>-95.31999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>99.23</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>139.63</v>
+        <v>135.49</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>162.58</v>
+        <v>157.12</v>
       </c>
       <c r="K62" t="n">
-        <v>31.46</v>
+        <v>30.4</v>
       </c>
       <c r="L62" t="n">
-        <v>165.6</v>
+        <v>160.03</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-47.04</v>
+        <v>-45.78</v>
       </c>
       <c r="K63" t="n">
-        <v>-91.61</v>
+        <v>-89.15000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>102.99</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>130.21</v>
+        <v>124.33</v>
       </c>
       <c r="K64" t="n">
-        <v>-181.41</v>
+        <v>-173.22</v>
       </c>
       <c r="L64" t="n">
-        <v>223.3</v>
+        <v>213.22</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>101.47</v>
+        <v>103.92</v>
       </c>
       <c r="K65" t="n">
-        <v>345.06</v>
+        <v>353.41</v>
       </c>
       <c r="L65" t="n">
-        <v>359.66</v>
+        <v>368.37</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-110.51</v>
+        <v>-112.47</v>
       </c>
       <c r="K66" t="n">
-        <v>-251.01</v>
+        <v>-255.45</v>
       </c>
       <c r="L66" t="n">
-        <v>274.26</v>
+        <v>279.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-170.52</v>
+        <v>-173.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-108.66</v>
+        <v>-110.34</v>
       </c>
       <c r="L67" t="n">
-        <v>202.2</v>
+        <v>205.33</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-159.64</v>
+        <v>-167.49</v>
       </c>
       <c r="K68" t="n">
-        <v>57.29</v>
+        <v>60.11</v>
       </c>
       <c r="L68" t="n">
-        <v>169.61</v>
+        <v>177.95</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>340.81</v>
+        <v>357.49</v>
       </c>
       <c r="K69" t="n">
-        <v>235.78</v>
+        <v>247.32</v>
       </c>
       <c r="L69" t="n">
-        <v>414.43</v>
+        <v>434.7</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-115.4</v>
+        <v>-118.35</v>
       </c>
       <c r="K70" t="n">
-        <v>197.73</v>
+        <v>202.79</v>
       </c>
       <c r="L70" t="n">
-        <v>228.94</v>
+        <v>234.8</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>423.54</v>
+        <v>449.31</v>
       </c>
       <c r="K71" t="n">
-        <v>77.98999999999999</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>430.66</v>
+        <v>456.86</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-134.08</v>
+        <v>-142.78</v>
       </c>
       <c r="K72" t="n">
-        <v>-257.31</v>
+        <v>-274.01</v>
       </c>
       <c r="L72" t="n">
-        <v>290.15</v>
+        <v>308.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>175.83</v>
+        <v>188.29</v>
       </c>
       <c r="K73" t="n">
-        <v>-379.05</v>
+        <v>-405.92</v>
       </c>
       <c r="L73" t="n">
-        <v>417.85</v>
+        <v>447.47</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-134.73</v>
+        <v>-127.35</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.48</v>
+        <v>-17.47</v>
       </c>
       <c r="L74" t="n">
-        <v>135.99</v>
+        <v>128.54</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-170</v>
+        <v>-166.75</v>
       </c>
       <c r="K75" t="n">
-        <v>19.06</v>
+        <v>18.7</v>
       </c>
       <c r="L75" t="n">
-        <v>171.07</v>
+        <v>167.79</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>72.25</v>
+        <v>69.38</v>
       </c>
       <c r="K76" t="n">
-        <v>-110.77</v>
+        <v>-106.36</v>
       </c>
       <c r="L76" t="n">
-        <v>132.25</v>
+        <v>126.98</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-85.23</v>
+        <v>-81.89</v>
       </c>
       <c r="K77" t="n">
-        <v>-169.65</v>
+        <v>-163</v>
       </c>
       <c r="L77" t="n">
-        <v>189.86</v>
+        <v>182.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>227.16</v>
+        <v>220.87</v>
       </c>
       <c r="K78" t="n">
-        <v>101.06</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>248.63</v>
+        <v>241.74</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>91.45</v>
+        <v>87.38</v>
       </c>
       <c r="K79" t="n">
-        <v>274.92</v>
+        <v>262.7</v>
       </c>
       <c r="L79" t="n">
-        <v>289.73</v>
+        <v>276.86</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.24</v>
+        <v>-10.15</v>
       </c>
       <c r="K80" t="n">
-        <v>345.97</v>
+        <v>343.15</v>
       </c>
       <c r="L80" t="n">
-        <v>346.12</v>
+        <v>343.3</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-277.55</v>
+        <v>-284.97</v>
       </c>
       <c r="K81" t="n">
-        <v>-83.91</v>
+        <v>-86.16</v>
       </c>
       <c r="L81" t="n">
-        <v>289.96</v>
+        <v>297.71</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-108.09</v>
+        <v>-106.98</v>
       </c>
       <c r="K82" t="n">
-        <v>-174.82</v>
+        <v>-173.02</v>
       </c>
       <c r="L82" t="n">
-        <v>205.53</v>
+        <v>203.42</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-156.98</v>
+        <v>-163.09</v>
       </c>
       <c r="K83" t="n">
-        <v>-236.91</v>
+        <v>-246.12</v>
       </c>
       <c r="L83" t="n">
-        <v>284.2</v>
+        <v>295.25</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-159.66</v>
+        <v>-169.23</v>
       </c>
       <c r="K84" t="n">
-        <v>236.78</v>
+        <v>250.98</v>
       </c>
       <c r="L84" t="n">
-        <v>285.58</v>
+        <v>302.7</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-86.48</v>
+        <v>-88.79000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>322.57</v>
+        <v>331.17</v>
       </c>
       <c r="L85" t="n">
-        <v>333.96</v>
+        <v>342.87</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>239</v>
+        <v>258.2</v>
       </c>
       <c r="K86" t="n">
-        <v>176.61</v>
+        <v>190.8</v>
       </c>
       <c r="L86" t="n">
-        <v>297.18</v>
+        <v>321.05</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-107.01</v>
+        <v>-114.69</v>
       </c>
       <c r="K87" t="n">
-        <v>158.16</v>
+        <v>169.5</v>
       </c>
       <c r="L87" t="n">
-        <v>190.96</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-129.57</v>
+        <v>-137.51</v>
       </c>
       <c r="K88" t="n">
-        <v>-131.07</v>
+        <v>-139.1</v>
       </c>
       <c r="L88" t="n">
-        <v>184.31</v>
+        <v>195.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-63.04</v>
+        <v>-28.3</v>
       </c>
       <c r="K14" t="n">
-        <v>-212</v>
+        <v>-95.16</v>
       </c>
       <c r="L14" t="n">
-        <v>221.17</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>59.26</v>
+        <v>29.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-48.08</v>
+        <v>-23.6</v>
       </c>
       <c r="L15" t="n">
-        <v>76.31</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.789999999999999</v>
+        <v>-4.59</v>
       </c>
       <c r="K16" t="n">
-        <v>-103.57</v>
+        <v>-48.59</v>
       </c>
       <c r="L16" t="n">
-        <v>104.03</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>125.43</v>
+        <v>60.03</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.72</v>
+        <v>-16.62</v>
       </c>
       <c r="L17" t="n">
-        <v>130.14</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>4.59</v>
+        <v>1.39</v>
       </c>
       <c r="K18" t="n">
-        <v>80.70999999999999</v>
+        <v>24.43</v>
       </c>
       <c r="L18" t="n">
-        <v>80.84</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-86.19</v>
+        <v>-41.48</v>
       </c>
       <c r="K19" t="n">
-        <v>-75.23999999999999</v>
+        <v>-36.21</v>
       </c>
       <c r="L19" t="n">
-        <v>114.41</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>272.85</v>
+        <v>132.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-100.89</v>
+        <v>-49</v>
       </c>
       <c r="L20" t="n">
-        <v>290.9</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-168.55</v>
+        <v>-83.81999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>104.67</v>
+        <v>52.05</v>
       </c>
       <c r="L21" t="n">
-        <v>198.4</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-31.73</v>
+        <v>-15.33</v>
       </c>
       <c r="K22" t="n">
-        <v>-243.7</v>
+        <v>-117.75</v>
       </c>
       <c r="L22" t="n">
-        <v>245.75</v>
+        <v>118.74</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>30.91</v>
+        <v>13.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-331.35</v>
+        <v>-148.81</v>
       </c>
       <c r="L23" t="n">
-        <v>332.79</v>
+        <v>149.45</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-43.34</v>
+        <v>-21.17</v>
       </c>
       <c r="K24" t="n">
-        <v>-255.57</v>
+        <v>-124.88</v>
       </c>
       <c r="L24" t="n">
-        <v>259.22</v>
+        <v>126.66</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>142.86</v>
+        <v>62.87</v>
       </c>
       <c r="K25" t="n">
-        <v>286.27</v>
+        <v>125.98</v>
       </c>
       <c r="L25" t="n">
-        <v>319.94</v>
+        <v>140.79</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-520.4400000000001</v>
+        <v>-277.46</v>
       </c>
       <c r="K26" t="n">
-        <v>115.21</v>
+        <v>61.42</v>
       </c>
       <c r="L26" t="n">
-        <v>533.04</v>
+        <v>284.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-227.51</v>
+        <v>-126.59</v>
       </c>
       <c r="K27" t="n">
-        <v>214.23</v>
+        <v>119.2</v>
       </c>
       <c r="L27" t="n">
-        <v>312.5</v>
+        <v>173.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-294.05</v>
+        <v>-158.44</v>
       </c>
       <c r="K28" t="n">
-        <v>-132.16</v>
+        <v>-71.20999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>322.39</v>
+        <v>173.71</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.48</v>
+        <v>-11.43</v>
       </c>
       <c r="K29" t="n">
-        <v>107.9</v>
+        <v>50.4</v>
       </c>
       <c r="L29" t="n">
-        <v>110.64</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>2.62</v>
+        <v>1.18</v>
       </c>
       <c r="K30" t="n">
-        <v>123.6</v>
+        <v>55.71</v>
       </c>
       <c r="L30" t="n">
-        <v>123.62</v>
+        <v>55.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>168.2</v>
+        <v>67.09</v>
       </c>
       <c r="K31" t="n">
-        <v>62.58</v>
+        <v>24.96</v>
       </c>
       <c r="L31" t="n">
-        <v>179.47</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>73.33</v>
+        <v>34.28</v>
       </c>
       <c r="K32" t="n">
-        <v>129.91</v>
+        <v>60.74</v>
       </c>
       <c r="L32" t="n">
-        <v>149.18</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>80.84999999999999</v>
+        <v>26.83</v>
       </c>
       <c r="K33" t="n">
-        <v>12.4</v>
+        <v>4.12</v>
       </c>
       <c r="L33" t="n">
-        <v>81.79000000000001</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>25.37</v>
+        <v>10.96</v>
       </c>
       <c r="K34" t="n">
-        <v>261.72</v>
+        <v>113.12</v>
       </c>
       <c r="L34" t="n">
-        <v>262.95</v>
+        <v>113.65</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-46.91</v>
+        <v>-22.66</v>
       </c>
       <c r="K35" t="n">
-        <v>-223.05</v>
+        <v>-107.73</v>
       </c>
       <c r="L35" t="n">
-        <v>227.93</v>
+        <v>110.08</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>171.9</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>127.41</v>
+        <v>60.85</v>
       </c>
       <c r="L36" t="n">
-        <v>213.97</v>
+        <v>102.19</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-172.21</v>
+        <v>-87.98</v>
       </c>
       <c r="K37" t="n">
-        <v>-29.1</v>
+        <v>-14.87</v>
       </c>
       <c r="L37" t="n">
-        <v>174.65</v>
+        <v>89.23</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-239.07</v>
+        <v>-108.57</v>
       </c>
       <c r="K38" t="n">
-        <v>-258.77</v>
+        <v>-117.51</v>
       </c>
       <c r="L38" t="n">
-        <v>352.3</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-35.73</v>
+        <v>-16.09</v>
       </c>
       <c r="K39" t="n">
-        <v>263.65</v>
+        <v>118.75</v>
       </c>
       <c r="L39" t="n">
-        <v>266.06</v>
+        <v>119.84</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>192.97</v>
+        <v>87.78</v>
       </c>
       <c r="K40" t="n">
-        <v>172.53</v>
+        <v>78.48</v>
       </c>
       <c r="L40" t="n">
-        <v>258.86</v>
+        <v>117.75</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>334.89</v>
+        <v>179.6</v>
       </c>
       <c r="K41" t="n">
-        <v>486.56</v>
+        <v>260.93</v>
       </c>
       <c r="L41" t="n">
-        <v>590.67</v>
+        <v>316.76</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-116.58</v>
+        <v>-61.73</v>
       </c>
       <c r="K42" t="n">
-        <v>-431.3</v>
+        <v>-228.37</v>
       </c>
       <c r="L42" t="n">
-        <v>446.78</v>
+        <v>236.57</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>549.4400000000001</v>
+        <v>292.23</v>
       </c>
       <c r="K43" t="n">
-        <v>-62.24</v>
+        <v>-33.1</v>
       </c>
       <c r="L43" t="n">
-        <v>552.95</v>
+        <v>294.1</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>4.79</v>
+        <v>2.07</v>
       </c>
       <c r="K44" t="n">
-        <v>130.24</v>
+        <v>56.12</v>
       </c>
       <c r="L44" t="n">
-        <v>130.33</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.79</v>
+        <v>-15.87</v>
       </c>
       <c r="K45" t="n">
-        <v>-175.65</v>
+        <v>-77.91</v>
       </c>
       <c r="L45" t="n">
-        <v>179.26</v>
+        <v>79.51000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>65.88</v>
+        <v>26.9</v>
       </c>
       <c r="K46" t="n">
-        <v>34.75</v>
+        <v>14.19</v>
       </c>
       <c r="L46" t="n">
-        <v>74.48</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>74.8</v>
+        <v>32.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.49</v>
+        <v>-20.9</v>
       </c>
       <c r="L47" t="n">
-        <v>88.59999999999999</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>118.31</v>
+        <v>50.76</v>
       </c>
       <c r="K48" t="n">
-        <v>-123.2</v>
+        <v>-52.85</v>
       </c>
       <c r="L48" t="n">
-        <v>170.81</v>
+        <v>73.28</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>169.72</v>
+        <v>75.27</v>
       </c>
       <c r="K49" t="n">
-        <v>86.98</v>
+        <v>38.57</v>
       </c>
       <c r="L49" t="n">
-        <v>190.71</v>
+        <v>84.56999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-27.68</v>
+        <v>-13.21</v>
       </c>
       <c r="K50" t="n">
-        <v>-167.15</v>
+        <v>-79.79000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>169.43</v>
+        <v>80.87</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>22.43</v>
+        <v>10.71</v>
       </c>
       <c r="K51" t="n">
-        <v>-148.81</v>
+        <v>-71.04000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>150.49</v>
+        <v>71.84</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-216.38</v>
+        <v>-103.57</v>
       </c>
       <c r="K52" t="n">
-        <v>90.72</v>
+        <v>43.42</v>
       </c>
       <c r="L52" t="n">
-        <v>234.63</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>260.3</v>
+        <v>114.12</v>
       </c>
       <c r="K53" t="n">
-        <v>43.22</v>
+        <v>18.95</v>
       </c>
       <c r="L53" t="n">
-        <v>263.87</v>
+        <v>115.68</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>283.88</v>
+        <v>134.76</v>
       </c>
       <c r="K54" t="n">
-        <v>-251.97</v>
+        <v>-119.61</v>
       </c>
       <c r="L54" t="n">
-        <v>379.57</v>
+        <v>180.19</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-81.53</v>
+        <v>-36.08</v>
       </c>
       <c r="K55" t="n">
-        <v>-284.48</v>
+        <v>-125.89</v>
       </c>
       <c r="L55" t="n">
-        <v>295.93</v>
+        <v>130.96</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-351.19</v>
+        <v>-186.79</v>
       </c>
       <c r="K56" t="n">
-        <v>-389.5</v>
+        <v>-207.17</v>
       </c>
       <c r="L56" t="n">
-        <v>524.45</v>
+        <v>278.94</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>277.57</v>
+        <v>148.05</v>
       </c>
       <c r="K57" t="n">
-        <v>-181.01</v>
+        <v>-96.55</v>
       </c>
       <c r="L57" t="n">
-        <v>331.38</v>
+        <v>176.75</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-177.75</v>
+        <v>-95.06999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>255.8</v>
+        <v>136.81</v>
       </c>
       <c r="L58" t="n">
-        <v>311.49</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>47.6</v>
+        <v>22.38</v>
       </c>
       <c r="K59" t="n">
-        <v>95.83</v>
+        <v>45.05</v>
       </c>
       <c r="L59" t="n">
-        <v>107</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>102.22</v>
+        <v>42.25</v>
       </c>
       <c r="K60" t="n">
-        <v>70.8</v>
+        <v>29.26</v>
       </c>
       <c r="L60" t="n">
-        <v>124.34</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-95.31999999999999</v>
+        <v>-38.07</v>
       </c>
       <c r="K61" t="n">
-        <v>96.29000000000001</v>
+        <v>38.45</v>
       </c>
       <c r="L61" t="n">
-        <v>135.49</v>
+        <v>54.11</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>157.12</v>
+        <v>65.37</v>
       </c>
       <c r="K62" t="n">
-        <v>30.4</v>
+        <v>12.65</v>
       </c>
       <c r="L62" t="n">
-        <v>160.03</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-45.78</v>
+        <v>-20.83</v>
       </c>
       <c r="K63" t="n">
-        <v>-89.15000000000001</v>
+        <v>-40.56</v>
       </c>
       <c r="L63" t="n">
-        <v>100.22</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>124.33</v>
+        <v>52.74</v>
       </c>
       <c r="K64" t="n">
-        <v>-173.22</v>
+        <v>-73.48</v>
       </c>
       <c r="L64" t="n">
-        <v>213.22</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>103.92</v>
+        <v>50.17</v>
       </c>
       <c r="K65" t="n">
-        <v>353.41</v>
+        <v>170.61</v>
       </c>
       <c r="L65" t="n">
-        <v>368.37</v>
+        <v>177.83</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-112.47</v>
+        <v>-53.77</v>
       </c>
       <c r="K66" t="n">
-        <v>-255.45</v>
+        <v>-122.12</v>
       </c>
       <c r="L66" t="n">
-        <v>279.11</v>
+        <v>133.44</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-173.16</v>
+        <v>-82.7</v>
       </c>
       <c r="K67" t="n">
-        <v>-110.34</v>
+        <v>-52.7</v>
       </c>
       <c r="L67" t="n">
-        <v>205.33</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-167.49</v>
+        <v>-47.59</v>
       </c>
       <c r="K68" t="n">
-        <v>60.11</v>
+        <v>17.08</v>
       </c>
       <c r="L68" t="n">
-        <v>177.95</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>357.49</v>
+        <v>171.53</v>
       </c>
       <c r="K69" t="n">
-        <v>247.32</v>
+        <v>118.67</v>
       </c>
       <c r="L69" t="n">
-        <v>434.7</v>
+        <v>208.58</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-118.35</v>
+        <v>-56.18</v>
       </c>
       <c r="K70" t="n">
-        <v>202.79</v>
+        <v>96.27</v>
       </c>
       <c r="L70" t="n">
-        <v>234.8</v>
+        <v>111.47</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>449.31</v>
+        <v>238.49</v>
       </c>
       <c r="K71" t="n">
-        <v>82.73999999999999</v>
+        <v>43.92</v>
       </c>
       <c r="L71" t="n">
-        <v>456.86</v>
+        <v>242.5</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-142.78</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-274.01</v>
+        <v>-144.88</v>
       </c>
       <c r="L72" t="n">
-        <v>308.98</v>
+        <v>163.37</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>188.29</v>
+        <v>99.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-405.92</v>
+        <v>-214.93</v>
       </c>
       <c r="L73" t="n">
-        <v>447.47</v>
+        <v>236.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-127.35</v>
+        <v>-51.21</v>
       </c>
       <c r="K74" t="n">
-        <v>-17.47</v>
+        <v>-7.02</v>
       </c>
       <c r="L74" t="n">
-        <v>128.54</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-166.75</v>
+        <v>-67.75</v>
       </c>
       <c r="K75" t="n">
-        <v>18.7</v>
+        <v>7.6</v>
       </c>
       <c r="L75" t="n">
-        <v>167.79</v>
+        <v>68.18000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>69.38</v>
+        <v>28.38</v>
       </c>
       <c r="K76" t="n">
-        <v>-106.36</v>
+        <v>-43.51</v>
       </c>
       <c r="L76" t="n">
-        <v>126.98</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-81.89</v>
+        <v>-34.02</v>
       </c>
       <c r="K77" t="n">
-        <v>-163</v>
+        <v>-67.72</v>
       </c>
       <c r="L77" t="n">
-        <v>182.41</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>220.87</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>98.26000000000001</v>
+        <v>41.91</v>
       </c>
       <c r="L78" t="n">
-        <v>241.74</v>
+        <v>103.11</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>87.38</v>
+        <v>36.61</v>
       </c>
       <c r="K79" t="n">
-        <v>262.7</v>
+        <v>110.07</v>
       </c>
       <c r="L79" t="n">
-        <v>276.86</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.15</v>
+        <v>-4.85</v>
       </c>
       <c r="K80" t="n">
-        <v>343.15</v>
+        <v>163.79</v>
       </c>
       <c r="L80" t="n">
-        <v>343.3</v>
+        <v>163.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-284.97</v>
+        <v>-140.12</v>
       </c>
       <c r="K81" t="n">
-        <v>-86.16</v>
+        <v>-42.36</v>
       </c>
       <c r="L81" t="n">
-        <v>297.71</v>
+        <v>146.38</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-106.98</v>
+        <v>-51.73</v>
       </c>
       <c r="K82" t="n">
-        <v>-173.02</v>
+        <v>-83.67</v>
       </c>
       <c r="L82" t="n">
-        <v>203.42</v>
+        <v>98.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-163.09</v>
+        <v>-71.77</v>
       </c>
       <c r="K83" t="n">
-        <v>-246.12</v>
+        <v>-108.31</v>
       </c>
       <c r="L83" t="n">
-        <v>295.25</v>
+        <v>129.93</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-169.23</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>250.98</v>
+        <v>112.5</v>
       </c>
       <c r="L84" t="n">
-        <v>302.7</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-88.79000000000001</v>
+        <v>-39.17</v>
       </c>
       <c r="K85" t="n">
-        <v>331.17</v>
+        <v>146.1</v>
       </c>
       <c r="L85" t="n">
-        <v>342.87</v>
+        <v>151.26</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>258.2</v>
+        <v>136.43</v>
       </c>
       <c r="K86" t="n">
-        <v>190.8</v>
+        <v>100.81</v>
       </c>
       <c r="L86" t="n">
-        <v>321.05</v>
+        <v>169.64</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-114.69</v>
+        <v>-53.57</v>
       </c>
       <c r="K87" t="n">
-        <v>169.5</v>
+        <v>79.17</v>
       </c>
       <c r="L87" t="n">
-        <v>204.65</v>
+        <v>95.59</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-137.51</v>
+        <v>-38.6</v>
       </c>
       <c r="K88" t="n">
-        <v>-139.1</v>
+        <v>-39.04</v>
       </c>
       <c r="L88" t="n">
-        <v>195.6</v>
+        <v>54.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-28.3</v>
+        <v>-26.08</v>
       </c>
       <c r="K14" t="n">
-        <v>-95.16</v>
+        <v>-87.70999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>99.28</v>
+        <v>91.51000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>29.09</v>
+        <v>30.08</v>
       </c>
       <c r="K15" t="n">
-        <v>-23.6</v>
+        <v>-24.4</v>
       </c>
       <c r="L15" t="n">
-        <v>37.46</v>
+        <v>38.73</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.59</v>
+        <v>-4.57</v>
       </c>
       <c r="K16" t="n">
-        <v>-48.59</v>
+        <v>-48.33</v>
       </c>
       <c r="L16" t="n">
-        <v>48.8</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>60.03</v>
+        <v>59.57</v>
       </c>
       <c r="K17" t="n">
-        <v>-16.62</v>
+        <v>-16.49</v>
       </c>
       <c r="L17" t="n">
-        <v>62.28</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="K18" t="n">
-        <v>24.43</v>
+        <v>23.27</v>
       </c>
       <c r="L18" t="n">
-        <v>24.47</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.48</v>
+        <v>-41.94</v>
       </c>
       <c r="K19" t="n">
-        <v>-36.21</v>
+        <v>-36.61</v>
       </c>
       <c r="L19" t="n">
-        <v>55.06</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>132.53</v>
+        <v>127.35</v>
       </c>
       <c r="K20" t="n">
-        <v>-49</v>
+        <v>-47.09</v>
       </c>
       <c r="L20" t="n">
-        <v>141.3</v>
+        <v>135.77</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-83.81999999999999</v>
+        <v>-82.63</v>
       </c>
       <c r="K21" t="n">
-        <v>52.05</v>
+        <v>51.31</v>
       </c>
       <c r="L21" t="n">
-        <v>98.66</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-15.33</v>
+        <v>-15.01</v>
       </c>
       <c r="K22" t="n">
-        <v>-117.75</v>
+        <v>-115.25</v>
       </c>
       <c r="L22" t="n">
-        <v>118.74</v>
+        <v>116.22</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>13.88</v>
+        <v>14.97</v>
       </c>
       <c r="K23" t="n">
-        <v>-148.81</v>
+        <v>-160.51</v>
       </c>
       <c r="L23" t="n">
-        <v>149.45</v>
+        <v>161.2</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-21.17</v>
+        <v>-21.26</v>
       </c>
       <c r="K24" t="n">
-        <v>-124.88</v>
+        <v>-125.37</v>
       </c>
       <c r="L24" t="n">
-        <v>126.66</v>
+        <v>127.16</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>62.87</v>
+        <v>66.59</v>
       </c>
       <c r="K25" t="n">
-        <v>125.98</v>
+        <v>133.44</v>
       </c>
       <c r="L25" t="n">
-        <v>140.79</v>
+        <v>149.13</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-277.46</v>
+        <v>-306.81</v>
       </c>
       <c r="K26" t="n">
-        <v>61.42</v>
+        <v>67.92</v>
       </c>
       <c r="L26" t="n">
-        <v>284.17</v>
+        <v>314.24</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-126.59</v>
+        <v>-127.71</v>
       </c>
       <c r="K27" t="n">
-        <v>119.2</v>
+        <v>120.25</v>
       </c>
       <c r="L27" t="n">
-        <v>173.88</v>
+        <v>175.41</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-158.44</v>
+        <v>-168.52</v>
       </c>
       <c r="K28" t="n">
-        <v>-71.20999999999999</v>
+        <v>-75.73999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>173.71</v>
+        <v>184.75</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.43</v>
+        <v>-11.31</v>
       </c>
       <c r="K29" t="n">
-        <v>50.4</v>
+        <v>49.85</v>
       </c>
       <c r="L29" t="n">
-        <v>51.68</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="K30" t="n">
-        <v>55.71</v>
+        <v>54.21</v>
       </c>
       <c r="L30" t="n">
-        <v>55.72</v>
+        <v>54.23</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>67.09</v>
+        <v>60.87</v>
       </c>
       <c r="K31" t="n">
-        <v>24.96</v>
+        <v>22.65</v>
       </c>
       <c r="L31" t="n">
-        <v>71.58</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>34.28</v>
+        <v>33.11</v>
       </c>
       <c r="K32" t="n">
-        <v>60.74</v>
+        <v>58.66</v>
       </c>
       <c r="L32" t="n">
-        <v>69.73999999999999</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>26.83</v>
+        <v>25.34</v>
       </c>
       <c r="K33" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="L33" t="n">
-        <v>27.14</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>10.96</v>
+        <v>10.02</v>
       </c>
       <c r="K34" t="n">
-        <v>113.12</v>
+        <v>103.37</v>
       </c>
       <c r="L34" t="n">
-        <v>113.65</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-22.66</v>
+        <v>-22.18</v>
       </c>
       <c r="K35" t="n">
-        <v>-107.73</v>
+        <v>-105.48</v>
       </c>
       <c r="L35" t="n">
-        <v>110.08</v>
+        <v>107.79</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>82.09999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="K36" t="n">
-        <v>60.85</v>
+        <v>60.76</v>
       </c>
       <c r="L36" t="n">
-        <v>102.19</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-87.98</v>
+        <v>-86.91</v>
       </c>
       <c r="K37" t="n">
-        <v>-14.87</v>
+        <v>-14.69</v>
       </c>
       <c r="L37" t="n">
-        <v>89.23</v>
+        <v>88.15000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-108.57</v>
+        <v>-106.87</v>
       </c>
       <c r="K38" t="n">
-        <v>-117.51</v>
+        <v>-115.68</v>
       </c>
       <c r="L38" t="n">
-        <v>159.99</v>
+        <v>157.49</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.09</v>
+        <v>-16.44</v>
       </c>
       <c r="K39" t="n">
-        <v>118.75</v>
+        <v>121.29</v>
       </c>
       <c r="L39" t="n">
-        <v>119.84</v>
+        <v>122.39</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>87.78</v>
+        <v>90.09</v>
       </c>
       <c r="K40" t="n">
-        <v>78.48</v>
+        <v>80.55</v>
       </c>
       <c r="L40" t="n">
-        <v>117.75</v>
+        <v>120.85</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>179.6</v>
+        <v>181.69</v>
       </c>
       <c r="K41" t="n">
-        <v>260.93</v>
+        <v>263.97</v>
       </c>
       <c r="L41" t="n">
-        <v>316.76</v>
+        <v>320.46</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-61.73</v>
+        <v>-68.73</v>
       </c>
       <c r="K42" t="n">
-        <v>-228.37</v>
+        <v>-254.26</v>
       </c>
       <c r="L42" t="n">
-        <v>236.57</v>
+        <v>263.38</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>292.23</v>
+        <v>323.69</v>
       </c>
       <c r="K43" t="n">
-        <v>-33.1</v>
+        <v>-36.67</v>
       </c>
       <c r="L43" t="n">
-        <v>294.1</v>
+        <v>325.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="K44" t="n">
-        <v>56.12</v>
+        <v>54.78</v>
       </c>
       <c r="L44" t="n">
-        <v>56.16</v>
+        <v>54.82</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-15.87</v>
+        <v>-15.05</v>
       </c>
       <c r="K45" t="n">
-        <v>-77.91</v>
+        <v>-73.89</v>
       </c>
       <c r="L45" t="n">
-        <v>79.51000000000001</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>26.9</v>
+        <v>25.33</v>
       </c>
       <c r="K46" t="n">
-        <v>14.19</v>
+        <v>13.37</v>
       </c>
       <c r="L46" t="n">
-        <v>30.42</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>32.92</v>
+        <v>31.96</v>
       </c>
       <c r="K47" t="n">
-        <v>-20.9</v>
+        <v>-20.29</v>
       </c>
       <c r="L47" t="n">
-        <v>38.99</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>50.76</v>
+        <v>43.93</v>
       </c>
       <c r="K48" t="n">
-        <v>-52.85</v>
+        <v>-45.75</v>
       </c>
       <c r="L48" t="n">
-        <v>73.28</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>75.27</v>
+        <v>71.39</v>
       </c>
       <c r="K49" t="n">
-        <v>38.57</v>
+        <v>36.58</v>
       </c>
       <c r="L49" t="n">
-        <v>84.56999999999999</v>
+        <v>80.20999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.21</v>
+        <v>-13.67</v>
       </c>
       <c r="K50" t="n">
-        <v>-79.79000000000001</v>
+        <v>-82.55</v>
       </c>
       <c r="L50" t="n">
-        <v>80.87</v>
+        <v>83.68000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>10.71</v>
+        <v>11.31</v>
       </c>
       <c r="K51" t="n">
-        <v>-71.04000000000001</v>
+        <v>-75.03</v>
       </c>
       <c r="L51" t="n">
-        <v>71.84</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-103.57</v>
+        <v>-102.19</v>
       </c>
       <c r="K52" t="n">
-        <v>43.42</v>
+        <v>42.85</v>
       </c>
       <c r="L52" t="n">
-        <v>112.3</v>
+        <v>110.81</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>114.12</v>
+        <v>123.47</v>
       </c>
       <c r="K53" t="n">
-        <v>18.95</v>
+        <v>20.5</v>
       </c>
       <c r="L53" t="n">
-        <v>115.68</v>
+        <v>125.16</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>134.76</v>
+        <v>132.29</v>
       </c>
       <c r="K54" t="n">
-        <v>-119.61</v>
+        <v>-117.42</v>
       </c>
       <c r="L54" t="n">
-        <v>180.19</v>
+        <v>176.89</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-36.08</v>
+        <v>-37.62</v>
       </c>
       <c r="K55" t="n">
-        <v>-125.89</v>
+        <v>-131.27</v>
       </c>
       <c r="L55" t="n">
-        <v>130.96</v>
+        <v>136.56</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-186.79</v>
+        <v>-208.57</v>
       </c>
       <c r="K56" t="n">
-        <v>-207.17</v>
+        <v>-231.32</v>
       </c>
       <c r="L56" t="n">
-        <v>278.94</v>
+        <v>311.46</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>148.05</v>
+        <v>163.73</v>
       </c>
       <c r="K57" t="n">
-        <v>-96.55</v>
+        <v>-106.77</v>
       </c>
       <c r="L57" t="n">
-        <v>176.75</v>
+        <v>195.47</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-95.06999999999999</v>
+        <v>-114.89</v>
       </c>
       <c r="K58" t="n">
-        <v>136.81</v>
+        <v>165.35</v>
       </c>
       <c r="L58" t="n">
-        <v>166.6</v>
+        <v>201.35</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>22.38</v>
+        <v>22.34</v>
       </c>
       <c r="K59" t="n">
-        <v>45.05</v>
+        <v>44.98</v>
       </c>
       <c r="L59" t="n">
-        <v>50.31</v>
+        <v>50.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>42.25</v>
+        <v>41.67</v>
       </c>
       <c r="K60" t="n">
-        <v>29.26</v>
+        <v>28.86</v>
       </c>
       <c r="L60" t="n">
-        <v>51.4</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-38.07</v>
+        <v>-35.64</v>
       </c>
       <c r="K61" t="n">
-        <v>38.45</v>
+        <v>36</v>
       </c>
       <c r="L61" t="n">
-        <v>54.11</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>65.37</v>
+        <v>62.75</v>
       </c>
       <c r="K62" t="n">
-        <v>12.65</v>
+        <v>12.14</v>
       </c>
       <c r="L62" t="n">
-        <v>66.58</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-20.83</v>
+        <v>-21.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-40.56</v>
+        <v>-41.95</v>
       </c>
       <c r="L63" t="n">
-        <v>45.6</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>52.74</v>
+        <v>49.33</v>
       </c>
       <c r="K64" t="n">
-        <v>-73.48</v>
+        <v>-68.72</v>
       </c>
       <c r="L64" t="n">
-        <v>90.45</v>
+        <v>84.59</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>50.17</v>
+        <v>47.44</v>
       </c>
       <c r="K65" t="n">
-        <v>170.61</v>
+        <v>161.32</v>
       </c>
       <c r="L65" t="n">
-        <v>177.83</v>
+        <v>168.15</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-53.77</v>
+        <v>-52.39</v>
       </c>
       <c r="K66" t="n">
-        <v>-122.12</v>
+        <v>-118.99</v>
       </c>
       <c r="L66" t="n">
-        <v>133.44</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-82.7</v>
+        <v>-83.51000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-52.7</v>
+        <v>-53.21</v>
       </c>
       <c r="L67" t="n">
-        <v>98.06999999999999</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-47.59</v>
+        <v>-49.46</v>
       </c>
       <c r="K68" t="n">
-        <v>17.08</v>
+        <v>17.75</v>
       </c>
       <c r="L68" t="n">
-        <v>50.56</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>171.53</v>
+        <v>165.67</v>
       </c>
       <c r="K69" t="n">
-        <v>118.67</v>
+        <v>114.61</v>
       </c>
       <c r="L69" t="n">
-        <v>208.58</v>
+        <v>201.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-56.18</v>
+        <v>-57.77</v>
       </c>
       <c r="K70" t="n">
-        <v>96.27</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>111.47</v>
+        <v>114.61</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>238.49</v>
+        <v>266.87</v>
       </c>
       <c r="K71" t="n">
-        <v>43.92</v>
+        <v>49.14</v>
       </c>
       <c r="L71" t="n">
-        <v>242.5</v>
+        <v>271.35</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-75.48999999999999</v>
+        <v>-88.36</v>
       </c>
       <c r="K72" t="n">
-        <v>-144.88</v>
+        <v>-169.57</v>
       </c>
       <c r="L72" t="n">
-        <v>163.37</v>
+        <v>191.21</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>99.7</v>
+        <v>112.17</v>
       </c>
       <c r="K73" t="n">
-        <v>-214.93</v>
+        <v>-241.82</v>
       </c>
       <c r="L73" t="n">
-        <v>236.93</v>
+        <v>266.57</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-51.21</v>
+        <v>-45.38</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.02</v>
+        <v>-6.22</v>
       </c>
       <c r="L74" t="n">
-        <v>51.68</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-67.75</v>
+        <v>-64.7</v>
       </c>
       <c r="K75" t="n">
-        <v>7.6</v>
+        <v>7.25</v>
       </c>
       <c r="L75" t="n">
-        <v>68.18000000000001</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>28.38</v>
+        <v>27.86</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.51</v>
+        <v>-42.7</v>
       </c>
       <c r="L76" t="n">
-        <v>51.95</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-34.02</v>
+        <v>-32.09</v>
       </c>
       <c r="K77" t="n">
-        <v>-67.72</v>
+        <v>-63.87</v>
       </c>
       <c r="L77" t="n">
-        <v>75.78</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>94.20999999999999</v>
+        <v>78.97</v>
       </c>
       <c r="K78" t="n">
-        <v>41.91</v>
+        <v>35.13</v>
       </c>
       <c r="L78" t="n">
-        <v>103.11</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>36.61</v>
+        <v>32.08</v>
       </c>
       <c r="K79" t="n">
-        <v>110.07</v>
+        <v>96.45</v>
       </c>
       <c r="L79" t="n">
-        <v>116</v>
+        <v>101.65</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.85</v>
+        <v>-4.33</v>
       </c>
       <c r="K80" t="n">
-        <v>163.79</v>
+        <v>146.39</v>
       </c>
       <c r="L80" t="n">
-        <v>163.86</v>
+        <v>146.45</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-140.12</v>
+        <v>-134.52</v>
       </c>
       <c r="K81" t="n">
-        <v>-42.36</v>
+        <v>-40.67</v>
       </c>
       <c r="L81" t="n">
-        <v>146.38</v>
+        <v>140.54</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-51.73</v>
+        <v>-51.28</v>
       </c>
       <c r="K82" t="n">
-        <v>-83.67</v>
+        <v>-82.94</v>
       </c>
       <c r="L82" t="n">
-        <v>98.37</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-71.77</v>
+        <v>-77.48</v>
       </c>
       <c r="K83" t="n">
-        <v>-108.31</v>
+        <v>-116.94</v>
       </c>
       <c r="L83" t="n">
-        <v>129.93</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-75.84999999999999</v>
+        <v>-77.66</v>
       </c>
       <c r="K84" t="n">
-        <v>112.5</v>
+        <v>115.17</v>
       </c>
       <c r="L84" t="n">
-        <v>135.68</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-39.17</v>
+        <v>-41.35</v>
       </c>
       <c r="K85" t="n">
-        <v>146.1</v>
+        <v>154.23</v>
       </c>
       <c r="L85" t="n">
-        <v>151.26</v>
+        <v>159.67</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>136.43</v>
+        <v>158.61</v>
       </c>
       <c r="K86" t="n">
-        <v>100.81</v>
+        <v>117.21</v>
       </c>
       <c r="L86" t="n">
-        <v>169.64</v>
+        <v>197.22</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-53.57</v>
+        <v>-56.99</v>
       </c>
       <c r="K87" t="n">
-        <v>79.17</v>
+        <v>84.23</v>
       </c>
       <c r="L87" t="n">
-        <v>95.59</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-38.6</v>
+        <v>-42.83</v>
       </c>
       <c r="K88" t="n">
-        <v>-39.04</v>
+        <v>-43.33</v>
       </c>
       <c r="L88" t="n">
-        <v>54.9</v>
+        <v>60.93</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-26.08</v>
+        <v>-24.31</v>
       </c>
       <c r="K14" t="n">
-        <v>-87.70999999999999</v>
+        <v>-81.77</v>
       </c>
       <c r="L14" t="n">
-        <v>91.51000000000001</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>30.08</v>
+        <v>31.6</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.4</v>
+        <v>-25.64</v>
       </c>
       <c r="L15" t="n">
-        <v>38.73</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.57</v>
+        <v>-4.64</v>
       </c>
       <c r="K16" t="n">
-        <v>-48.33</v>
+        <v>-49.02</v>
       </c>
       <c r="L16" t="n">
-        <v>48.55</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>59.57</v>
+        <v>60.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-16.49</v>
+        <v>-16.66</v>
       </c>
       <c r="L17" t="n">
-        <v>61.81</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="K18" t="n">
-        <v>23.27</v>
+        <v>25.3</v>
       </c>
       <c r="L18" t="n">
-        <v>23.31</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.94</v>
+        <v>-43.23</v>
       </c>
       <c r="K19" t="n">
-        <v>-36.61</v>
+        <v>-37.74</v>
       </c>
       <c r="L19" t="n">
-        <v>55.67</v>
+        <v>57.38</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>127.35</v>
+        <v>123.04</v>
       </c>
       <c r="K20" t="n">
-        <v>-47.09</v>
+        <v>-45.49</v>
       </c>
       <c r="L20" t="n">
-        <v>135.77</v>
+        <v>131.18</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-82.63</v>
+        <v>-81.89</v>
       </c>
       <c r="K21" t="n">
-        <v>51.31</v>
+        <v>50.85</v>
       </c>
       <c r="L21" t="n">
-        <v>97.27</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-15.01</v>
+        <v>-14.84</v>
       </c>
       <c r="K22" t="n">
-        <v>-115.25</v>
+        <v>-113.96</v>
       </c>
       <c r="L22" t="n">
-        <v>116.22</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>14.97</v>
+        <v>15.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-160.51</v>
+        <v>-162.92</v>
       </c>
       <c r="L23" t="n">
-        <v>161.2</v>
+        <v>163.63</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-21.26</v>
+        <v>-21.21</v>
       </c>
       <c r="K24" t="n">
-        <v>-125.37</v>
+        <v>-125.1</v>
       </c>
       <c r="L24" t="n">
-        <v>127.16</v>
+        <v>126.89</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>66.59</v>
+        <v>66.7</v>
       </c>
       <c r="K25" t="n">
-        <v>133.44</v>
+        <v>133.66</v>
       </c>
       <c r="L25" t="n">
-        <v>149.13</v>
+        <v>149.38</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-306.81</v>
+        <v>-298.51</v>
       </c>
       <c r="K26" t="n">
-        <v>67.92</v>
+        <v>66.08</v>
       </c>
       <c r="L26" t="n">
-        <v>314.24</v>
+        <v>305.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-127.71</v>
+        <v>-126.47</v>
       </c>
       <c r="K27" t="n">
-        <v>120.25</v>
+        <v>119.09</v>
       </c>
       <c r="L27" t="n">
-        <v>175.41</v>
+        <v>173.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-168.52</v>
+        <v>-171.47</v>
       </c>
       <c r="K28" t="n">
-        <v>-75.73999999999999</v>
+        <v>-77.06</v>
       </c>
       <c r="L28" t="n">
-        <v>184.75</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.31</v>
+        <v>-11.4</v>
       </c>
       <c r="K29" t="n">
-        <v>49.85</v>
+        <v>50.27</v>
       </c>
       <c r="L29" t="n">
-        <v>51.11</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="K30" t="n">
-        <v>54.21</v>
+        <v>53.96</v>
       </c>
       <c r="L30" t="n">
-        <v>54.23</v>
+        <v>53.97</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>60.87</v>
+        <v>59.6</v>
       </c>
       <c r="K31" t="n">
-        <v>22.65</v>
+        <v>22.18</v>
       </c>
       <c r="L31" t="n">
-        <v>64.95</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>33.11</v>
+        <v>32.57</v>
       </c>
       <c r="K32" t="n">
-        <v>58.66</v>
+        <v>57.7</v>
       </c>
       <c r="L32" t="n">
-        <v>67.36</v>
+        <v>66.26000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>25.34</v>
+        <v>27.61</v>
       </c>
       <c r="K33" t="n">
-        <v>3.89</v>
+        <v>4.23</v>
       </c>
       <c r="L33" t="n">
-        <v>25.64</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>10.02</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>103.37</v>
+        <v>96.52</v>
       </c>
       <c r="L34" t="n">
-        <v>103.85</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-22.18</v>
+        <v>-21.95</v>
       </c>
       <c r="K35" t="n">
-        <v>-105.48</v>
+        <v>-104.34</v>
       </c>
       <c r="L35" t="n">
-        <v>107.79</v>
+        <v>106.62</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>81.98</v>
+        <v>83.7</v>
       </c>
       <c r="K36" t="n">
-        <v>60.76</v>
+        <v>62.04</v>
       </c>
       <c r="L36" t="n">
-        <v>102.04</v>
+        <v>104.19</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-86.91</v>
+        <v>-85.86</v>
       </c>
       <c r="K37" t="n">
-        <v>-14.69</v>
+        <v>-14.51</v>
       </c>
       <c r="L37" t="n">
-        <v>88.15000000000001</v>
+        <v>87.06999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-106.87</v>
+        <v>-103.86</v>
       </c>
       <c r="K38" t="n">
-        <v>-115.68</v>
+        <v>-112.42</v>
       </c>
       <c r="L38" t="n">
-        <v>157.49</v>
+        <v>153.05</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.44</v>
+        <v>-16.7</v>
       </c>
       <c r="K39" t="n">
-        <v>121.29</v>
+        <v>123.25</v>
       </c>
       <c r="L39" t="n">
-        <v>122.39</v>
+        <v>124.38</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>90.09</v>
+        <v>91.89</v>
       </c>
       <c r="K40" t="n">
-        <v>80.55</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>120.85</v>
+        <v>123.26</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>181.69</v>
+        <v>173.24</v>
       </c>
       <c r="K41" t="n">
-        <v>263.97</v>
+        <v>251.69</v>
       </c>
       <c r="L41" t="n">
-        <v>320.46</v>
+        <v>305.55</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-68.73</v>
+        <v>-68.13</v>
       </c>
       <c r="K42" t="n">
-        <v>-254.26</v>
+        <v>-252.06</v>
       </c>
       <c r="L42" t="n">
-        <v>263.38</v>
+        <v>261.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>323.69</v>
+        <v>316.72</v>
       </c>
       <c r="K43" t="n">
-        <v>-36.67</v>
+        <v>-35.88</v>
       </c>
       <c r="L43" t="n">
-        <v>325.76</v>
+        <v>318.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="K44" t="n">
-        <v>54.78</v>
+        <v>55.1</v>
       </c>
       <c r="L44" t="n">
-        <v>54.82</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-15.05</v>
+        <v>-14.57</v>
       </c>
       <c r="K45" t="n">
-        <v>-73.89</v>
+        <v>-71.52</v>
       </c>
       <c r="L45" t="n">
-        <v>75.40000000000001</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>25.33</v>
+        <v>27.74</v>
       </c>
       <c r="K46" t="n">
-        <v>13.37</v>
+        <v>14.64</v>
       </c>
       <c r="L46" t="n">
-        <v>28.64</v>
+        <v>31.37</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>31.96</v>
+        <v>35.05</v>
       </c>
       <c r="K47" t="n">
-        <v>-20.29</v>
+        <v>-22.26</v>
       </c>
       <c r="L47" t="n">
-        <v>37.86</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>43.93</v>
+        <v>44.25</v>
       </c>
       <c r="K48" t="n">
-        <v>-45.75</v>
+        <v>-46.08</v>
       </c>
       <c r="L48" t="n">
-        <v>63.42</v>
+        <v>63.88</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>71.39</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>36.58</v>
+        <v>35.58</v>
       </c>
       <c r="L49" t="n">
-        <v>80.20999999999999</v>
+        <v>78.01000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.67</v>
+        <v>-14.43</v>
       </c>
       <c r="K50" t="n">
-        <v>-82.55</v>
+        <v>-87.14</v>
       </c>
       <c r="L50" t="n">
-        <v>83.68000000000001</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>11.31</v>
+        <v>12.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-75.03</v>
+        <v>-81.03</v>
       </c>
       <c r="L51" t="n">
-        <v>75.88</v>
+        <v>81.94</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-102.19</v>
+        <v>-103.69</v>
       </c>
       <c r="K52" t="n">
-        <v>42.85</v>
+        <v>43.48</v>
       </c>
       <c r="L52" t="n">
-        <v>110.81</v>
+        <v>112.44</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>123.47</v>
+        <v>126.84</v>
       </c>
       <c r="K53" t="n">
-        <v>20.5</v>
+        <v>21.06</v>
       </c>
       <c r="L53" t="n">
-        <v>125.16</v>
+        <v>128.58</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>132.29</v>
+        <v>128.41</v>
       </c>
       <c r="K54" t="n">
-        <v>-117.42</v>
+        <v>-113.97</v>
       </c>
       <c r="L54" t="n">
-        <v>176.89</v>
+        <v>171.69</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-37.62</v>
+        <v>-38.2</v>
       </c>
       <c r="K55" t="n">
-        <v>-131.27</v>
+        <v>-133.3</v>
       </c>
       <c r="L55" t="n">
-        <v>136.56</v>
+        <v>138.66</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-208.57</v>
+        <v>-206.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-231.32</v>
+        <v>-228.54</v>
       </c>
       <c r="L56" t="n">
-        <v>311.46</v>
+        <v>307.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>163.73</v>
+        <v>169.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-106.77</v>
+        <v>-110.37</v>
       </c>
       <c r="L57" t="n">
-        <v>195.47</v>
+        <v>202.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-114.89</v>
+        <v>-122.97</v>
       </c>
       <c r="K58" t="n">
-        <v>165.35</v>
+        <v>176.97</v>
       </c>
       <c r="L58" t="n">
-        <v>201.35</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>22.34</v>
+        <v>22.74</v>
       </c>
       <c r="K59" t="n">
-        <v>44.98</v>
+        <v>45.78</v>
       </c>
       <c r="L59" t="n">
-        <v>50.22</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>41.67</v>
+        <v>42.68</v>
       </c>
       <c r="K60" t="n">
-        <v>28.86</v>
+        <v>29.56</v>
       </c>
       <c r="L60" t="n">
-        <v>50.69</v>
+        <v>51.91</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-35.64</v>
+        <v>-36.57</v>
       </c>
       <c r="K61" t="n">
-        <v>36</v>
+        <v>36.94</v>
       </c>
       <c r="L61" t="n">
-        <v>50.66</v>
+        <v>51.98</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>62.75</v>
+        <v>63.8</v>
       </c>
       <c r="K62" t="n">
-        <v>12.14</v>
+        <v>12.34</v>
       </c>
       <c r="L62" t="n">
-        <v>63.92</v>
+        <v>64.98</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-21.54</v>
+        <v>-22.93</v>
       </c>
       <c r="K63" t="n">
-        <v>-41.95</v>
+        <v>-44.66</v>
       </c>
       <c r="L63" t="n">
-        <v>47.16</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>49.33</v>
+        <v>47.6</v>
       </c>
       <c r="K64" t="n">
-        <v>-68.72</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>84.59</v>
+        <v>81.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>47.44</v>
+        <v>44.99</v>
       </c>
       <c r="K65" t="n">
-        <v>161.32</v>
+        <v>153.01</v>
       </c>
       <c r="L65" t="n">
-        <v>168.15</v>
+        <v>159.49</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-52.39</v>
+        <v>-52.21</v>
       </c>
       <c r="K66" t="n">
-        <v>-118.99</v>
+        <v>-118.58</v>
       </c>
       <c r="L66" t="n">
-        <v>130.01</v>
+        <v>129.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-83.51000000000001</v>
+        <v>-86.31</v>
       </c>
       <c r="K67" t="n">
-        <v>-53.21</v>
+        <v>-55</v>
       </c>
       <c r="L67" t="n">
-        <v>99.02</v>
+        <v>102.35</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-49.46</v>
+        <v>-54.2</v>
       </c>
       <c r="K68" t="n">
-        <v>17.75</v>
+        <v>19.45</v>
       </c>
       <c r="L68" t="n">
-        <v>52.55</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>165.67</v>
+        <v>157.69</v>
       </c>
       <c r="K69" t="n">
-        <v>114.61</v>
+        <v>109.1</v>
       </c>
       <c r="L69" t="n">
-        <v>201.45</v>
+        <v>191.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-57.77</v>
+        <v>-59.14</v>
       </c>
       <c r="K70" t="n">
-        <v>98.98999999999999</v>
+        <v>101.33</v>
       </c>
       <c r="L70" t="n">
-        <v>114.61</v>
+        <v>117.33</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>266.87</v>
+        <v>265.17</v>
       </c>
       <c r="K71" t="n">
-        <v>49.14</v>
+        <v>48.83</v>
       </c>
       <c r="L71" t="n">
-        <v>271.35</v>
+        <v>269.63</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-88.36</v>
+        <v>-92.84999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-169.57</v>
+        <v>-178.19</v>
       </c>
       <c r="L72" t="n">
-        <v>191.21</v>
+        <v>200.93</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>112.17</v>
+        <v>112.59</v>
       </c>
       <c r="K73" t="n">
-        <v>-241.82</v>
+        <v>-242.72</v>
       </c>
       <c r="L73" t="n">
-        <v>266.57</v>
+        <v>267.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-45.38</v>
+        <v>-46.79</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.22</v>
+        <v>-6.42</v>
       </c>
       <c r="L74" t="n">
-        <v>45.8</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.7</v>
+        <v>-64.09</v>
       </c>
       <c r="K75" t="n">
-        <v>7.25</v>
+        <v>7.19</v>
       </c>
       <c r="L75" t="n">
-        <v>65.11</v>
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>27.86</v>
+        <v>28.42</v>
       </c>
       <c r="K76" t="n">
-        <v>-42.7</v>
+        <v>-43.57</v>
       </c>
       <c r="L76" t="n">
-        <v>50.98</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-32.09</v>
+        <v>-31.78</v>
       </c>
       <c r="K77" t="n">
-        <v>-63.87</v>
+        <v>-63.25</v>
       </c>
       <c r="L77" t="n">
-        <v>71.47</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>78.97</v>
+        <v>76.7</v>
       </c>
       <c r="K78" t="n">
-        <v>35.13</v>
+        <v>34.13</v>
       </c>
       <c r="L78" t="n">
-        <v>86.44</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>32.08</v>
+        <v>30.31</v>
       </c>
       <c r="K79" t="n">
-        <v>96.45</v>
+        <v>91.11</v>
       </c>
       <c r="L79" t="n">
-        <v>101.65</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.33</v>
+        <v>-4.19</v>
       </c>
       <c r="K80" t="n">
-        <v>146.39</v>
+        <v>141.58</v>
       </c>
       <c r="L80" t="n">
-        <v>146.45</v>
+        <v>141.64</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-134.52</v>
+        <v>-129.48</v>
       </c>
       <c r="K81" t="n">
-        <v>-40.67</v>
+        <v>-39.15</v>
       </c>
       <c r="L81" t="n">
-        <v>140.54</v>
+        <v>135.27</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-51.28</v>
+        <v>-51.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-82.94</v>
+        <v>-83.19</v>
       </c>
       <c r="L82" t="n">
-        <v>97.51000000000001</v>
+        <v>97.81</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-77.48</v>
+        <v>-79.3</v>
       </c>
       <c r="K83" t="n">
-        <v>-116.94</v>
+        <v>-119.68</v>
       </c>
       <c r="L83" t="n">
-        <v>140.28</v>
+        <v>143.57</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-77.66</v>
+        <v>-78.81</v>
       </c>
       <c r="K84" t="n">
-        <v>115.17</v>
+        <v>116.89</v>
       </c>
       <c r="L84" t="n">
-        <v>138.9</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.35</v>
+        <v>-41.22</v>
       </c>
       <c r="K85" t="n">
-        <v>154.23</v>
+        <v>153.74</v>
       </c>
       <c r="L85" t="n">
-        <v>159.67</v>
+        <v>159.17</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>158.61</v>
+        <v>166.62</v>
       </c>
       <c r="K86" t="n">
-        <v>117.21</v>
+        <v>123.13</v>
       </c>
       <c r="L86" t="n">
-        <v>197.22</v>
+        <v>207.18</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-56.99</v>
+        <v>-63.14</v>
       </c>
       <c r="K87" t="n">
-        <v>84.23</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>101.7</v>
+        <v>112.68</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-42.83</v>
+        <v>-46.99</v>
       </c>
       <c r="K88" t="n">
-        <v>-43.33</v>
+        <v>-47.53</v>
       </c>
       <c r="L88" t="n">
-        <v>60.93</v>
+        <v>66.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.07</v>
+        <v>4.25</v>
       </c>
       <c r="F14" t="n">
-        <v>14.27</v>
+        <v>12.25</v>
       </c>
       <c r="G14" t="n">
-        <v>303.3</v>
+        <v>301.5</v>
       </c>
       <c r="H14" t="n">
-        <v>31</v>
+        <v>28.8</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.31</v>
+        <v>-61.07</v>
       </c>
       <c r="K14" t="n">
-        <v>-81.77</v>
+        <v>-45.16</v>
       </c>
       <c r="L14" t="n">
-        <v>85.31</v>
+        <v>75.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:30:06</t>
+          <t>04:28:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="F15" t="n">
-        <v>13.96</v>
+        <v>14.38</v>
       </c>
       <c r="G15" t="n">
-        <v>290.7</v>
+        <v>302.9</v>
       </c>
       <c r="H15" t="n">
-        <v>23.2</v>
+        <v>26.4</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>31.6</v>
+        <v>64.72</v>
       </c>
       <c r="K15" t="n">
-        <v>-25.64</v>
+        <v>-17.67</v>
       </c>
       <c r="L15" t="n">
-        <v>40.69</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:31:19</t>
+          <t>04:30:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.86</v>
+        <v>4.03</v>
       </c>
       <c r="F16" t="n">
-        <v>14.18</v>
+        <v>14.57</v>
       </c>
       <c r="G16" t="n">
-        <v>302.4</v>
+        <v>301</v>
       </c>
       <c r="H16" t="n">
-        <v>29.2</v>
+        <v>33.7</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.64</v>
+        <v>0.34</v>
       </c>
       <c r="K16" t="n">
-        <v>-49.02</v>
+        <v>25.8</v>
       </c>
       <c r="L16" t="n">
-        <v>49.24</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:36:20</t>
+          <t>04:35:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="F17" t="n">
-        <v>14.14</v>
+        <v>10.96</v>
       </c>
       <c r="G17" t="n">
-        <v>298.7</v>
+        <v>302.6</v>
       </c>
       <c r="H17" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>60.2</v>
+        <v>-55.67</v>
       </c>
       <c r="K17" t="n">
-        <v>-16.66</v>
+        <v>-43.15</v>
       </c>
       <c r="L17" t="n">
-        <v>62.46</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:38:58</t>
+          <t>04:36:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.07</v>
+        <v>4.29</v>
       </c>
       <c r="F18" t="n">
-        <v>14.05</v>
+        <v>13.1</v>
       </c>
       <c r="G18" t="n">
-        <v>313.4</v>
+        <v>307.3</v>
       </c>
       <c r="H18" t="n">
-        <v>35.3</v>
+        <v>33.9</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>1.44</v>
+        <v>86</v>
       </c>
       <c r="K18" t="n">
-        <v>25.3</v>
+        <v>-32.37</v>
       </c>
       <c r="L18" t="n">
-        <v>25.34</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:41:07</t>
+          <t>04:38:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="F19" t="n">
-        <v>14.12</v>
+        <v>10.72</v>
       </c>
       <c r="G19" t="n">
-        <v>291.9</v>
+        <v>297.3</v>
       </c>
       <c r="H19" t="n">
-        <v>27.9</v>
+        <v>27.1</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.23</v>
+        <v>-65.62</v>
       </c>
       <c r="K19" t="n">
-        <v>-37.74</v>
+        <v>40.44</v>
       </c>
       <c r="L19" t="n">
-        <v>57.38</v>
+        <v>77.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:45:52</t>
+          <t>04:42:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="F20" t="n">
-        <v>14.36</v>
+        <v>10.96</v>
       </c>
       <c r="G20" t="n">
-        <v>313.7</v>
+        <v>306.6</v>
       </c>
       <c r="H20" t="n">
-        <v>30.4</v>
+        <v>25.4</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>123.04</v>
+        <v>-25.56</v>
       </c>
       <c r="K20" t="n">
-        <v>-45.49</v>
+        <v>-108.92</v>
       </c>
       <c r="L20" t="n">
-        <v>131.18</v>
+        <v>111.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:47:37</t>
+          <t>04:44:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.85</v>
+        <v>5.24</v>
       </c>
       <c r="F21" t="n">
-        <v>13.86</v>
+        <v>15.7</v>
       </c>
       <c r="G21" t="n">
-        <v>300.1</v>
+        <v>317.4</v>
       </c>
       <c r="H21" t="n">
-        <v>29</v>
+        <v>25.5</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-81.89</v>
+        <v>7.85</v>
       </c>
       <c r="K21" t="n">
-        <v>50.85</v>
+        <v>-126.61</v>
       </c>
       <c r="L21" t="n">
-        <v>96.39</v>
+        <v>126.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:48:38</t>
+          <t>04:45:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.45</v>
+        <v>4.01</v>
       </c>
       <c r="F22" t="n">
-        <v>14.33</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>296.8</v>
+        <v>281.6</v>
       </c>
       <c r="H22" t="n">
-        <v>24.8</v>
+        <v>28.2</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-14.84</v>
+        <v>-29.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-113.96</v>
+        <v>-115.93</v>
       </c>
       <c r="L22" t="n">
-        <v>114.92</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:53:25</t>
+          <t>04:49:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.28</v>
+        <v>4.9</v>
       </c>
       <c r="F23" t="n">
-        <v>14.87</v>
+        <v>13.45</v>
       </c>
       <c r="G23" t="n">
-        <v>296.9</v>
+        <v>312.6</v>
       </c>
       <c r="H23" t="n">
-        <v>25.9</v>
+        <v>27.8</v>
       </c>
       <c r="I23" t="n">
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>15.2</v>
+        <v>57.81</v>
       </c>
       <c r="K23" t="n">
-        <v>-162.92</v>
+        <v>174.08</v>
       </c>
       <c r="L23" t="n">
-        <v>163.63</v>
+        <v>183.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:55:05</t>
+          <t>04:51:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.06</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>13.07</v>
+        <v>16.21</v>
       </c>
       <c r="G24" t="n">
-        <v>302.4</v>
+        <v>303.3</v>
       </c>
       <c r="H24" t="n">
-        <v>24.2</v>
+        <v>31.3</v>
       </c>
       <c r="I24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-21.21</v>
+        <v>-249.45</v>
       </c>
       <c r="K24" t="n">
-        <v>-125.1</v>
+        <v>59.21</v>
       </c>
       <c r="L24" t="n">
-        <v>126.89</v>
+        <v>256.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:57:01</t>
+          <t>04:52:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.93</v>
+        <v>3.53</v>
       </c>
       <c r="F25" t="n">
-        <v>14.62</v>
+        <v>10.37</v>
       </c>
       <c r="G25" t="n">
-        <v>301.4</v>
+        <v>303.2</v>
       </c>
       <c r="H25" t="n">
-        <v>25.7</v>
+        <v>28.1</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>66.7</v>
+        <v>-118.83</v>
       </c>
       <c r="K25" t="n">
-        <v>133.66</v>
+        <v>107.86</v>
       </c>
       <c r="L25" t="n">
-        <v>149.38</v>
+        <v>160.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:02:18</t>
+          <t>04:57:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.04</v>
+        <v>4.21</v>
       </c>
       <c r="F26" t="n">
-        <v>14.16</v>
+        <v>9.82</v>
       </c>
       <c r="G26" t="n">
-        <v>308.4</v>
+        <v>310.9</v>
       </c>
       <c r="H26" t="n">
-        <v>34.4</v>
+        <v>27.4</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-298.51</v>
+        <v>-215.68</v>
       </c>
       <c r="K26" t="n">
-        <v>66.08</v>
+        <v>-55.64</v>
       </c>
       <c r="L26" t="n">
-        <v>305.74</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:04:24</t>
+          <t>04:58:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.58</v>
+        <v>3.81</v>
       </c>
       <c r="F27" t="n">
-        <v>14.16</v>
+        <v>8.31</v>
       </c>
       <c r="G27" t="n">
-        <v>302</v>
+        <v>295.8</v>
       </c>
       <c r="H27" t="n">
-        <v>23.6</v>
+        <v>30.6</v>
       </c>
       <c r="I27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-126.47</v>
+        <v>-85.25</v>
       </c>
       <c r="K27" t="n">
-        <v>119.09</v>
+        <v>180.48</v>
       </c>
       <c r="L27" t="n">
-        <v>173.72</v>
+        <v>199.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:05:29</t>
+          <t>04:59:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.24</v>
+        <v>3.98</v>
       </c>
       <c r="F28" t="n">
-        <v>14.54</v>
+        <v>9.81</v>
       </c>
       <c r="G28" t="n">
-        <v>300.7</v>
+        <v>306.3</v>
       </c>
       <c r="H28" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-171.47</v>
+        <v>-41</v>
       </c>
       <c r="K28" t="n">
-        <v>-77.06</v>
+        <v>231.61</v>
       </c>
       <c r="L28" t="n">
-        <v>188</v>
+        <v>235.21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:15:34</t>
+          <t>05:08:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.88</v>
+        <v>4.89</v>
       </c>
       <c r="F29" t="n">
-        <v>13.79</v>
+        <v>15.19</v>
       </c>
       <c r="G29" t="n">
-        <v>307.2</v>
+        <v>304.7</v>
       </c>
       <c r="H29" t="n">
-        <v>27.5</v>
+        <v>26.3</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.4</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>50.27</v>
+        <v>29.77</v>
       </c>
       <c r="L29" t="n">
-        <v>51.54</v>
+        <v>81.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:05</t>
+          <t>05:10:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="F30" t="n">
-        <v>14.31</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>293</v>
+        <v>298.2</v>
       </c>
       <c r="H30" t="n">
-        <v>24.7</v>
+        <v>26.8</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>1.14</v>
+        <v>33.5</v>
       </c>
       <c r="K30" t="n">
-        <v>53.96</v>
+        <v>59.5</v>
       </c>
       <c r="L30" t="n">
-        <v>53.97</v>
+        <v>68.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:17:51</t>
+          <t>05:11:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.93</v>
+        <v>4.29</v>
       </c>
       <c r="F31" t="n">
-        <v>14.23</v>
+        <v>13.11</v>
       </c>
       <c r="G31" t="n">
-        <v>298.4</v>
+        <v>296.9</v>
       </c>
       <c r="H31" t="n">
-        <v>29</v>
+        <v>23.8</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>59.6</v>
+        <v>31.53</v>
       </c>
       <c r="K31" t="n">
-        <v>22.18</v>
+        <v>5.44</v>
       </c>
       <c r="L31" t="n">
-        <v>63.6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:21:47</t>
+          <t>05:16:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.96</v>
+        <v>4.42</v>
       </c>
       <c r="F32" t="n">
-        <v>13.91</v>
+        <v>13.94</v>
       </c>
       <c r="G32" t="n">
-        <v>299.6</v>
+        <v>322.5</v>
       </c>
       <c r="H32" t="n">
-        <v>21.3</v>
+        <v>28.1</v>
       </c>
       <c r="I32" t="n">
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>32.57</v>
+        <v>10.36</v>
       </c>
       <c r="K32" t="n">
-        <v>57.7</v>
+        <v>117.96</v>
       </c>
       <c r="L32" t="n">
-        <v>66.26000000000001</v>
+        <v>118.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:23:24</t>
+          <t>05:17:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
       <c r="F33" t="n">
-        <v>13.84</v>
+        <v>10.95</v>
       </c>
       <c r="G33" t="n">
-        <v>293.4</v>
+        <v>305.5</v>
       </c>
       <c r="H33" t="n">
-        <v>28</v>
+        <v>23.5</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>27.61</v>
+        <v>-17.58</v>
       </c>
       <c r="K33" t="n">
-        <v>4.23</v>
+        <v>-85.59</v>
       </c>
       <c r="L33" t="n">
-        <v>27.93</v>
+        <v>87.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:24:52</t>
+          <t>05:19:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.45</v>
+        <v>4.94</v>
       </c>
       <c r="F34" t="n">
-        <v>15.12</v>
+        <v>12.05</v>
       </c>
       <c r="G34" t="n">
-        <v>302.1</v>
+        <v>298.1</v>
       </c>
       <c r="H34" t="n">
-        <v>30.8</v>
+        <v>33.1</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>9.359999999999999</v>
+        <v>56.3</v>
       </c>
       <c r="K34" t="n">
-        <v>96.52</v>
+        <v>40.91</v>
       </c>
       <c r="L34" t="n">
-        <v>96.97</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:27:48</t>
+          <t>05:24:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.46</v>
+        <v>3.36</v>
       </c>
       <c r="F35" t="n">
-        <v>14.27</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>292.8</v>
+        <v>289.2</v>
       </c>
       <c r="H35" t="n">
-        <v>34.2</v>
+        <v>27.7</v>
       </c>
       <c r="I35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.95</v>
+        <v>-108.67</v>
       </c>
       <c r="K35" t="n">
-        <v>-104.34</v>
+        <v>-15.18</v>
       </c>
       <c r="L35" t="n">
-        <v>106.62</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:29:24</t>
+          <t>05:25:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.98</v>
+        <v>4.43</v>
       </c>
       <c r="F36" t="n">
-        <v>13.9</v>
+        <v>11.34</v>
       </c>
       <c r="G36" t="n">
-        <v>312.1</v>
+        <v>309.7</v>
       </c>
       <c r="H36" t="n">
-        <v>23.2</v>
+        <v>33.9</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>83.7</v>
+        <v>-106.48</v>
       </c>
       <c r="K36" t="n">
-        <v>62.04</v>
+        <v>-102.54</v>
       </c>
       <c r="L36" t="n">
-        <v>104.19</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:31:39</t>
+          <t>05:26:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.39</v>
+        <v>4.49</v>
       </c>
       <c r="F37" t="n">
-        <v>13.46</v>
+        <v>15.19</v>
       </c>
       <c r="G37" t="n">
-        <v>301.2</v>
+        <v>304</v>
       </c>
       <c r="H37" t="n">
-        <v>26.8</v>
+        <v>24.5</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-85.86</v>
+        <v>-25.95</v>
       </c>
       <c r="K37" t="n">
-        <v>-14.51</v>
+        <v>134.23</v>
       </c>
       <c r="L37" t="n">
-        <v>87.06999999999999</v>
+        <v>136.71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:36:51</t>
+          <t>05:31:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="F38" t="n">
-        <v>14.48</v>
+        <v>13.28</v>
       </c>
       <c r="G38" t="n">
-        <v>313.7</v>
+        <v>305.2</v>
       </c>
       <c r="H38" t="n">
-        <v>24.8</v>
+        <v>21.3</v>
       </c>
       <c r="I38" t="n">
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-103.86</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-112.42</v>
+        <v>120.21</v>
       </c>
       <c r="L38" t="n">
-        <v>153.05</v>
+        <v>145.15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:38:24</t>
+          <t>05:33:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.53</v>
+        <v>4.3</v>
       </c>
       <c r="F39" t="n">
-        <v>14.19</v>
+        <v>11.98</v>
       </c>
       <c r="G39" t="n">
-        <v>294.9</v>
+        <v>305.8</v>
       </c>
       <c r="H39" t="n">
-        <v>25.4</v>
+        <v>26.9</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.7</v>
+        <v>113.48</v>
       </c>
       <c r="K39" t="n">
-        <v>123.25</v>
+        <v>193.09</v>
       </c>
       <c r="L39" t="n">
-        <v>124.38</v>
+        <v>223.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:40:27</t>
+          <t>05:35:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.47</v>
+        <v>4.8</v>
       </c>
       <c r="F40" t="n">
-        <v>14.26</v>
+        <v>11.19</v>
       </c>
       <c r="G40" t="n">
-        <v>288.6</v>
+        <v>299.5</v>
       </c>
       <c r="H40" t="n">
-        <v>28.9</v>
+        <v>22.4</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>91.89</v>
+        <v>-68.64</v>
       </c>
       <c r="K40" t="n">
-        <v>82.15000000000001</v>
+        <v>-181.56</v>
       </c>
       <c r="L40" t="n">
-        <v>123.26</v>
+        <v>194.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:45:08</t>
+          <t>05:39:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.35</v>
+        <v>4.94</v>
       </c>
       <c r="F41" t="n">
-        <v>14.28</v>
+        <v>16.21</v>
       </c>
       <c r="G41" t="n">
-        <v>299.6</v>
+        <v>295.4</v>
       </c>
       <c r="H41" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>173.24</v>
+        <v>338.93</v>
       </c>
       <c r="K41" t="n">
-        <v>251.69</v>
+        <v>-35.06</v>
       </c>
       <c r="L41" t="n">
-        <v>305.55</v>
+        <v>340.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:46:59</t>
+          <t>05:42:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.84</v>
+        <v>4.22</v>
       </c>
       <c r="F42" t="n">
-        <v>13.97</v>
+        <v>14.47</v>
       </c>
       <c r="G42" t="n">
-        <v>290.7</v>
+        <v>300</v>
       </c>
       <c r="H42" t="n">
-        <v>21.9</v>
+        <v>24.7</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J42" t="n">
-        <v>-68.13</v>
+        <v>-50.37</v>
       </c>
       <c r="K42" t="n">
-        <v>-252.06</v>
+        <v>237.32</v>
       </c>
       <c r="L42" t="n">
-        <v>261.11</v>
+        <v>242.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:48:07</t>
+          <t>05:44:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.97</v>
+        <v>4.07</v>
       </c>
       <c r="F43" t="n">
-        <v>13.76</v>
+        <v>12.11</v>
       </c>
       <c r="G43" t="n">
-        <v>303.9</v>
+        <v>301.3</v>
       </c>
       <c r="H43" t="n">
-        <v>32.4</v>
+        <v>29.4</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>316.72</v>
+        <v>-106.46</v>
       </c>
       <c r="K43" t="n">
-        <v>-35.88</v>
+        <v>-248.93</v>
       </c>
       <c r="L43" t="n">
-        <v>318.74</v>
+        <v>270.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:57:50</t>
+          <t>05:55:56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>9.99</v>
       </c>
       <c r="G44" t="n">
-        <v>295.3</v>
+        <v>285.6</v>
       </c>
       <c r="H44" t="n">
-        <v>32.8</v>
+        <v>27.8</v>
       </c>
       <c r="I44" t="n">
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>2.03</v>
+        <v>27.26</v>
       </c>
       <c r="K44" t="n">
-        <v>55.1</v>
+        <v>16.13</v>
       </c>
       <c r="L44" t="n">
-        <v>55.14</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05:59:27</t>
+          <t>05:56:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="F45" t="n">
-        <v>14.06</v>
+        <v>11.26</v>
       </c>
       <c r="G45" t="n">
-        <v>304.7</v>
+        <v>294.9</v>
       </c>
       <c r="H45" t="n">
-        <v>37.4</v>
+        <v>28.3</v>
       </c>
       <c r="I45" t="n">
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.57</v>
+        <v>35.85</v>
       </c>
       <c r="K45" t="n">
-        <v>-71.52</v>
+        <v>-24.25</v>
       </c>
       <c r="L45" t="n">
-        <v>72.98999999999999</v>
+        <v>43.29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:00:56</t>
+          <t>05:59:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.39</v>
+        <v>5.58</v>
       </c>
       <c r="F46" t="n">
-        <v>13.27</v>
+        <v>15.98</v>
       </c>
       <c r="G46" t="n">
-        <v>301.5</v>
+        <v>298.7</v>
       </c>
       <c r="H46" t="n">
-        <v>21.7</v>
+        <v>27</v>
       </c>
       <c r="I46" t="n">
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>27.74</v>
+        <v>42.01</v>
       </c>
       <c r="K46" t="n">
-        <v>14.64</v>
+        <v>-43.95</v>
       </c>
       <c r="L46" t="n">
-        <v>31.37</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:06:20</t>
+          <t>06:04:41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="F47" t="n">
-        <v>13.74</v>
+        <v>10.83</v>
       </c>
       <c r="G47" t="n">
-        <v>302.6</v>
+        <v>309.1</v>
       </c>
       <c r="H47" t="n">
-        <v>28.1</v>
+        <v>26.2</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>35.05</v>
+        <v>78.08</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.26</v>
+        <v>43.22</v>
       </c>
       <c r="L47" t="n">
-        <v>41.52</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:08:06</t>
+          <t>06:05:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.62</v>
+        <v>4.75</v>
       </c>
       <c r="F48" t="n">
-        <v>13.93</v>
+        <v>13.91</v>
       </c>
       <c r="G48" t="n">
-        <v>299.9</v>
+        <v>302</v>
       </c>
       <c r="H48" t="n">
-        <v>27</v>
+        <v>28.4</v>
       </c>
       <c r="I48" t="n">
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>44.25</v>
+        <v>-10.38</v>
       </c>
       <c r="K48" t="n">
-        <v>-46.08</v>
+        <v>-61.89</v>
       </c>
       <c r="L48" t="n">
-        <v>63.88</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:09:26</t>
+          <t>06:06:54</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.28</v>
+        <v>4.79</v>
       </c>
       <c r="F49" t="n">
-        <v>14.45</v>
+        <v>15.18</v>
       </c>
       <c r="G49" t="n">
-        <v>298.4</v>
+        <v>306.6</v>
       </c>
       <c r="H49" t="n">
-        <v>21.1</v>
+        <v>27.3</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>69.43000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="K49" t="n">
-        <v>35.58</v>
+        <v>-59.97</v>
       </c>
       <c r="L49" t="n">
-        <v>78.01000000000001</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:14:51</t>
+          <t>06:10:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.79</v>
+        <v>5.83</v>
       </c>
       <c r="F50" t="n">
-        <v>14.1</v>
+        <v>16.21</v>
       </c>
       <c r="G50" t="n">
-        <v>302.6</v>
+        <v>312.5</v>
       </c>
       <c r="H50" t="n">
-        <v>27.7</v>
+        <v>22.6</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.43</v>
+        <v>-122.03</v>
       </c>
       <c r="K50" t="n">
-        <v>-87.14</v>
+        <v>66.88</v>
       </c>
       <c r="L50" t="n">
-        <v>88.33</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:17:07</t>
+          <t>06:12:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="F51" t="n">
-        <v>14.33</v>
+        <v>14.43</v>
       </c>
       <c r="G51" t="n">
-        <v>300.6</v>
+        <v>304.8</v>
       </c>
       <c r="H51" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>12.21</v>
+        <v>106.57</v>
       </c>
       <c r="K51" t="n">
-        <v>-81.03</v>
+        <v>28.39</v>
       </c>
       <c r="L51" t="n">
-        <v>81.94</v>
+        <v>110.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:19:14</t>
+          <t>06:13:31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.86</v>
+        <v>4.18</v>
       </c>
       <c r="F52" t="n">
-        <v>14.62</v>
+        <v>13.81</v>
       </c>
       <c r="G52" t="n">
-        <v>291.1</v>
+        <v>287.9</v>
       </c>
       <c r="H52" t="n">
-        <v>25.7</v>
+        <v>21</v>
       </c>
       <c r="I52" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-103.69</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>43.48</v>
+        <v>-91.58</v>
       </c>
       <c r="L52" t="n">
-        <v>112.44</v>
+        <v>134.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:22:28</t>
+          <t>06:18:58</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.87</v>
+        <v>4.61</v>
       </c>
       <c r="F53" t="n">
-        <v>14.23</v>
+        <v>13.29</v>
       </c>
       <c r="G53" t="n">
-        <v>304</v>
+        <v>293.2</v>
       </c>
       <c r="H53" t="n">
-        <v>28.7</v>
+        <v>22.9</v>
       </c>
       <c r="I53" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>126.84</v>
+        <v>-77.87</v>
       </c>
       <c r="K53" t="n">
-        <v>21.06</v>
+        <v>-146.99</v>
       </c>
       <c r="L53" t="n">
-        <v>128.58</v>
+        <v>166.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:24:33</t>
+          <t>06:19:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.22</v>
+        <v>4.93</v>
       </c>
       <c r="F54" t="n">
-        <v>13.39</v>
+        <v>13.96</v>
       </c>
       <c r="G54" t="n">
-        <v>287.8</v>
+        <v>301.1</v>
       </c>
       <c r="H54" t="n">
-        <v>31.1</v>
+        <v>29.2</v>
       </c>
       <c r="I54" t="n">
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>128.41</v>
+        <v>-157.53</v>
       </c>
       <c r="K54" t="n">
-        <v>-113.97</v>
+        <v>-147.02</v>
       </c>
       <c r="L54" t="n">
-        <v>171.69</v>
+        <v>215.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:26:51</t>
+          <t>06:22:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.64</v>
+        <v>4.44</v>
       </c>
       <c r="F55" t="n">
-        <v>13.66</v>
+        <v>11.03</v>
       </c>
       <c r="G55" t="n">
-        <v>291.8</v>
+        <v>296</v>
       </c>
       <c r="H55" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-38.2</v>
+        <v>107.64</v>
       </c>
       <c r="K55" t="n">
-        <v>-133.3</v>
+        <v>-81.09999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>138.66</v>
+        <v>134.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:31:20</t>
+          <t>06:26:38</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.97</v>
+        <v>5.12</v>
       </c>
       <c r="F56" t="n">
-        <v>14.05</v>
+        <v>15.89</v>
       </c>
       <c r="G56" t="n">
-        <v>304.4</v>
+        <v>280.9</v>
       </c>
       <c r="H56" t="n">
-        <v>26.4</v>
+        <v>27.3</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-206.06</v>
+        <v>-198.43</v>
       </c>
       <c r="K56" t="n">
-        <v>-228.54</v>
+        <v>168.53</v>
       </c>
       <c r="L56" t="n">
-        <v>307.72</v>
+        <v>260.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:32:21</t>
+          <t>06:28:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.48</v>
+        <v>3.8</v>
       </c>
       <c r="F57" t="n">
-        <v>13.8</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>303.6</v>
+        <v>308</v>
       </c>
       <c r="H57" t="n">
-        <v>22.5</v>
+        <v>28</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>169.24</v>
+        <v>24.86</v>
       </c>
       <c r="K57" t="n">
-        <v>-110.37</v>
+        <v>191.36</v>
       </c>
       <c r="L57" t="n">
-        <v>202.05</v>
+        <v>192.96</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:33:16</t>
+          <t>06:29:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.14</v>
+        <v>4.45</v>
       </c>
       <c r="F58" t="n">
-        <v>13.04</v>
+        <v>14.34</v>
       </c>
       <c r="G58" t="n">
-        <v>300.4</v>
+        <v>297.9</v>
       </c>
       <c r="H58" t="n">
-        <v>29.3</v>
+        <v>23.2</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-122.97</v>
+        <v>111.45</v>
       </c>
       <c r="K58" t="n">
-        <v>176.97</v>
+        <v>188.32</v>
       </c>
       <c r="L58" t="n">
-        <v>215.5</v>
+        <v>218.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:43:05</t>
+          <t>06:38:41</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.85</v>
+        <v>4.95</v>
       </c>
       <c r="F59" t="n">
-        <v>14.4</v>
+        <v>16.21</v>
       </c>
       <c r="G59" t="n">
-        <v>301.9</v>
+        <v>285.8</v>
       </c>
       <c r="H59" t="n">
-        <v>29</v>
+        <v>33.1</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>22.74</v>
+        <v>-47.04</v>
       </c>
       <c r="K59" t="n">
-        <v>45.78</v>
+        <v>44.38</v>
       </c>
       <c r="L59" t="n">
-        <v>51.11</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:45:29</t>
+          <t>06:39:38</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.51</v>
+        <v>4.79</v>
       </c>
       <c r="F60" t="n">
-        <v>13.89</v>
+        <v>12.54</v>
       </c>
       <c r="G60" t="n">
-        <v>292.3</v>
+        <v>300.7</v>
       </c>
       <c r="H60" t="n">
-        <v>30.3</v>
+        <v>27.9</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>42.68</v>
+        <v>60.96</v>
       </c>
       <c r="K60" t="n">
-        <v>29.56</v>
+        <v>11.85</v>
       </c>
       <c r="L60" t="n">
-        <v>51.91</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:47:54</t>
+          <t>06:40:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.98</v>
+        <v>4.07</v>
       </c>
       <c r="F61" t="n">
-        <v>13.29</v>
+        <v>16.21</v>
       </c>
       <c r="G61" t="n">
-        <v>312.1</v>
+        <v>302.6</v>
       </c>
       <c r="H61" t="n">
-        <v>27.3</v>
+        <v>16.2</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-36.57</v>
+        <v>-27.25</v>
       </c>
       <c r="K61" t="n">
-        <v>36.94</v>
+        <v>-51.97</v>
       </c>
       <c r="L61" t="n">
-        <v>51.98</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:52:42</t>
+          <t>06:46:04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.83</v>
+        <v>4.55</v>
       </c>
       <c r="F62" t="n">
-        <v>14.03</v>
+        <v>11.7</v>
       </c>
       <c r="G62" t="n">
-        <v>301.6</v>
+        <v>301.7</v>
       </c>
       <c r="H62" t="n">
-        <v>23.9</v>
+        <v>32.9</v>
       </c>
       <c r="I62" t="n">
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>63.8</v>
+        <v>51.58</v>
       </c>
       <c r="K62" t="n">
-        <v>12.34</v>
+        <v>-74.56</v>
       </c>
       <c r="L62" t="n">
-        <v>64.98</v>
+        <v>90.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:54:26</t>
+          <t>06:48:31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.12</v>
+        <v>4.43</v>
       </c>
       <c r="F63" t="n">
-        <v>14.13</v>
+        <v>16.21</v>
       </c>
       <c r="G63" t="n">
-        <v>278.3</v>
+        <v>297.4</v>
       </c>
       <c r="H63" t="n">
-        <v>34.7</v>
+        <v>19.5</v>
       </c>
       <c r="I63" t="n">
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.93</v>
+        <v>30.34</v>
       </c>
       <c r="K63" t="n">
-        <v>-44.66</v>
+        <v>102.98</v>
       </c>
       <c r="L63" t="n">
-        <v>50.2</v>
+        <v>107.36</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:56:00</t>
+          <t>06:50:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.58</v>
+        <v>5.32</v>
       </c>
       <c r="F64" t="n">
-        <v>14.08</v>
+        <v>14.53</v>
       </c>
       <c r="G64" t="n">
-        <v>311.6</v>
+        <v>299.2</v>
       </c>
       <c r="H64" t="n">
-        <v>23.5</v>
+        <v>34.6</v>
       </c>
       <c r="I64" t="n">
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>47.6</v>
+        <v>-33.16</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.31999999999999</v>
+        <v>-73.86</v>
       </c>
       <c r="L64" t="n">
-        <v>81.63</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:00:59</t>
+          <t>06:55:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.47</v>
+        <v>4.96</v>
       </c>
       <c r="F65" t="n">
-        <v>13.87</v>
+        <v>14.39</v>
       </c>
       <c r="G65" t="n">
-        <v>284.9</v>
+        <v>303.8</v>
       </c>
       <c r="H65" t="n">
-        <v>25.4</v>
+        <v>21.7</v>
       </c>
       <c r="I65" t="n">
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>44.99</v>
+        <v>-113.93</v>
       </c>
       <c r="K65" t="n">
-        <v>153.01</v>
+        <v>-41.97</v>
       </c>
       <c r="L65" t="n">
-        <v>159.49</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:01:53</t>
+          <t>06:56:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.36</v>
+        <v>4.88</v>
       </c>
       <c r="F66" t="n">
-        <v>13.95</v>
+        <v>13.44</v>
       </c>
       <c r="G66" t="n">
-        <v>315.1</v>
+        <v>309.8</v>
       </c>
       <c r="H66" t="n">
-        <v>24.5</v>
+        <v>28.5</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-52.21</v>
+        <v>-83.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-118.58</v>
+        <v>52.31</v>
       </c>
       <c r="L66" t="n">
-        <v>129.57</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:03:16</t>
+          <t>06:57:05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.98</v>
+        <v>4.11</v>
       </c>
       <c r="F67" t="n">
-        <v>14.18</v>
+        <v>12.58</v>
       </c>
       <c r="G67" t="n">
-        <v>289.3</v>
+        <v>302.2</v>
       </c>
       <c r="H67" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-86.31</v>
+        <v>130.12</v>
       </c>
       <c r="K67" t="n">
-        <v>-55</v>
+        <v>98.8</v>
       </c>
       <c r="L67" t="n">
-        <v>102.35</v>
+        <v>163.38</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:08:02</t>
+          <t>07:01:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.92</v>
+        <v>4.19</v>
       </c>
       <c r="F68" t="n">
-        <v>14.48</v>
+        <v>11.91</v>
       </c>
       <c r="G68" t="n">
-        <v>302.8</v>
+        <v>295.9</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>29.2</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-54.2</v>
+        <v>-98.94</v>
       </c>
       <c r="K68" t="n">
-        <v>19.45</v>
+        <v>126.05</v>
       </c>
       <c r="L68" t="n">
-        <v>57.58</v>
+        <v>160.25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:09:21</t>
+          <t>07:02:38</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.16</v>
+        <v>4.86</v>
       </c>
       <c r="F69" t="n">
-        <v>14.1</v>
+        <v>15.24</v>
       </c>
       <c r="G69" t="n">
-        <v>292.6</v>
+        <v>299.9</v>
       </c>
       <c r="H69" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>157.69</v>
+        <v>197.36</v>
       </c>
       <c r="K69" t="n">
-        <v>109.1</v>
+        <v>48.25</v>
       </c>
       <c r="L69" t="n">
-        <v>191.75</v>
+        <v>203.18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:11:13</t>
+          <t>07:03:09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.22</v>
+        <v>4.75</v>
       </c>
       <c r="F70" t="n">
-        <v>13.79</v>
+        <v>14.12</v>
       </c>
       <c r="G70" t="n">
-        <v>304.4</v>
+        <v>303.8</v>
       </c>
       <c r="H70" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="I70" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>-59.14</v>
+        <v>-90.33</v>
       </c>
       <c r="K70" t="n">
-        <v>101.33</v>
+        <v>-107.36</v>
       </c>
       <c r="L70" t="n">
-        <v>117.33</v>
+        <v>140.31</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:17:46</t>
+          <t>07:08:36</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.91</v>
+        <v>4.8</v>
       </c>
       <c r="F71" t="n">
-        <v>13.99</v>
+        <v>14.32</v>
       </c>
       <c r="G71" t="n">
-        <v>306.3</v>
+        <v>303.1</v>
       </c>
       <c r="H71" t="n">
-        <v>29.7</v>
+        <v>30.5</v>
       </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>265.17</v>
+        <v>101.06</v>
       </c>
       <c r="K71" t="n">
-        <v>48.83</v>
+        <v>-272.13</v>
       </c>
       <c r="L71" t="n">
-        <v>269.63</v>
+        <v>290.29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:19:43</t>
+          <t>07:10:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.8</v>
+        <v>5.22</v>
       </c>
       <c r="F72" t="n">
-        <v>14.18</v>
+        <v>11.89</v>
       </c>
       <c r="G72" t="n">
-        <v>298.6</v>
+        <v>298.9</v>
       </c>
       <c r="H72" t="n">
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-92.84999999999999</v>
+        <v>-265.46</v>
       </c>
       <c r="K72" t="n">
-        <v>-178.19</v>
+        <v>16.13</v>
       </c>
       <c r="L72" t="n">
-        <v>200.93</v>
+        <v>265.95</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:21:30</t>
+          <t>07:11:34</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.84</v>
+        <v>4.54</v>
       </c>
       <c r="F73" t="n">
-        <v>14.15</v>
+        <v>16.21</v>
       </c>
       <c r="G73" t="n">
-        <v>306.8</v>
+        <v>293.1</v>
       </c>
       <c r="H73" t="n">
-        <v>20.1</v>
+        <v>25.2</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>112.59</v>
+        <v>-292.37</v>
       </c>
       <c r="K73" t="n">
-        <v>-242.72</v>
+        <v>51.04</v>
       </c>
       <c r="L73" t="n">
-        <v>267.56</v>
+        <v>296.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:30:11</t>
+          <t>07:23:06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.29</v>
+        <v>4.53</v>
       </c>
       <c r="F74" t="n">
-        <v>13.94</v>
+        <v>11.97</v>
       </c>
       <c r="G74" t="n">
-        <v>303.5</v>
+        <v>302.2</v>
       </c>
       <c r="H74" t="n">
-        <v>19</v>
+        <v>25.6</v>
       </c>
       <c r="I74" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-46.79</v>
+        <v>33.02</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.42</v>
+        <v>-51.57</v>
       </c>
       <c r="L74" t="n">
-        <v>47.23</v>
+        <v>61.23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:32:21</t>
+          <t>07:24:48</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.61</v>
+        <v>4.76</v>
       </c>
       <c r="F75" t="n">
-        <v>13.65</v>
+        <v>11.68</v>
       </c>
       <c r="G75" t="n">
-        <v>296.2</v>
+        <v>293.7</v>
       </c>
       <c r="H75" t="n">
-        <v>27.1</v>
+        <v>24.3</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.09</v>
+        <v>-28.17</v>
       </c>
       <c r="K75" t="n">
-        <v>7.19</v>
+        <v>-55.84</v>
       </c>
       <c r="L75" t="n">
-        <v>64.48999999999999</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:33:06</t>
+          <t>07:26:58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.57</v>
+        <v>5.41</v>
       </c>
       <c r="F76" t="n">
-        <v>14.1</v>
+        <v>13.21</v>
       </c>
       <c r="G76" t="n">
-        <v>297.1</v>
+        <v>306.8</v>
       </c>
       <c r="H76" t="n">
-        <v>23.7</v>
+        <v>22.2</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>28.42</v>
+        <v>70.87</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.57</v>
+        <v>32.27</v>
       </c>
       <c r="L76" t="n">
-        <v>52.02</v>
+        <v>77.87</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:37:55</t>
+          <t>07:29:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="F77" t="n">
-        <v>13.68</v>
+        <v>16.21</v>
       </c>
       <c r="G77" t="n">
-        <v>294.5</v>
+        <v>305.5</v>
       </c>
       <c r="H77" t="n">
-        <v>28.1</v>
+        <v>33.3</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-31.78</v>
+        <v>34.64</v>
       </c>
       <c r="K77" t="n">
-        <v>-63.25</v>
+        <v>113.85</v>
       </c>
       <c r="L77" t="n">
-        <v>70.78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:39:07</t>
+          <t>07:31:14</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.45</v>
+        <v>4.72</v>
       </c>
       <c r="F78" t="n">
-        <v>14.34</v>
+        <v>13.83</v>
       </c>
       <c r="G78" t="n">
-        <v>290.3</v>
+        <v>290</v>
       </c>
       <c r="H78" t="n">
-        <v>20.4</v>
+        <v>28.4</v>
       </c>
       <c r="I78" t="n">
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>76.7</v>
+        <v>-3.96</v>
       </c>
       <c r="K78" t="n">
-        <v>34.13</v>
+        <v>108.16</v>
       </c>
       <c r="L78" t="n">
-        <v>83.95</v>
+        <v>108.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:41:03</t>
+          <t>07:33:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.99</v>
+        <v>4.02</v>
       </c>
       <c r="F79" t="n">
-        <v>14.27</v>
+        <v>14.8</v>
       </c>
       <c r="G79" t="n">
-        <v>312.5</v>
+        <v>295.4</v>
       </c>
       <c r="H79" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I79" t="n">
         <v>23</v>
       </c>
-      <c r="I79" t="n">
-        <v>29</v>
-      </c>
       <c r="J79" t="n">
-        <v>30.31</v>
+        <v>-103.73</v>
       </c>
       <c r="K79" t="n">
-        <v>91.11</v>
+        <v>-31.72</v>
       </c>
       <c r="L79" t="n">
-        <v>96.02</v>
+        <v>108.47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:46:30</t>
+          <t>07:38:03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.77</v>
+        <v>4.4</v>
       </c>
       <c r="F80" t="n">
-        <v>13.5</v>
+        <v>12.24</v>
       </c>
       <c r="G80" t="n">
-        <v>302.8</v>
+        <v>298.5</v>
       </c>
       <c r="H80" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="I80" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.19</v>
+        <v>-75.76000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>141.58</v>
+        <v>-92.18000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>141.64</v>
+        <v>119.31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:48:20</t>
+          <t>07:39:34</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.07</v>
+        <v>4.89</v>
       </c>
       <c r="F81" t="n">
-        <v>13.77</v>
+        <v>15.43</v>
       </c>
       <c r="G81" t="n">
-        <v>300.7</v>
+        <v>285.7</v>
       </c>
       <c r="H81" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="I81" t="n">
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-129.48</v>
+        <v>-83.73</v>
       </c>
       <c r="K81" t="n">
-        <v>-39.15</v>
+        <v>-103.39</v>
       </c>
       <c r="L81" t="n">
-        <v>135.27</v>
+        <v>133.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:49:15</t>
+          <t>07:41:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.43</v>
+        <v>4.52</v>
       </c>
       <c r="F82" t="n">
-        <v>13.92</v>
+        <v>15.86</v>
       </c>
       <c r="G82" t="n">
-        <v>298.3</v>
+        <v>294.7</v>
       </c>
       <c r="H82" t="n">
-        <v>24.9</v>
+        <v>32.5</v>
       </c>
       <c r="I82" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-51.44</v>
+        <v>-79.56999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-83.19</v>
+        <v>98.84</v>
       </c>
       <c r="L82" t="n">
-        <v>97.81</v>
+        <v>126.89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:52:45</t>
+          <t>07:46:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="F83" t="n">
-        <v>13.28</v>
+        <v>16.21</v>
       </c>
       <c r="G83" t="n">
-        <v>301.1</v>
+        <v>302.1</v>
       </c>
       <c r="H83" t="n">
-        <v>25.7</v>
+        <v>33.6</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-79.3</v>
+        <v>-70.28</v>
       </c>
       <c r="K83" t="n">
-        <v>-119.68</v>
+        <v>178.57</v>
       </c>
       <c r="L83" t="n">
-        <v>143.57</v>
+        <v>191.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:54:55</t>
+          <t>07:48:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.56</v>
+        <v>4.69</v>
       </c>
       <c r="F84" t="n">
-        <v>13.73</v>
+        <v>13.5</v>
       </c>
       <c r="G84" t="n">
-        <v>310.8</v>
+        <v>307.4</v>
       </c>
       <c r="H84" t="n">
-        <v>32.1</v>
+        <v>25</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-78.81</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>116.89</v>
+        <v>114.26</v>
       </c>
       <c r="L84" t="n">
-        <v>140.98</v>
+        <v>149.89</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:55:29</t>
+          <t>07:49:49</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.97</v>
+        <v>4.49</v>
       </c>
       <c r="F85" t="n">
-        <v>14.1</v>
+        <v>13.02</v>
       </c>
       <c r="G85" t="n">
-        <v>313</v>
+        <v>299.1</v>
       </c>
       <c r="H85" t="n">
-        <v>25.7</v>
+        <v>35.7</v>
       </c>
       <c r="I85" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.22</v>
+        <v>-104.07</v>
       </c>
       <c r="K85" t="n">
-        <v>153.74</v>
+        <v>69.98</v>
       </c>
       <c r="L85" t="n">
-        <v>159.17</v>
+        <v>125.41</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07:59:30</t>
+          <t>07:55:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.72</v>
+        <v>4.83</v>
       </c>
       <c r="F86" t="n">
-        <v>14.36</v>
+        <v>15.72</v>
       </c>
       <c r="G86" t="n">
-        <v>296</v>
+        <v>294.9</v>
       </c>
       <c r="H86" t="n">
-        <v>25.6</v>
+        <v>26.9</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>166.62</v>
+        <v>-204.2</v>
       </c>
       <c r="K86" t="n">
-        <v>123.13</v>
+        <v>-46.2</v>
       </c>
       <c r="L86" t="n">
-        <v>207.18</v>
+        <v>209.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:01:47</t>
+          <t>07:57:48</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.52</v>
+        <v>5.51</v>
       </c>
       <c r="F87" t="n">
-        <v>13.95</v>
+        <v>16.21</v>
       </c>
       <c r="G87" t="n">
-        <v>317.2</v>
+        <v>297.4</v>
       </c>
       <c r="H87" t="n">
-        <v>29.5</v>
+        <v>28.9</v>
       </c>
       <c r="I87" t="n">
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-63.14</v>
+        <v>183.14</v>
       </c>
       <c r="K87" t="n">
-        <v>93.31999999999999</v>
+        <v>389.74</v>
       </c>
       <c r="L87" t="n">
-        <v>112.68</v>
+        <v>430.63</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:03:30</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="F88" t="n">
-        <v>13.74</v>
+        <v>15.19</v>
       </c>
       <c r="G88" t="n">
-        <v>299.8</v>
+        <v>285.2</v>
       </c>
       <c r="H88" t="n">
-        <v>29.4</v>
+        <v>35</v>
       </c>
       <c r="I88" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-46.99</v>
+        <v>-180.02</v>
       </c>
       <c r="K88" t="n">
-        <v>-47.53</v>
+        <v>-364.05</v>
       </c>
       <c r="L88" t="n">
-        <v>66.84</v>
+        <v>406.13</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-61.07</v>
+        <v>-59.53</v>
       </c>
       <c r="K14" t="n">
-        <v>-45.16</v>
+        <v>-44.03</v>
       </c>
       <c r="L14" t="n">
-        <v>75.95</v>
+        <v>74.04000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>64.72</v>
+        <v>63.23</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.67</v>
+        <v>-17.26</v>
       </c>
       <c r="L15" t="n">
-        <v>67.09</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -727,10 +727,10 @@
         <v>0.34</v>
       </c>
       <c r="K16" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="L16" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-55.67</v>
+        <v>-56.62</v>
       </c>
       <c r="K17" t="n">
-        <v>-43.15</v>
+        <v>-43.88</v>
       </c>
       <c r="L17" t="n">
-        <v>70.43000000000001</v>
+        <v>71.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>86</v>
+        <v>78.13</v>
       </c>
       <c r="K18" t="n">
-        <v>-32.37</v>
+        <v>-29.41</v>
       </c>
       <c r="L18" t="n">
-        <v>91.89</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-65.62</v>
+        <v>-61.26</v>
       </c>
       <c r="K19" t="n">
-        <v>40.44</v>
+        <v>37.76</v>
       </c>
       <c r="L19" t="n">
-        <v>77.08</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-25.56</v>
+        <v>-22.67</v>
       </c>
       <c r="K20" t="n">
-        <v>-108.92</v>
+        <v>-96.64</v>
       </c>
       <c r="L20" t="n">
-        <v>111.88</v>
+        <v>99.26000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>7.85</v>
+        <v>7.49</v>
       </c>
       <c r="K21" t="n">
-        <v>-126.61</v>
+        <v>-120.88</v>
       </c>
       <c r="L21" t="n">
-        <v>126.85</v>
+        <v>121.11</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-29.39</v>
+        <v>-29.93</v>
       </c>
       <c r="K22" t="n">
-        <v>-115.93</v>
+        <v>-118.05</v>
       </c>
       <c r="L22" t="n">
-        <v>119.6</v>
+        <v>121.78</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>57.81</v>
+        <v>55.88</v>
       </c>
       <c r="K23" t="n">
-        <v>174.08</v>
+        <v>168.29</v>
       </c>
       <c r="L23" t="n">
-        <v>183.43</v>
+        <v>177.33</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-249.45</v>
+        <v>-256.65</v>
       </c>
       <c r="K24" t="n">
-        <v>59.21</v>
+        <v>60.92</v>
       </c>
       <c r="L24" t="n">
-        <v>256.38</v>
+        <v>263.78</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-118.83</v>
+        <v>-111.28</v>
       </c>
       <c r="K25" t="n">
-        <v>107.86</v>
+        <v>101.01</v>
       </c>
       <c r="L25" t="n">
-        <v>160.48</v>
+        <v>150.29</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-215.68</v>
+        <v>-217.23</v>
       </c>
       <c r="K26" t="n">
-        <v>-55.64</v>
+        <v>-56.04</v>
       </c>
       <c r="L26" t="n">
-        <v>222.74</v>
+        <v>224.34</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-85.25</v>
+        <v>-78.19</v>
       </c>
       <c r="K27" t="n">
-        <v>180.48</v>
+        <v>165.53</v>
       </c>
       <c r="L27" t="n">
-        <v>199.6</v>
+        <v>183.07</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-41</v>
+        <v>-40.39</v>
       </c>
       <c r="K28" t="n">
-        <v>231.61</v>
+        <v>228.17</v>
       </c>
       <c r="L28" t="n">
-        <v>235.21</v>
+        <v>231.72</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>76.26000000000001</v>
+        <v>77.16</v>
       </c>
       <c r="K29" t="n">
-        <v>29.77</v>
+        <v>30.12</v>
       </c>
       <c r="L29" t="n">
-        <v>81.86</v>
+        <v>82.83</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>33.5</v>
+        <v>32.71</v>
       </c>
       <c r="K30" t="n">
-        <v>59.5</v>
+        <v>58.09</v>
       </c>
       <c r="L30" t="n">
-        <v>68.28</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>31.53</v>
+        <v>31.38</v>
       </c>
       <c r="K31" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="L31" t="n">
-        <v>32</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>10.36</v>
+        <v>9.16</v>
       </c>
       <c r="K32" t="n">
-        <v>117.96</v>
+        <v>104.28</v>
       </c>
       <c r="L32" t="n">
-        <v>118.42</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-17.58</v>
+        <v>-17.82</v>
       </c>
       <c r="K33" t="n">
-        <v>-85.59</v>
+        <v>-86.79000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>87.38</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>56.3</v>
+        <v>49.66</v>
       </c>
       <c r="K34" t="n">
-        <v>40.91</v>
+        <v>36.08</v>
       </c>
       <c r="L34" t="n">
-        <v>69.59999999999999</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-108.67</v>
+        <v>-96.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-15.18</v>
+        <v>-13.49</v>
       </c>
       <c r="L35" t="n">
-        <v>109.72</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-106.48</v>
+        <v>-104.11</v>
       </c>
       <c r="K36" t="n">
-        <v>-102.54</v>
+        <v>-100.25</v>
       </c>
       <c r="L36" t="n">
-        <v>147.82</v>
+        <v>144.53</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-25.95</v>
+        <v>-26.41</v>
       </c>
       <c r="K37" t="n">
-        <v>134.23</v>
+        <v>136.59</v>
       </c>
       <c r="L37" t="n">
-        <v>136.71</v>
+        <v>139.12</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>81.34999999999999</v>
+        <v>74.38</v>
       </c>
       <c r="K38" t="n">
-        <v>120.21</v>
+        <v>109.91</v>
       </c>
       <c r="L38" t="n">
-        <v>145.15</v>
+        <v>132.71</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>113.48</v>
+        <v>108.88</v>
       </c>
       <c r="K39" t="n">
-        <v>193.09</v>
+        <v>185.27</v>
       </c>
       <c r="L39" t="n">
-        <v>223.97</v>
+        <v>214.9</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-68.64</v>
+        <v>-70.58</v>
       </c>
       <c r="K40" t="n">
-        <v>-181.56</v>
+        <v>-186.68</v>
       </c>
       <c r="L40" t="n">
-        <v>194.1</v>
+        <v>199.58</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>338.93</v>
+        <v>315.03</v>
       </c>
       <c r="K41" t="n">
-        <v>-35.06</v>
+        <v>-32.58</v>
       </c>
       <c r="L41" t="n">
-        <v>340.74</v>
+        <v>316.71</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>29</v>
       </c>
       <c r="J42" t="n">
-        <v>-50.37</v>
+        <v>-45.1</v>
       </c>
       <c r="K42" t="n">
-        <v>237.32</v>
+        <v>212.48</v>
       </c>
       <c r="L42" t="n">
-        <v>242.61</v>
+        <v>217.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-106.46</v>
+        <v>-102.67</v>
       </c>
       <c r="K43" t="n">
-        <v>-248.93</v>
+        <v>-240.06</v>
       </c>
       <c r="L43" t="n">
-        <v>270.74</v>
+        <v>261.09</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>27.26</v>
+        <v>25.38</v>
       </c>
       <c r="K44" t="n">
-        <v>16.13</v>
+        <v>15.02</v>
       </c>
       <c r="L44" t="n">
-        <v>31.67</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>35.85</v>
+        <v>35.67</v>
       </c>
       <c r="K45" t="n">
-        <v>-24.25</v>
+        <v>-24.13</v>
       </c>
       <c r="L45" t="n">
-        <v>43.29</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>42.01</v>
+        <v>37.95</v>
       </c>
       <c r="K46" t="n">
-        <v>-43.95</v>
+        <v>-39.71</v>
       </c>
       <c r="L46" t="n">
-        <v>60.8</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>78.08</v>
+        <v>76.12</v>
       </c>
       <c r="K47" t="n">
-        <v>43.22</v>
+        <v>42.14</v>
       </c>
       <c r="L47" t="n">
-        <v>89.25</v>
+        <v>87.01000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-10.38</v>
+        <v>-9.16</v>
       </c>
       <c r="K48" t="n">
-        <v>-61.89</v>
+        <v>-54.63</v>
       </c>
       <c r="L48" t="n">
-        <v>62.75</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>10.24</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-59.97</v>
+        <v>-54.37</v>
       </c>
       <c r="L49" t="n">
-        <v>60.84</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>-122.03</v>
+        <v>-107.99</v>
       </c>
       <c r="K50" t="n">
-        <v>66.88</v>
+        <v>59.19</v>
       </c>
       <c r="L50" t="n">
-        <v>139.15</v>
+        <v>123.15</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>106.57</v>
+        <v>94.5</v>
       </c>
       <c r="K51" t="n">
-        <v>28.39</v>
+        <v>25.17</v>
       </c>
       <c r="L51" t="n">
-        <v>110.28</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>98.45999999999999</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-91.58</v>
+        <v>-83.48</v>
       </c>
       <c r="L52" t="n">
-        <v>134.47</v>
+        <v>122.59</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-77.87</v>
+        <v>-80.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-146.99</v>
+        <v>-151.04</v>
       </c>
       <c r="L53" t="n">
-        <v>166.34</v>
+        <v>170.92</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-157.53</v>
+        <v>-158.93</v>
       </c>
       <c r="K54" t="n">
-        <v>-147.02</v>
+        <v>-148.32</v>
       </c>
       <c r="L54" t="n">
-        <v>215.48</v>
+        <v>217.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>107.64</v>
+        <v>105.59</v>
       </c>
       <c r="K55" t="n">
-        <v>-81.09999999999999</v>
+        <v>-79.55</v>
       </c>
       <c r="L55" t="n">
-        <v>134.78</v>
+        <v>132.21</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-198.43</v>
+        <v>-193.79</v>
       </c>
       <c r="K56" t="n">
-        <v>168.53</v>
+        <v>164.59</v>
       </c>
       <c r="L56" t="n">
-        <v>260.34</v>
+        <v>254.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>24.86</v>
+        <v>22.8</v>
       </c>
       <c r="K57" t="n">
-        <v>191.36</v>
+        <v>175.49</v>
       </c>
       <c r="L57" t="n">
-        <v>192.96</v>
+        <v>176.97</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>111.45</v>
+        <v>105.86</v>
       </c>
       <c r="K58" t="n">
-        <v>188.32</v>
+        <v>178.87</v>
       </c>
       <c r="L58" t="n">
-        <v>218.82</v>
+        <v>207.85</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.04</v>
+        <v>-45.72</v>
       </c>
       <c r="K59" t="n">
-        <v>44.38</v>
+        <v>43.13</v>
       </c>
       <c r="L59" t="n">
-        <v>64.67</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>60.96</v>
+        <v>59.29</v>
       </c>
       <c r="K60" t="n">
-        <v>11.85</v>
+        <v>11.52</v>
       </c>
       <c r="L60" t="n">
-        <v>62.1</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-27.25</v>
+        <v>-27.67</v>
       </c>
       <c r="K61" t="n">
-        <v>-51.97</v>
+        <v>-52.78</v>
       </c>
       <c r="L61" t="n">
-        <v>58.68</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>51.58</v>
+        <v>48</v>
       </c>
       <c r="K62" t="n">
-        <v>-74.56</v>
+        <v>-69.38</v>
       </c>
       <c r="L62" t="n">
-        <v>90.67</v>
+        <v>84.37</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>30.34</v>
+        <v>26.82</v>
       </c>
       <c r="K63" t="n">
-        <v>102.98</v>
+        <v>91.03</v>
       </c>
       <c r="L63" t="n">
-        <v>107.36</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>-33.16</v>
+        <v>-29.21</v>
       </c>
       <c r="K64" t="n">
-        <v>-73.86</v>
+        <v>-65.05</v>
       </c>
       <c r="L64" t="n">
-        <v>80.95999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-113.93</v>
+        <v>-113.55</v>
       </c>
       <c r="K65" t="n">
-        <v>-41.97</v>
+        <v>-41.83</v>
       </c>
       <c r="L65" t="n">
-        <v>121.41</v>
+        <v>121.01</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-83.56</v>
+        <v>-84.97</v>
       </c>
       <c r="K66" t="n">
-        <v>52.31</v>
+        <v>53.2</v>
       </c>
       <c r="L66" t="n">
-        <v>98.58</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>130.12</v>
+        <v>129.93</v>
       </c>
       <c r="K67" t="n">
-        <v>98.8</v>
+        <v>98.66</v>
       </c>
       <c r="L67" t="n">
-        <v>163.38</v>
+        <v>163.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-98.94</v>
+        <v>-100.99</v>
       </c>
       <c r="K68" t="n">
-        <v>126.05</v>
+        <v>128.67</v>
       </c>
       <c r="L68" t="n">
-        <v>160.25</v>
+        <v>163.57</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>197.36</v>
+        <v>202.97</v>
       </c>
       <c r="K69" t="n">
-        <v>48.25</v>
+        <v>49.62</v>
       </c>
       <c r="L69" t="n">
-        <v>203.18</v>
+        <v>208.95</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>-90.33</v>
+        <v>-83.16</v>
       </c>
       <c r="K70" t="n">
-        <v>-107.36</v>
+        <v>-98.84</v>
       </c>
       <c r="L70" t="n">
-        <v>140.31</v>
+        <v>129.17</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>101.06</v>
+        <v>100.69</v>
       </c>
       <c r="K71" t="n">
-        <v>-272.13</v>
+        <v>-271.15</v>
       </c>
       <c r="L71" t="n">
-        <v>290.29</v>
+        <v>289.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-265.46</v>
+        <v>-240.59</v>
       </c>
       <c r="K72" t="n">
-        <v>16.13</v>
+        <v>14.62</v>
       </c>
       <c r="L72" t="n">
-        <v>265.95</v>
+        <v>241.03</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-292.37</v>
+        <v>-271.04</v>
       </c>
       <c r="K73" t="n">
-        <v>51.04</v>
+        <v>47.32</v>
       </c>
       <c r="L73" t="n">
-        <v>296.79</v>
+        <v>275.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>33.02</v>
+        <v>32.82</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.57</v>
+        <v>-51.26</v>
       </c>
       <c r="L74" t="n">
-        <v>61.23</v>
+        <v>60.86</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.17</v>
+        <v>-24.86</v>
       </c>
       <c r="K75" t="n">
-        <v>-55.84</v>
+        <v>-49.29</v>
       </c>
       <c r="L75" t="n">
-        <v>62.54</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>70.87</v>
+        <v>71.55</v>
       </c>
       <c r="K76" t="n">
-        <v>32.27</v>
+        <v>32.58</v>
       </c>
       <c r="L76" t="n">
-        <v>77.87</v>
+        <v>78.62</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>34.64</v>
+        <v>33.68</v>
       </c>
       <c r="K77" t="n">
-        <v>113.85</v>
+        <v>110.66</v>
       </c>
       <c r="L77" t="n">
-        <v>119</v>
+        <v>115.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.96</v>
+        <v>-3.77</v>
       </c>
       <c r="K78" t="n">
-        <v>108.16</v>
+        <v>102.95</v>
       </c>
       <c r="L78" t="n">
-        <v>108.23</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-103.73</v>
+        <v>-105.37</v>
       </c>
       <c r="K79" t="n">
-        <v>-31.72</v>
+        <v>-32.22</v>
       </c>
       <c r="L79" t="n">
-        <v>108.47</v>
+        <v>110.18</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-75.76000000000001</v>
+        <v>-72.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-92.18000000000001</v>
+        <v>-88.17</v>
       </c>
       <c r="L80" t="n">
-        <v>119.31</v>
+        <v>114.13</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-83.73</v>
+        <v>-83.48</v>
       </c>
       <c r="K81" t="n">
-        <v>-103.39</v>
+        <v>-103.07</v>
       </c>
       <c r="L81" t="n">
-        <v>133.04</v>
+        <v>132.64</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-79.56999999999999</v>
+        <v>-74.34</v>
       </c>
       <c r="K82" t="n">
-        <v>98.84</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>126.89</v>
+        <v>118.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-70.28</v>
+        <v>-63.03</v>
       </c>
       <c r="K83" t="n">
-        <v>178.57</v>
+        <v>160.14</v>
       </c>
       <c r="L83" t="n">
-        <v>191.91</v>
+        <v>172.1</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>97.01000000000001</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>114.26</v>
+        <v>115.19</v>
       </c>
       <c r="L84" t="n">
-        <v>149.89</v>
+        <v>151.1</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-104.07</v>
+        <v>-104.21</v>
       </c>
       <c r="K85" t="n">
-        <v>69.98</v>
+        <v>70.08</v>
       </c>
       <c r="L85" t="n">
-        <v>125.41</v>
+        <v>125.58</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-204.2</v>
+        <v>-207.74</v>
       </c>
       <c r="K86" t="n">
-        <v>-46.2</v>
+        <v>-47</v>
       </c>
       <c r="L86" t="n">
-        <v>209.37</v>
+        <v>212.99</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>183.14</v>
+        <v>175.06</v>
       </c>
       <c r="K87" t="n">
-        <v>389.74</v>
+        <v>372.54</v>
       </c>
       <c r="L87" t="n">
-        <v>430.63</v>
+        <v>411.62</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-180.02</v>
+        <v>-179.38</v>
       </c>
       <c r="K88" t="n">
-        <v>-364.05</v>
+        <v>-362.76</v>
       </c>
       <c r="L88" t="n">
-        <v>406.13</v>
+        <v>404.68</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.25</v>
+        <v>4.51</v>
       </c>
       <c r="F14" t="n">
-        <v>12.25</v>
+        <v>15.84</v>
       </c>
       <c r="G14" t="n">
-        <v>301.5</v>
+        <v>312.3</v>
       </c>
       <c r="H14" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-59.53</v>
+        <v>65.41</v>
       </c>
       <c r="K14" t="n">
-        <v>-44.03</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>74.04000000000001</v>
+        <v>101.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:28:56</t>
+          <t>04:28:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8</v>
+        <v>4.12</v>
       </c>
       <c r="F15" t="n">
-        <v>14.38</v>
+        <v>8.67</v>
       </c>
       <c r="G15" t="n">
-        <v>302.9</v>
+        <v>294.7</v>
       </c>
       <c r="H15" t="n">
-        <v>26.4</v>
+        <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>63.23</v>
+        <v>20.81</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.26</v>
+        <v>66.13</v>
       </c>
       <c r="L15" t="n">
-        <v>65.54000000000001</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:30:35</t>
+          <t>04:30:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.03</v>
+        <v>3.35</v>
       </c>
       <c r="F16" t="n">
-        <v>14.57</v>
+        <v>9.41</v>
       </c>
       <c r="G16" t="n">
-        <v>301</v>
+        <v>282.4</v>
       </c>
       <c r="H16" t="n">
-        <v>33.7</v>
+        <v>22.5</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>0.34</v>
+        <v>-53.67</v>
       </c>
       <c r="K16" t="n">
-        <v>25.7</v>
+        <v>-26.06</v>
       </c>
       <c r="L16" t="n">
-        <v>25.7</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:35:01</t>
+          <t>04:36:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.77</v>
+        <v>4.05</v>
       </c>
       <c r="F17" t="n">
-        <v>10.96</v>
+        <v>12.14</v>
       </c>
       <c r="G17" t="n">
-        <v>302.6</v>
+        <v>313.9</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>42.5</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.62</v>
+        <v>110.51</v>
       </c>
       <c r="K17" t="n">
-        <v>-43.88</v>
+        <v>76.89</v>
       </c>
       <c r="L17" t="n">
-        <v>71.63</v>
+        <v>134.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:36:49</t>
+          <t>04:37:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.29</v>
+        <v>5.16</v>
       </c>
       <c r="F18" t="n">
-        <v>13.1</v>
+        <v>14.1</v>
       </c>
       <c r="G18" t="n">
-        <v>307.3</v>
+        <v>304.7</v>
       </c>
       <c r="H18" t="n">
-        <v>33.9</v>
+        <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>78.13</v>
+        <v>-66.98</v>
       </c>
       <c r="K18" t="n">
-        <v>-29.41</v>
+        <v>109.31</v>
       </c>
       <c r="L18" t="n">
-        <v>83.48</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:38:55</t>
+          <t>04:40:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.81</v>
+        <v>3.72</v>
       </c>
       <c r="F19" t="n">
-        <v>10.72</v>
+        <v>7.21</v>
       </c>
       <c r="G19" t="n">
-        <v>297.3</v>
+        <v>298.5</v>
       </c>
       <c r="H19" t="n">
-        <v>27.1</v>
+        <v>31.9</v>
       </c>
       <c r="I19" t="n">
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-61.26</v>
+        <v>-13.9</v>
       </c>
       <c r="K19" t="n">
-        <v>37.76</v>
+        <v>72.25</v>
       </c>
       <c r="L19" t="n">
-        <v>71.95999999999999</v>
+        <v>73.56999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:42:44</t>
+          <t>04:44:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
       <c r="F20" t="n">
-        <v>10.96</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>306.6</v>
+        <v>307.8</v>
       </c>
       <c r="H20" t="n">
-        <v>25.4</v>
+        <v>35.9</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J20" t="n">
-        <v>-22.67</v>
+        <v>165.56</v>
       </c>
       <c r="K20" t="n">
-        <v>-96.64</v>
+        <v>75.5</v>
       </c>
       <c r="L20" t="n">
-        <v>99.26000000000001</v>
+        <v>181.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:44:14</t>
+          <t>04:46:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.24</v>
+        <v>4.21</v>
       </c>
       <c r="F21" t="n">
-        <v>15.7</v>
+        <v>10.9</v>
       </c>
       <c r="G21" t="n">
-        <v>317.4</v>
+        <v>310.9</v>
       </c>
       <c r="H21" t="n">
-        <v>25.5</v>
+        <v>36.6</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>7.49</v>
+        <v>3.24</v>
       </c>
       <c r="K21" t="n">
-        <v>-120.88</v>
+        <v>-23</v>
       </c>
       <c r="L21" t="n">
-        <v>121.11</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:45:01</t>
+          <t>04:48:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.01</v>
+        <v>3.47</v>
       </c>
       <c r="F22" t="n">
-        <v>9.539999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G22" t="n">
-        <v>281.6</v>
+        <v>309.9</v>
       </c>
       <c r="H22" t="n">
-        <v>28.2</v>
+        <v>29.6</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-29.93</v>
+        <v>-45.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-118.05</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>121.78</v>
+        <v>106.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:49:46</t>
+          <t>04:53:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.9</v>
+        <v>4.44</v>
       </c>
       <c r="F23" t="n">
-        <v>13.45</v>
+        <v>12.5</v>
       </c>
       <c r="G23" t="n">
-        <v>312.6</v>
+        <v>283.2</v>
       </c>
       <c r="H23" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>55.88</v>
+        <v>34.08</v>
       </c>
       <c r="K23" t="n">
-        <v>168.29</v>
+        <v>207.63</v>
       </c>
       <c r="L23" t="n">
-        <v>177.33</v>
+        <v>210.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:51:34</t>
+          <t>04:55:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4.46</v>
       </c>
       <c r="F24" t="n">
-        <v>16.21</v>
+        <v>12.57</v>
       </c>
       <c r="G24" t="n">
-        <v>303.3</v>
+        <v>308.1</v>
       </c>
       <c r="H24" t="n">
-        <v>31.3</v>
+        <v>20.7</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-256.65</v>
+        <v>-231.13</v>
       </c>
       <c r="K24" t="n">
-        <v>60.92</v>
+        <v>-141.71</v>
       </c>
       <c r="L24" t="n">
-        <v>263.78</v>
+        <v>271.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:52:57</t>
+          <t>04:57:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.53</v>
+        <v>4.56</v>
       </c>
       <c r="F25" t="n">
-        <v>10.37</v>
+        <v>13.73</v>
       </c>
       <c r="G25" t="n">
-        <v>303.2</v>
+        <v>297.6</v>
       </c>
       <c r="H25" t="n">
-        <v>28.1</v>
+        <v>67.3</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-111.28</v>
+        <v>-230.8</v>
       </c>
       <c r="K25" t="n">
-        <v>101.01</v>
+        <v>86.08</v>
       </c>
       <c r="L25" t="n">
-        <v>150.29</v>
+        <v>246.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>04:57:27</t>
+          <t>05:02:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.21</v>
+        <v>3.99</v>
       </c>
       <c r="F26" t="n">
-        <v>9.82</v>
+        <v>11.38</v>
       </c>
       <c r="G26" t="n">
-        <v>310.9</v>
+        <v>310.8</v>
       </c>
       <c r="H26" t="n">
-        <v>27.4</v>
+        <v>18.9</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>-217.23</v>
+        <v>-25.64</v>
       </c>
       <c r="K26" t="n">
-        <v>-56.04</v>
+        <v>231.91</v>
       </c>
       <c r="L26" t="n">
-        <v>224.34</v>
+        <v>233.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04:58:21</t>
+          <t>05:04:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.81</v>
+        <v>4.9</v>
       </c>
       <c r="F27" t="n">
-        <v>8.31</v>
+        <v>13.3</v>
       </c>
       <c r="G27" t="n">
-        <v>295.8</v>
+        <v>302.1</v>
       </c>
       <c r="H27" t="n">
-        <v>30.6</v>
+        <v>26.3</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-78.19</v>
+        <v>-263.48</v>
       </c>
       <c r="K27" t="n">
-        <v>165.53</v>
+        <v>-402.69</v>
       </c>
       <c r="L27" t="n">
-        <v>183.07</v>
+        <v>481.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>04:59:21</t>
+          <t>05:05:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.98</v>
+        <v>4.16</v>
       </c>
       <c r="F28" t="n">
-        <v>9.81</v>
+        <v>11.9</v>
       </c>
       <c r="G28" t="n">
-        <v>306.3</v>
+        <v>308.5</v>
       </c>
       <c r="H28" t="n">
-        <v>23.5</v>
+        <v>44.2</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J28" t="n">
-        <v>-40.39</v>
+        <v>-259.27</v>
       </c>
       <c r="K28" t="n">
-        <v>228.17</v>
+        <v>-144.51</v>
       </c>
       <c r="L28" t="n">
-        <v>231.72</v>
+        <v>296.82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:08:19</t>
+          <t>05:16:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.89</v>
+        <v>4.47</v>
       </c>
       <c r="F29" t="n">
-        <v>15.19</v>
+        <v>12.53</v>
       </c>
       <c r="G29" t="n">
-        <v>304.7</v>
+        <v>301.6</v>
       </c>
       <c r="H29" t="n">
-        <v>26.3</v>
+        <v>45.1</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>77.16</v>
+        <v>-69.42</v>
       </c>
       <c r="K29" t="n">
-        <v>30.12</v>
+        <v>-79.7</v>
       </c>
       <c r="L29" t="n">
-        <v>82.83</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:10:12</t>
+          <t>05:17:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.91</v>
+        <v>3.47</v>
       </c>
       <c r="F30" t="n">
-        <v>8.130000000000001</v>
+        <v>7.36</v>
       </c>
       <c r="G30" t="n">
-        <v>298.2</v>
+        <v>304.8</v>
       </c>
       <c r="H30" t="n">
-        <v>26.8</v>
+        <v>24.8</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>32.71</v>
+        <v>23.14</v>
       </c>
       <c r="K30" t="n">
-        <v>58.09</v>
+        <v>54.18</v>
       </c>
       <c r="L30" t="n">
-        <v>66.67</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:11:45</t>
+          <t>05:20:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
       <c r="F31" t="n">
-        <v>13.11</v>
+        <v>15.87</v>
       </c>
       <c r="G31" t="n">
-        <v>296.9</v>
+        <v>287.4</v>
       </c>
       <c r="H31" t="n">
-        <v>23.8</v>
+        <v>61.5</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>31.38</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>5.41</v>
+        <v>-24.15</v>
       </c>
       <c r="L31" t="n">
-        <v>31.84</v>
+        <v>84.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:16:40</t>
+          <t>05:23:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="F32" t="n">
-        <v>13.94</v>
+        <v>12.34</v>
       </c>
       <c r="G32" t="n">
-        <v>322.5</v>
+        <v>313.7</v>
       </c>
       <c r="H32" t="n">
-        <v>28.1</v>
+        <v>15.1</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>9.16</v>
+        <v>92.63</v>
       </c>
       <c r="K32" t="n">
-        <v>104.28</v>
+        <v>48.81</v>
       </c>
       <c r="L32" t="n">
-        <v>104.68</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:17:47</t>
+          <t>05:24:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.42</v>
+        <v>4.86</v>
       </c>
       <c r="F33" t="n">
-        <v>10.95</v>
+        <v>12.38</v>
       </c>
       <c r="G33" t="n">
-        <v>305.5</v>
+        <v>291</v>
       </c>
       <c r="H33" t="n">
-        <v>23.5</v>
+        <v>79.5</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-17.82</v>
+        <v>31.71</v>
       </c>
       <c r="K33" t="n">
-        <v>-86.79000000000001</v>
+        <v>-149.05</v>
       </c>
       <c r="L33" t="n">
-        <v>88.59999999999999</v>
+        <v>152.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:19:37</t>
+          <t>05:26:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.94</v>
+        <v>4.52</v>
       </c>
       <c r="F34" t="n">
-        <v>12.05</v>
+        <v>12.27</v>
       </c>
       <c r="G34" t="n">
-        <v>298.1</v>
+        <v>291.6</v>
       </c>
       <c r="H34" t="n">
-        <v>33.1</v>
+        <v>50.2</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>49.66</v>
+        <v>75.7</v>
       </c>
       <c r="K34" t="n">
-        <v>36.08</v>
+        <v>-99.26000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>61.39</v>
+        <v>124.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:24:08</t>
+          <t>05:30:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.36</v>
+        <v>5.08</v>
       </c>
       <c r="F35" t="n">
-        <v>9.539999999999999</v>
+        <v>14.18</v>
       </c>
       <c r="G35" t="n">
-        <v>289.2</v>
+        <v>298.1</v>
       </c>
       <c r="H35" t="n">
-        <v>27.7</v>
+        <v>57.6</v>
       </c>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-96.58</v>
+        <v>-60.54</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.49</v>
+        <v>174.29</v>
       </c>
       <c r="L35" t="n">
-        <v>97.51000000000001</v>
+        <v>184.51</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:25:35</t>
+          <t>05:31:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.43</v>
+        <v>4.28</v>
       </c>
       <c r="F36" t="n">
-        <v>11.34</v>
+        <v>10.83</v>
       </c>
       <c r="G36" t="n">
-        <v>309.7</v>
+        <v>289.3</v>
       </c>
       <c r="H36" t="n">
-        <v>33.9</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-104.11</v>
+        <v>-50.46</v>
       </c>
       <c r="K36" t="n">
-        <v>-100.25</v>
+        <v>162.41</v>
       </c>
       <c r="L36" t="n">
-        <v>144.53</v>
+        <v>170.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:26:40</t>
+          <t>05:33:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.49</v>
+        <v>3.89</v>
       </c>
       <c r="F37" t="n">
-        <v>15.19</v>
+        <v>10.23</v>
       </c>
       <c r="G37" t="n">
-        <v>304</v>
+        <v>299.2</v>
       </c>
       <c r="H37" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>-26.41</v>
+        <v>37.61</v>
       </c>
       <c r="K37" t="n">
-        <v>136.59</v>
+        <v>-136.59</v>
       </c>
       <c r="L37" t="n">
-        <v>139.12</v>
+        <v>141.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:31:48</t>
+          <t>05:37:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.44</v>
+        <v>4.15</v>
       </c>
       <c r="F38" t="n">
-        <v>13.28</v>
+        <v>11.98</v>
       </c>
       <c r="G38" t="n">
-        <v>305.2</v>
+        <v>295.3</v>
       </c>
       <c r="H38" t="n">
-        <v>21.3</v>
+        <v>79.2</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>74.38</v>
+        <v>162.99</v>
       </c>
       <c r="K38" t="n">
-        <v>109.91</v>
+        <v>-100.63</v>
       </c>
       <c r="L38" t="n">
-        <v>132.71</v>
+        <v>191.55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:33:51</t>
+          <t>05:39:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="F39" t="n">
-        <v>11.98</v>
+        <v>11.45</v>
       </c>
       <c r="G39" t="n">
-        <v>305.8</v>
+        <v>299.3</v>
       </c>
       <c r="H39" t="n">
-        <v>26.9</v>
+        <v>17.4</v>
       </c>
       <c r="I39" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>108.88</v>
+        <v>-64.58</v>
       </c>
       <c r="K39" t="n">
-        <v>185.27</v>
+        <v>-261.06</v>
       </c>
       <c r="L39" t="n">
-        <v>214.9</v>
+        <v>268.93</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:35:46</t>
+          <t>05:40:44</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="F40" t="n">
-        <v>11.19</v>
+        <v>12.41</v>
       </c>
       <c r="G40" t="n">
-        <v>299.5</v>
+        <v>313.1</v>
       </c>
       <c r="H40" t="n">
-        <v>22.4</v>
+        <v>32.2</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-70.58</v>
+        <v>187.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-186.68</v>
+        <v>181.35</v>
       </c>
       <c r="L40" t="n">
-        <v>199.58</v>
+        <v>260.57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:39:59</t>
+          <t>05:44:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="F41" t="n">
-        <v>16.21</v>
+        <v>14.79</v>
       </c>
       <c r="G41" t="n">
-        <v>295.4</v>
+        <v>294.2</v>
       </c>
       <c r="H41" t="n">
-        <v>29</v>
+        <v>20.2</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>315.03</v>
+        <v>325.7</v>
       </c>
       <c r="K41" t="n">
-        <v>-32.58</v>
+        <v>-266.63</v>
       </c>
       <c r="L41" t="n">
-        <v>316.71</v>
+        <v>420.92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:42:14</t>
+          <t>05:46:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.22</v>
+        <v>5.28</v>
       </c>
       <c r="F42" t="n">
-        <v>14.47</v>
+        <v>15.98</v>
       </c>
       <c r="G42" t="n">
-        <v>300</v>
+        <v>305.9</v>
       </c>
       <c r="H42" t="n">
-        <v>24.7</v>
+        <v>52.7</v>
       </c>
       <c r="I42" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J42" t="n">
-        <v>-45.1</v>
+        <v>-335.58</v>
       </c>
       <c r="K42" t="n">
-        <v>212.48</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>217.21</v>
+        <v>346.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:44:53</t>
+          <t>05:47:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.07</v>
+        <v>5.15</v>
       </c>
       <c r="F43" t="n">
-        <v>12.11</v>
+        <v>16.21</v>
       </c>
       <c r="G43" t="n">
-        <v>301.3</v>
+        <v>303.8</v>
       </c>
       <c r="H43" t="n">
-        <v>29.4</v>
+        <v>73.3</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-102.67</v>
+        <v>-426.92</v>
       </c>
       <c r="K43" t="n">
-        <v>-240.06</v>
+        <v>50.56</v>
       </c>
       <c r="L43" t="n">
-        <v>261.09</v>
+        <v>429.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:55:56</t>
+          <t>05:54:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.37</v>
+        <v>4.21</v>
       </c>
       <c r="F44" t="n">
-        <v>9.99</v>
+        <v>11.69</v>
       </c>
       <c r="G44" t="n">
-        <v>285.6</v>
+        <v>286.4</v>
       </c>
       <c r="H44" t="n">
-        <v>27.8</v>
+        <v>48.6</v>
       </c>
       <c r="I44" t="n">
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>25.38</v>
+        <v>76.41</v>
       </c>
       <c r="K44" t="n">
-        <v>15.02</v>
+        <v>0.16</v>
       </c>
       <c r="L44" t="n">
-        <v>29.49</v>
+        <v>76.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05:56:58</t>
+          <t>05:55:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.3</v>
+        <v>5.77</v>
       </c>
       <c r="F45" t="n">
-        <v>11.26</v>
+        <v>16.21</v>
       </c>
       <c r="G45" t="n">
-        <v>294.9</v>
+        <v>289.5</v>
       </c>
       <c r="H45" t="n">
-        <v>28.3</v>
+        <v>17.1</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>35.67</v>
+        <v>-29.25</v>
       </c>
       <c r="K45" t="n">
-        <v>-24.13</v>
+        <v>170.22</v>
       </c>
       <c r="L45" t="n">
-        <v>43.07</v>
+        <v>172.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05:59:02</t>
+          <t>05:58:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.58</v>
+        <v>4.43</v>
       </c>
       <c r="F46" t="n">
-        <v>15.98</v>
+        <v>11.53</v>
       </c>
       <c r="G46" t="n">
-        <v>298.7</v>
+        <v>303.7</v>
       </c>
       <c r="H46" t="n">
-        <v>27</v>
+        <v>50.1</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>37.95</v>
+        <v>-3.79</v>
       </c>
       <c r="K46" t="n">
-        <v>-39.71</v>
+        <v>-107.56</v>
       </c>
       <c r="L46" t="n">
-        <v>54.93</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:04:41</t>
+          <t>06:02:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="F47" t="n">
-        <v>10.83</v>
+        <v>10.49</v>
       </c>
       <c r="G47" t="n">
-        <v>309.1</v>
+        <v>311.3</v>
       </c>
       <c r="H47" t="n">
-        <v>26.2</v>
+        <v>60.2</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>76.12</v>
+        <v>-100.98</v>
       </c>
       <c r="K47" t="n">
-        <v>42.14</v>
+        <v>4.02</v>
       </c>
       <c r="L47" t="n">
-        <v>87.01000000000001</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:05:52</t>
+          <t>06:03:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.75</v>
+        <v>4.97</v>
       </c>
       <c r="F48" t="n">
-        <v>13.91</v>
+        <v>16.21</v>
       </c>
       <c r="G48" t="n">
-        <v>302</v>
+        <v>301.9</v>
       </c>
       <c r="H48" t="n">
-        <v>28.4</v>
+        <v>49.4</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.16</v>
+        <v>-140.85</v>
       </c>
       <c r="K48" t="n">
-        <v>-54.63</v>
+        <v>-11.36</v>
       </c>
       <c r="L48" t="n">
-        <v>55.39</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:06:54</t>
+          <t>06:05:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.79</v>
+        <v>4.27</v>
       </c>
       <c r="F49" t="n">
-        <v>15.18</v>
+        <v>13.37</v>
       </c>
       <c r="G49" t="n">
-        <v>306.6</v>
+        <v>296</v>
       </c>
       <c r="H49" t="n">
-        <v>27.3</v>
+        <v>35.4</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>9.289999999999999</v>
+        <v>-59.89</v>
       </c>
       <c r="K49" t="n">
-        <v>-54.37</v>
+        <v>-38.69</v>
       </c>
       <c r="L49" t="n">
-        <v>55.16</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:10:07</t>
+          <t>06:11:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.83</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>16.21</v>
+        <v>10.89</v>
       </c>
       <c r="G50" t="n">
-        <v>312.5</v>
+        <v>300.2</v>
       </c>
       <c r="H50" t="n">
-        <v>22.6</v>
+        <v>43.1</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-107.99</v>
+        <v>-155.45</v>
       </c>
       <c r="K50" t="n">
-        <v>59.19</v>
+        <v>51.33</v>
       </c>
       <c r="L50" t="n">
-        <v>123.15</v>
+        <v>163.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:12:02</t>
+          <t>06:13:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.84</v>
+        <v>4.18</v>
       </c>
       <c r="F51" t="n">
-        <v>14.43</v>
+        <v>12.41</v>
       </c>
       <c r="G51" t="n">
-        <v>304.8</v>
+        <v>311.8</v>
       </c>
       <c r="H51" t="n">
-        <v>29</v>
+        <v>58.5</v>
       </c>
       <c r="I51" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>94.5</v>
+        <v>132.47</v>
       </c>
       <c r="K51" t="n">
-        <v>25.17</v>
+        <v>105.63</v>
       </c>
       <c r="L51" t="n">
-        <v>97.79000000000001</v>
+        <v>169.43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:13:31</t>
+          <t>06:14:10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.18</v>
+        <v>4.72</v>
       </c>
       <c r="F52" t="n">
-        <v>13.81</v>
+        <v>14.84</v>
       </c>
       <c r="G52" t="n">
-        <v>287.9</v>
+        <v>301</v>
       </c>
       <c r="H52" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I52" t="n">
         <v>21</v>
       </c>
-      <c r="I52" t="n">
-        <v>28</v>
-      </c>
       <c r="J52" t="n">
-        <v>89.76000000000001</v>
+        <v>221.77</v>
       </c>
       <c r="K52" t="n">
-        <v>-83.48</v>
+        <v>-68.39</v>
       </c>
       <c r="L52" t="n">
-        <v>122.59</v>
+        <v>232.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:18:58</t>
+          <t>06:19:21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.61</v>
+        <v>4.36</v>
       </c>
       <c r="F53" t="n">
-        <v>13.29</v>
+        <v>12.22</v>
       </c>
       <c r="G53" t="n">
-        <v>293.2</v>
+        <v>310.9</v>
       </c>
       <c r="H53" t="n">
-        <v>22.9</v>
+        <v>65.8</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-80.02</v>
+        <v>-319.01</v>
       </c>
       <c r="K53" t="n">
-        <v>-151.04</v>
+        <v>-6.48</v>
       </c>
       <c r="L53" t="n">
-        <v>170.92</v>
+        <v>319.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:19:58</t>
+          <t>06:20:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.93</v>
+        <v>4.23</v>
       </c>
       <c r="F54" t="n">
-        <v>13.96</v>
+        <v>10.64</v>
       </c>
       <c r="G54" t="n">
-        <v>301.1</v>
+        <v>308.9</v>
       </c>
       <c r="H54" t="n">
-        <v>29.2</v>
+        <v>44.8</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-158.93</v>
+        <v>-177.36</v>
       </c>
       <c r="K54" t="n">
-        <v>-148.32</v>
+        <v>-178.17</v>
       </c>
       <c r="L54" t="n">
-        <v>217.39</v>
+        <v>251.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:22:05</t>
+          <t>06:21:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.44</v>
+        <v>4.74</v>
       </c>
       <c r="F55" t="n">
-        <v>11.03</v>
+        <v>14.83</v>
       </c>
       <c r="G55" t="n">
-        <v>296</v>
+        <v>295.4</v>
       </c>
       <c r="H55" t="n">
-        <v>28.8</v>
+        <v>56.6</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>105.59</v>
+        <v>-15.85</v>
       </c>
       <c r="K55" t="n">
-        <v>-79.55</v>
+        <v>267.77</v>
       </c>
       <c r="L55" t="n">
-        <v>132.21</v>
+        <v>268.24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:26:38</t>
+          <t>06:26:56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.12</v>
+        <v>4.13</v>
       </c>
       <c r="F56" t="n">
-        <v>15.89</v>
+        <v>12.43</v>
       </c>
       <c r="G56" t="n">
-        <v>280.9</v>
+        <v>297.8</v>
       </c>
       <c r="H56" t="n">
-        <v>27.3</v>
+        <v>34.4</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-193.79</v>
+        <v>-129.09</v>
       </c>
       <c r="K56" t="n">
-        <v>164.59</v>
+        <v>320.47</v>
       </c>
       <c r="L56" t="n">
-        <v>254.25</v>
+        <v>345.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:28:46</t>
+          <t>06:28:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.8</v>
+        <v>4.94</v>
       </c>
       <c r="F57" t="n">
-        <v>9.369999999999999</v>
+        <v>16.21</v>
       </c>
       <c r="G57" t="n">
-        <v>308</v>
+        <v>300.3</v>
       </c>
       <c r="H57" t="n">
-        <v>28</v>
+        <v>32.9</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>22.8</v>
+        <v>417.6</v>
       </c>
       <c r="K57" t="n">
-        <v>175.49</v>
+        <v>-135.68</v>
       </c>
       <c r="L57" t="n">
-        <v>176.97</v>
+        <v>439.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:29:40</t>
+          <t>06:30:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.45</v>
+        <v>3.59</v>
       </c>
       <c r="F58" t="n">
-        <v>14.34</v>
+        <v>13.19</v>
       </c>
       <c r="G58" t="n">
-        <v>297.9</v>
+        <v>313</v>
       </c>
       <c r="H58" t="n">
-        <v>23.2</v>
+        <v>77</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>105.86</v>
+        <v>-251.61</v>
       </c>
       <c r="K58" t="n">
-        <v>178.87</v>
+        <v>62.95</v>
       </c>
       <c r="L58" t="n">
-        <v>207.85</v>
+        <v>259.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:38:41</t>
+          <t>06:42:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.95</v>
+        <v>4.66</v>
       </c>
       <c r="F59" t="n">
-        <v>16.21</v>
+        <v>14.82</v>
       </c>
       <c r="G59" t="n">
-        <v>285.8</v>
+        <v>293.6</v>
       </c>
       <c r="H59" t="n">
-        <v>33.1</v>
+        <v>30</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-45.72</v>
+        <v>72.52</v>
       </c>
       <c r="K59" t="n">
-        <v>43.13</v>
+        <v>-120.06</v>
       </c>
       <c r="L59" t="n">
-        <v>62.85</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:39:38</t>
+          <t>06:44:49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.79</v>
+        <v>4.4</v>
       </c>
       <c r="F60" t="n">
-        <v>12.54</v>
+        <v>13.32</v>
       </c>
       <c r="G60" t="n">
-        <v>300.7</v>
+        <v>305.5</v>
       </c>
       <c r="H60" t="n">
-        <v>27.9</v>
+        <v>18.2</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>59.29</v>
+        <v>-61.49</v>
       </c>
       <c r="K60" t="n">
-        <v>11.52</v>
+        <v>43.39</v>
       </c>
       <c r="L60" t="n">
-        <v>60.4</v>
+        <v>75.26000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:40:57</t>
+          <t>06:46:51</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.07</v>
+        <v>4.89</v>
       </c>
       <c r="F61" t="n">
         <v>16.21</v>
       </c>
       <c r="G61" t="n">
-        <v>302.6</v>
+        <v>300.2</v>
       </c>
       <c r="H61" t="n">
-        <v>16.2</v>
+        <v>51.7</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-27.67</v>
+        <v>-85.28</v>
       </c>
       <c r="K61" t="n">
-        <v>-52.78</v>
+        <v>-62.99</v>
       </c>
       <c r="L61" t="n">
-        <v>59.59</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:46:04</t>
+          <t>06:50:40</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.55</v>
+        <v>4.76</v>
       </c>
       <c r="F62" t="n">
-        <v>11.7</v>
+        <v>12.91</v>
       </c>
       <c r="G62" t="n">
-        <v>301.7</v>
+        <v>299.3</v>
       </c>
       <c r="H62" t="n">
-        <v>32.9</v>
+        <v>38.8</v>
       </c>
       <c r="I62" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>48</v>
+        <v>112.87</v>
       </c>
       <c r="K62" t="n">
-        <v>-69.38</v>
+        <v>36.66</v>
       </c>
       <c r="L62" t="n">
-        <v>84.37</v>
+        <v>118.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:48:31</t>
+          <t>06:53:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.43</v>
+        <v>4.17</v>
       </c>
       <c r="F63" t="n">
-        <v>16.21</v>
+        <v>14.97</v>
       </c>
       <c r="G63" t="n">
-        <v>297.4</v>
+        <v>307.1</v>
       </c>
       <c r="H63" t="n">
-        <v>19.5</v>
+        <v>39.6</v>
       </c>
       <c r="I63" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>26.82</v>
+        <v>29.82</v>
       </c>
       <c r="K63" t="n">
-        <v>91.03</v>
+        <v>105.19</v>
       </c>
       <c r="L63" t="n">
-        <v>94.90000000000001</v>
+        <v>109.34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:50:27</t>
+          <t>06:55:22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.32</v>
+        <v>4.45</v>
       </c>
       <c r="F64" t="n">
-        <v>14.53</v>
+        <v>13.95</v>
       </c>
       <c r="G64" t="n">
-        <v>299.2</v>
+        <v>302.8</v>
       </c>
       <c r="H64" t="n">
-        <v>34.6</v>
+        <v>49.5</v>
       </c>
       <c r="I64" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.21</v>
+        <v>-43.6</v>
       </c>
       <c r="K64" t="n">
-        <v>-65.05</v>
+        <v>-109.74</v>
       </c>
       <c r="L64" t="n">
-        <v>71.3</v>
+        <v>118.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06:55:10</t>
+          <t>07:00:09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.96</v>
+        <v>5.31</v>
       </c>
       <c r="F65" t="n">
-        <v>14.39</v>
+        <v>13.26</v>
       </c>
       <c r="G65" t="n">
-        <v>303.8</v>
+        <v>300.9</v>
       </c>
       <c r="H65" t="n">
-        <v>21.7</v>
+        <v>54.1</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-113.55</v>
+        <v>-166.79</v>
       </c>
       <c r="K65" t="n">
-        <v>-41.83</v>
+        <v>181.12</v>
       </c>
       <c r="L65" t="n">
-        <v>121.01</v>
+        <v>246.22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06:56:00</t>
+          <t>07:02:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.88</v>
+        <v>5.58</v>
       </c>
       <c r="F66" t="n">
-        <v>13.44</v>
+        <v>16.21</v>
       </c>
       <c r="G66" t="n">
-        <v>309.8</v>
+        <v>283.2</v>
       </c>
       <c r="H66" t="n">
-        <v>28.5</v>
+        <v>67.7</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-84.97</v>
+        <v>208.16</v>
       </c>
       <c r="K66" t="n">
-        <v>53.2</v>
+        <v>-7.19</v>
       </c>
       <c r="L66" t="n">
-        <v>100.25</v>
+        <v>208.28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06:57:05</t>
+          <t>07:03:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="F67" t="n">
-        <v>12.58</v>
+        <v>13.4</v>
       </c>
       <c r="G67" t="n">
-        <v>302.2</v>
+        <v>288.1</v>
       </c>
       <c r="H67" t="n">
-        <v>23.4</v>
+        <v>20.2</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>129.93</v>
+        <v>-69.14</v>
       </c>
       <c r="K67" t="n">
-        <v>98.66</v>
+        <v>-140.7</v>
       </c>
       <c r="L67" t="n">
-        <v>163.14</v>
+        <v>156.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:01:02</t>
+          <t>07:08:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.19</v>
+        <v>4.98</v>
       </c>
       <c r="F68" t="n">
-        <v>11.91</v>
+        <v>14.71</v>
       </c>
       <c r="G68" t="n">
-        <v>295.9</v>
+        <v>311.5</v>
       </c>
       <c r="H68" t="n">
-        <v>29.2</v>
+        <v>0.2</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-100.99</v>
+        <v>-63.86</v>
       </c>
       <c r="K68" t="n">
-        <v>128.67</v>
+        <v>-285.88</v>
       </c>
       <c r="L68" t="n">
-        <v>163.57</v>
+        <v>292.93</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:02:38</t>
+          <t>07:10:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.86</v>
+        <v>4.32</v>
       </c>
       <c r="F69" t="n">
-        <v>15.24</v>
+        <v>13.06</v>
       </c>
       <c r="G69" t="n">
-        <v>299.9</v>
+        <v>305.1</v>
       </c>
       <c r="H69" t="n">
-        <v>30.2</v>
+        <v>73</v>
       </c>
       <c r="I69" t="n">
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>202.97</v>
+        <v>-199.02</v>
       </c>
       <c r="K69" t="n">
-        <v>49.62</v>
+        <v>130.97</v>
       </c>
       <c r="L69" t="n">
-        <v>208.95</v>
+        <v>238.25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:03:09</t>
+          <t>07:11:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.75</v>
+        <v>4.59</v>
       </c>
       <c r="F70" t="n">
-        <v>14.12</v>
+        <v>13.42</v>
       </c>
       <c r="G70" t="n">
-        <v>303.8</v>
+        <v>301.7</v>
       </c>
       <c r="H70" t="n">
-        <v>26.4</v>
+        <v>69.3</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>-83.16</v>
+        <v>-123.48</v>
       </c>
       <c r="K70" t="n">
-        <v>-98.84</v>
+        <v>261.59</v>
       </c>
       <c r="L70" t="n">
-        <v>129.17</v>
+        <v>289.27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:08:36</t>
+          <t>07:15:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.8</v>
+        <v>4.89</v>
       </c>
       <c r="F71" t="n">
-        <v>14.32</v>
+        <v>12.51</v>
       </c>
       <c r="G71" t="n">
-        <v>303.1</v>
+        <v>286.1</v>
       </c>
       <c r="H71" t="n">
-        <v>30.5</v>
+        <v>28.7</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>100.69</v>
+        <v>253.45</v>
       </c>
       <c r="K71" t="n">
-        <v>-271.15</v>
+        <v>134.87</v>
       </c>
       <c r="L71" t="n">
-        <v>289.24</v>
+        <v>287.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:10:29</t>
+          <t>07:17:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.22</v>
+        <v>4.79</v>
       </c>
       <c r="F72" t="n">
-        <v>11.89</v>
+        <v>16.21</v>
       </c>
       <c r="G72" t="n">
-        <v>298.9</v>
+        <v>304.3</v>
       </c>
       <c r="H72" t="n">
-        <v>28.8</v>
+        <v>26.7</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-240.59</v>
+        <v>53.2</v>
       </c>
       <c r="K72" t="n">
-        <v>14.62</v>
+        <v>356.39</v>
       </c>
       <c r="L72" t="n">
-        <v>241.03</v>
+        <v>360.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:11:34</t>
+          <t>07:18:24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="F73" t="n">
         <v>16.21</v>
       </c>
       <c r="G73" t="n">
-        <v>293.1</v>
+        <v>292.8</v>
       </c>
       <c r="H73" t="n">
-        <v>25.2</v>
+        <v>1.9</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J73" t="n">
-        <v>-271.04</v>
+        <v>-171.13</v>
       </c>
       <c r="K73" t="n">
-        <v>47.32</v>
+        <v>-247.92</v>
       </c>
       <c r="L73" t="n">
-        <v>275.14</v>
+        <v>301.25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:23:06</t>
+          <t>07:29:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="F74" t="n">
-        <v>11.97</v>
+        <v>13.24</v>
       </c>
       <c r="G74" t="n">
-        <v>302.2</v>
+        <v>308.7</v>
       </c>
       <c r="H74" t="n">
-        <v>25.6</v>
+        <v>39.7</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>32.82</v>
+        <v>-99.23999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.26</v>
+        <v>18.32</v>
       </c>
       <c r="L74" t="n">
-        <v>60.86</v>
+        <v>100.92</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:24:48</t>
+          <t>07:30:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.76</v>
+        <v>5.09</v>
       </c>
       <c r="F75" t="n">
-        <v>11.68</v>
+        <v>14.57</v>
       </c>
       <c r="G75" t="n">
-        <v>293.7</v>
+        <v>300.8</v>
       </c>
       <c r="H75" t="n">
-        <v>24.3</v>
+        <v>46.8</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-24.86</v>
+        <v>108.02</v>
       </c>
       <c r="K75" t="n">
-        <v>-49.29</v>
+        <v>30.29</v>
       </c>
       <c r="L75" t="n">
-        <v>55.2</v>
+        <v>112.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:26:58</t>
+          <t>07:32:37</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.41</v>
+        <v>6.36</v>
       </c>
       <c r="F76" t="n">
-        <v>13.21</v>
+        <v>16.21</v>
       </c>
       <c r="G76" t="n">
-        <v>306.8</v>
+        <v>309.4</v>
       </c>
       <c r="H76" t="n">
-        <v>22.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>71.55</v>
+        <v>-28.98</v>
       </c>
       <c r="K76" t="n">
-        <v>32.58</v>
+        <v>136.83</v>
       </c>
       <c r="L76" t="n">
-        <v>78.62</v>
+        <v>139.87</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:29:57</t>
+          <t>07:37:55</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.95</v>
+        <v>3.95</v>
       </c>
       <c r="F77" t="n">
-        <v>16.21</v>
+        <v>10.4</v>
       </c>
       <c r="G77" t="n">
-        <v>305.5</v>
+        <v>307.1</v>
       </c>
       <c r="H77" t="n">
-        <v>33.3</v>
+        <v>16.1</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>33.68</v>
+        <v>56.79</v>
       </c>
       <c r="K77" t="n">
-        <v>110.66</v>
+        <v>-80.06</v>
       </c>
       <c r="L77" t="n">
-        <v>115.67</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:31:14</t>
+          <t>07:38:33</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.72</v>
+        <v>5.21</v>
       </c>
       <c r="F78" t="n">
-        <v>13.83</v>
+        <v>14.39</v>
       </c>
       <c r="G78" t="n">
-        <v>290</v>
+        <v>306.4</v>
       </c>
       <c r="H78" t="n">
-        <v>28.4</v>
+        <v>45</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.77</v>
+        <v>-124.13</v>
       </c>
       <c r="K78" t="n">
-        <v>102.95</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>103.02</v>
+        <v>150.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:33:30</t>
+          <t>07:41:05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.02</v>
+        <v>4.96</v>
       </c>
       <c r="F79" t="n">
-        <v>14.8</v>
+        <v>13.05</v>
       </c>
       <c r="G79" t="n">
-        <v>295.4</v>
+        <v>304.9</v>
       </c>
       <c r="H79" t="n">
-        <v>27.4</v>
+        <v>33</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J79" t="n">
-        <v>-105.37</v>
+        <v>-57.63</v>
       </c>
       <c r="K79" t="n">
-        <v>-32.22</v>
+        <v>-126.07</v>
       </c>
       <c r="L79" t="n">
-        <v>110.18</v>
+        <v>138.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:38:03</t>
+          <t>07:46:28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="F80" t="n">
-        <v>12.24</v>
+        <v>12.37</v>
       </c>
       <c r="G80" t="n">
-        <v>298.5</v>
+        <v>290.8</v>
       </c>
       <c r="H80" t="n">
-        <v>26.2</v>
+        <v>24.3</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>-72.47</v>
+        <v>125.94</v>
       </c>
       <c r="K80" t="n">
-        <v>-88.17</v>
+        <v>105.76</v>
       </c>
       <c r="L80" t="n">
-        <v>114.13</v>
+        <v>164.46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:39:34</t>
+          <t>07:48:12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.89</v>
+        <v>5.27</v>
       </c>
       <c r="F81" t="n">
-        <v>15.43</v>
+        <v>16.21</v>
       </c>
       <c r="G81" t="n">
-        <v>285.7</v>
+        <v>309.1</v>
       </c>
       <c r="H81" t="n">
-        <v>27.6</v>
+        <v>70.3</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-83.48</v>
+        <v>-222.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-103.07</v>
+        <v>21.08</v>
       </c>
       <c r="L81" t="n">
-        <v>132.64</v>
+        <v>223.87</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:41:29</t>
+          <t>07:50:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.52</v>
+        <v>4.01</v>
       </c>
       <c r="F82" t="n">
-        <v>15.86</v>
+        <v>11.29</v>
       </c>
       <c r="G82" t="n">
-        <v>294.7</v>
+        <v>292.1</v>
       </c>
       <c r="H82" t="n">
-        <v>32.5</v>
+        <v>41.1</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>-74.34</v>
+        <v>106.34</v>
       </c>
       <c r="K82" t="n">
-        <v>92.34999999999999</v>
+        <v>107.42</v>
       </c>
       <c r="L82" t="n">
-        <v>118.55</v>
+        <v>151.15</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:46:14</t>
+          <t>07:55:31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.94</v>
+        <v>4.35</v>
       </c>
       <c r="F83" t="n">
-        <v>16.21</v>
+        <v>13.75</v>
       </c>
       <c r="G83" t="n">
-        <v>302.1</v>
+        <v>303.3</v>
       </c>
       <c r="H83" t="n">
-        <v>33.6</v>
+        <v>25.2</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-63.03</v>
+        <v>-268.05</v>
       </c>
       <c r="K83" t="n">
-        <v>160.14</v>
+        <v>-54.48</v>
       </c>
       <c r="L83" t="n">
-        <v>172.1</v>
+        <v>273.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:48:30</t>
+          <t>07:56:31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="F84" t="n">
-        <v>13.5</v>
+        <v>11.54</v>
       </c>
       <c r="G84" t="n">
-        <v>307.4</v>
+        <v>299.3</v>
       </c>
       <c r="H84" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I84" t="n">
         <v>25</v>
       </c>
-      <c r="I84" t="n">
-        <v>24</v>
-      </c>
       <c r="J84" t="n">
-        <v>97.79000000000001</v>
+        <v>-3.78</v>
       </c>
       <c r="K84" t="n">
-        <v>115.19</v>
+        <v>-213.64</v>
       </c>
       <c r="L84" t="n">
-        <v>151.1</v>
+        <v>213.68</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:49:49</t>
+          <t>07:58:39</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.49</v>
+        <v>4.76</v>
       </c>
       <c r="F85" t="n">
-        <v>13.02</v>
+        <v>16.21</v>
       </c>
       <c r="G85" t="n">
-        <v>299.1</v>
+        <v>309.6</v>
       </c>
       <c r="H85" t="n">
-        <v>35.7</v>
+        <v>53.1</v>
       </c>
       <c r="I85" t="n">
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-104.21</v>
+        <v>160.79</v>
       </c>
       <c r="K85" t="n">
-        <v>70.08</v>
+        <v>277.2</v>
       </c>
       <c r="L85" t="n">
-        <v>125.58</v>
+        <v>320.45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07:55:27</t>
+          <t>08:03:14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="F86" t="n">
-        <v>15.72</v>
+        <v>13.71</v>
       </c>
       <c r="G86" t="n">
-        <v>294.9</v>
+        <v>291</v>
       </c>
       <c r="H86" t="n">
-        <v>26.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-207.74</v>
+        <v>252.54</v>
       </c>
       <c r="K86" t="n">
-        <v>-47</v>
+        <v>168.22</v>
       </c>
       <c r="L86" t="n">
-        <v>212.99</v>
+        <v>303.44</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07:57:48</t>
+          <t>08:05:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.51</v>
+        <v>4.69</v>
       </c>
       <c r="F87" t="n">
         <v>16.21</v>
       </c>
       <c r="G87" t="n">
-        <v>297.4</v>
+        <v>303.9</v>
       </c>
       <c r="H87" t="n">
-        <v>28.9</v>
+        <v>47.5</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>175.06</v>
+        <v>0.55</v>
       </c>
       <c r="K87" t="n">
-        <v>372.54</v>
+        <v>-360.71</v>
       </c>
       <c r="L87" t="n">
-        <v>411.62</v>
+        <v>360.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>08:07:28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.81</v>
+        <v>6.06</v>
       </c>
       <c r="F88" t="n">
-        <v>15.19</v>
+        <v>16.21</v>
       </c>
       <c r="G88" t="n">
-        <v>285.2</v>
+        <v>296</v>
       </c>
       <c r="H88" t="n">
-        <v>35</v>
+        <v>60.7</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>-179.38</v>
+        <v>-214.77</v>
       </c>
       <c r="K88" t="n">
-        <v>-362.76</v>
+        <v>434.29</v>
       </c>
       <c r="L88" t="n">
-        <v>404.68</v>
+        <v>484.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.51</v>
+        <v>4.6</v>
       </c>
       <c r="F14" t="n">
-        <v>15.84</v>
+        <v>13.44</v>
       </c>
       <c r="G14" t="n">
-        <v>312.3</v>
+        <v>300.8</v>
       </c>
       <c r="H14" t="n">
-        <v>28.6</v>
+        <v>32.6</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>65.41</v>
+        <v>50.68</v>
       </c>
       <c r="K14" t="n">
-        <v>-77.56999999999999</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>101.47</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:28:53</t>
+          <t>04:29:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.12</v>
+        <v>3.74</v>
       </c>
       <c r="F15" t="n">
-        <v>8.67</v>
+        <v>9.44</v>
       </c>
       <c r="G15" t="n">
-        <v>294.7</v>
+        <v>317.7</v>
       </c>
       <c r="H15" t="n">
-        <v>48.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>20.81</v>
+        <v>26.32</v>
       </c>
       <c r="K15" t="n">
-        <v>66.13</v>
+        <v>50.38</v>
       </c>
       <c r="L15" t="n">
-        <v>69.33</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:30:13</t>
+          <t>04:31:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="F16" t="n">
-        <v>9.41</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>282.4</v>
+        <v>307.4</v>
       </c>
       <c r="H16" t="n">
-        <v>22.5</v>
+        <v>44.3</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.67</v>
+        <v>60.87</v>
       </c>
       <c r="K16" t="n">
-        <v>-26.06</v>
+        <v>-38.41</v>
       </c>
       <c r="L16" t="n">
-        <v>59.67</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:36:22</t>
+          <t>04:35:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.05</v>
+        <v>4.31</v>
       </c>
       <c r="F17" t="n">
-        <v>12.14</v>
+        <v>11.6</v>
       </c>
       <c r="G17" t="n">
-        <v>313.9</v>
+        <v>294.5</v>
       </c>
       <c r="H17" t="n">
-        <v>42.5</v>
+        <v>22.7</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>110.51</v>
+        <v>79.81</v>
       </c>
       <c r="K17" t="n">
-        <v>76.89</v>
+        <v>49.44</v>
       </c>
       <c r="L17" t="n">
-        <v>134.63</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:37:57</t>
+          <t>04:37:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.16</v>
+        <v>4.08</v>
       </c>
       <c r="F18" t="n">
-        <v>14.1</v>
+        <v>10.94</v>
       </c>
       <c r="G18" t="n">
-        <v>304.7</v>
+        <v>307.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3</v>
+        <v>26.8</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.98</v>
+        <v>34.38</v>
       </c>
       <c r="K18" t="n">
-        <v>109.31</v>
+        <v>-90.92</v>
       </c>
       <c r="L18" t="n">
-        <v>128.2</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:40:13</t>
+          <t>04:39:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.72</v>
+        <v>4.97</v>
       </c>
       <c r="F19" t="n">
-        <v>7.21</v>
+        <v>14.62</v>
       </c>
       <c r="G19" t="n">
-        <v>298.5</v>
+        <v>304.5</v>
       </c>
       <c r="H19" t="n">
-        <v>31.9</v>
+        <v>55.9</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.9</v>
+        <v>-132.33</v>
       </c>
       <c r="K19" t="n">
-        <v>72.25</v>
+        <v>-18.17</v>
       </c>
       <c r="L19" t="n">
-        <v>73.56999999999999</v>
+        <v>133.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:44:31</t>
+          <t>04:44:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.33</v>
+        <v>4.99</v>
       </c>
       <c r="F20" t="n">
-        <v>9.550000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="G20" t="n">
-        <v>307.8</v>
+        <v>294</v>
       </c>
       <c r="H20" t="n">
-        <v>35.9</v>
+        <v>80</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>165.56</v>
+        <v>-152.53</v>
       </c>
       <c r="K20" t="n">
-        <v>75.5</v>
+        <v>-126.88</v>
       </c>
       <c r="L20" t="n">
-        <v>181.96</v>
+        <v>198.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:46:39</t>
+          <t>04:45:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.21</v>
+        <v>3.83</v>
       </c>
       <c r="F21" t="n">
-        <v>10.9</v>
+        <v>9.43</v>
       </c>
       <c r="G21" t="n">
-        <v>310.9</v>
+        <v>316.9</v>
       </c>
       <c r="H21" t="n">
-        <v>36.6</v>
+        <v>42.1</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>3.24</v>
+        <v>158.5</v>
       </c>
       <c r="K21" t="n">
-        <v>-23</v>
+        <v>-72.88</v>
       </c>
       <c r="L21" t="n">
-        <v>23.23</v>
+        <v>174.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:48:01</t>
+          <t>04:47:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="F22" t="n">
-        <v>8.6</v>
+        <v>10.79</v>
       </c>
       <c r="G22" t="n">
-        <v>309.9</v>
+        <v>304.7</v>
       </c>
       <c r="H22" t="n">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-45.59</v>
+        <v>-60.17</v>
       </c>
       <c r="K22" t="n">
-        <v>96.51000000000001</v>
+        <v>106.46</v>
       </c>
       <c r="L22" t="n">
-        <v>106.74</v>
+        <v>122.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:53:08</t>
+          <t>04:52:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.44</v>
+        <v>4.19</v>
       </c>
       <c r="F23" t="n">
-        <v>12.5</v>
+        <v>12.59</v>
       </c>
       <c r="G23" t="n">
-        <v>283.2</v>
+        <v>293.9</v>
       </c>
       <c r="H23" t="n">
-        <v>32</v>
+        <v>35.5</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>34.08</v>
+        <v>-109.92</v>
       </c>
       <c r="K23" t="n">
-        <v>207.63</v>
+        <v>-258.05</v>
       </c>
       <c r="L23" t="n">
-        <v>210.41</v>
+        <v>280.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:55:13</t>
+          <t>04:53:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="F24" t="n">
-        <v>12.57</v>
+        <v>13.53</v>
       </c>
       <c r="G24" t="n">
-        <v>308.1</v>
+        <v>292.3</v>
       </c>
       <c r="H24" t="n">
-        <v>20.7</v>
+        <v>72.8</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-231.13</v>
+        <v>335.63</v>
       </c>
       <c r="K24" t="n">
-        <v>-141.71</v>
+        <v>42.6</v>
       </c>
       <c r="L24" t="n">
-        <v>271.11</v>
+        <v>338.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:57:39</t>
+          <t>04:55:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.56</v>
+        <v>4.26</v>
       </c>
       <c r="F25" t="n">
-        <v>13.73</v>
+        <v>13.54</v>
       </c>
       <c r="G25" t="n">
-        <v>297.6</v>
+        <v>310.1</v>
       </c>
       <c r="H25" t="n">
-        <v>67.3</v>
+        <v>55.5</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-230.8</v>
+        <v>26.48</v>
       </c>
       <c r="K25" t="n">
-        <v>86.08</v>
+        <v>-209.31</v>
       </c>
       <c r="L25" t="n">
-        <v>246.33</v>
+        <v>210.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:02:30</t>
+          <t>05:00:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.99</v>
+        <v>4.11</v>
       </c>
       <c r="F26" t="n">
-        <v>11.38</v>
+        <v>10.71</v>
       </c>
       <c r="G26" t="n">
-        <v>310.8</v>
+        <v>288.1</v>
       </c>
       <c r="H26" t="n">
-        <v>18.9</v>
+        <v>44.6</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-25.64</v>
+        <v>-218.73</v>
       </c>
       <c r="K26" t="n">
-        <v>231.91</v>
+        <v>-158.25</v>
       </c>
       <c r="L26" t="n">
-        <v>233.32</v>
+        <v>269.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:04:36</t>
+          <t>05:02:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.9</v>
+        <v>4.36</v>
       </c>
       <c r="F27" t="n">
-        <v>13.3</v>
+        <v>14.01</v>
       </c>
       <c r="G27" t="n">
-        <v>302.1</v>
+        <v>298.8</v>
       </c>
       <c r="H27" t="n">
-        <v>26.3</v>
+        <v>39.4</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-263.48</v>
+        <v>-174.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-402.69</v>
+        <v>289.61</v>
       </c>
       <c r="L27" t="n">
-        <v>481.22</v>
+        <v>338.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:05:37</t>
+          <t>05:04:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.16</v>
+        <v>5.36</v>
       </c>
       <c r="F28" t="n">
-        <v>11.9</v>
+        <v>16.21</v>
       </c>
       <c r="G28" t="n">
-        <v>308.5</v>
+        <v>319.6</v>
       </c>
       <c r="H28" t="n">
-        <v>44.2</v>
+        <v>28.6</v>
       </c>
       <c r="I28" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-259.27</v>
+        <v>-176.92</v>
       </c>
       <c r="K28" t="n">
-        <v>-144.51</v>
+        <v>233.35</v>
       </c>
       <c r="L28" t="n">
-        <v>296.82</v>
+        <v>292.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:16:21</t>
+          <t>05:14:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.47</v>
+        <v>3.79</v>
       </c>
       <c r="F29" t="n">
-        <v>12.53</v>
+        <v>11.91</v>
       </c>
       <c r="G29" t="n">
-        <v>301.6</v>
+        <v>314.5</v>
       </c>
       <c r="H29" t="n">
-        <v>45.1</v>
+        <v>24.1</v>
       </c>
       <c r="I29" t="n">
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>-69.42</v>
+        <v>39.51</v>
       </c>
       <c r="K29" t="n">
-        <v>-79.7</v>
+        <v>52.3</v>
       </c>
       <c r="L29" t="n">
-        <v>105.7</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:56</t>
+          <t>05:16:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.47</v>
+        <v>3.76</v>
       </c>
       <c r="F30" t="n">
-        <v>7.36</v>
+        <v>11.04</v>
       </c>
       <c r="G30" t="n">
-        <v>304.8</v>
+        <v>304.5</v>
       </c>
       <c r="H30" t="n">
-        <v>24.8</v>
+        <v>67.8</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>23.14</v>
+        <v>23.17</v>
       </c>
       <c r="K30" t="n">
-        <v>54.18</v>
+        <v>-63.43</v>
       </c>
       <c r="L30" t="n">
-        <v>58.91</v>
+        <v>67.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:20:00</t>
+          <t>05:17:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.17</v>
+        <v>4.75</v>
       </c>
       <c r="F31" t="n">
-        <v>15.87</v>
+        <v>12.28</v>
       </c>
       <c r="G31" t="n">
-        <v>287.4</v>
+        <v>297.9</v>
       </c>
       <c r="H31" t="n">
-        <v>61.5</v>
+        <v>44.6</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-81.18000000000001</v>
+        <v>-56.96</v>
       </c>
       <c r="K31" t="n">
-        <v>-24.15</v>
+        <v>107.7</v>
       </c>
       <c r="L31" t="n">
-        <v>84.69</v>
+        <v>121.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:23:50</t>
+          <t>05:23:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="F32" t="n">
-        <v>12.34</v>
+        <v>13.84</v>
       </c>
       <c r="G32" t="n">
-        <v>313.7</v>
+        <v>288.9</v>
       </c>
       <c r="H32" t="n">
-        <v>15.1</v>
+        <v>32.3</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>92.63</v>
+        <v>114.69</v>
       </c>
       <c r="K32" t="n">
-        <v>48.81</v>
+        <v>-12.97</v>
       </c>
       <c r="L32" t="n">
-        <v>104.7</v>
+        <v>115.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:24:59</t>
+          <t>05:25:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.86</v>
+        <v>4.02</v>
       </c>
       <c r="F33" t="n">
-        <v>12.38</v>
+        <v>14.53</v>
       </c>
       <c r="G33" t="n">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="H33" t="n">
-        <v>79.5</v>
+        <v>54</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>31.71</v>
+        <v>-93.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-149.05</v>
+        <v>-20.3</v>
       </c>
       <c r="L33" t="n">
-        <v>152.39</v>
+        <v>96.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:26:50</t>
+          <t>05:27:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.52</v>
+        <v>3.88</v>
       </c>
       <c r="F34" t="n">
-        <v>12.27</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>291.6</v>
+        <v>306</v>
       </c>
       <c r="H34" t="n">
-        <v>50.2</v>
+        <v>60.6</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>75.7</v>
+        <v>-74.28</v>
       </c>
       <c r="K34" t="n">
-        <v>-99.26000000000001</v>
+        <v>39.58</v>
       </c>
       <c r="L34" t="n">
-        <v>124.83</v>
+        <v>84.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:30:21</t>
+          <t>05:32:44</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.08</v>
+        <v>4.62</v>
       </c>
       <c r="F35" t="n">
-        <v>14.18</v>
+        <v>10.68</v>
       </c>
       <c r="G35" t="n">
-        <v>298.1</v>
+        <v>297.8</v>
       </c>
       <c r="H35" t="n">
-        <v>57.6</v>
+        <v>58.3</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-60.54</v>
+        <v>-209</v>
       </c>
       <c r="K35" t="n">
-        <v>174.29</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>184.51</v>
+        <v>226.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:31:37</t>
+          <t>05:34:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="F36" t="n">
-        <v>10.83</v>
+        <v>11.05</v>
       </c>
       <c r="G36" t="n">
-        <v>289.3</v>
+        <v>297.2</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>32.6</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-50.46</v>
+        <v>-104.41</v>
       </c>
       <c r="K36" t="n">
-        <v>162.41</v>
+        <v>88.89</v>
       </c>
       <c r="L36" t="n">
-        <v>170.07</v>
+        <v>137.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:33:04</t>
+          <t>05:36:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="F37" t="n">
-        <v>10.23</v>
+        <v>13.84</v>
       </c>
       <c r="G37" t="n">
-        <v>299.2</v>
+        <v>294.7</v>
       </c>
       <c r="H37" t="n">
-        <v>24.7</v>
+        <v>36.6</v>
       </c>
       <c r="I37" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>37.61</v>
+        <v>-75.92</v>
       </c>
       <c r="K37" t="n">
-        <v>-136.59</v>
+        <v>128.82</v>
       </c>
       <c r="L37" t="n">
-        <v>141.67</v>
+        <v>149.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:37:50</t>
+          <t>05:40:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="F38" t="n">
-        <v>11.98</v>
+        <v>12.52</v>
       </c>
       <c r="G38" t="n">
-        <v>295.3</v>
+        <v>302.1</v>
       </c>
       <c r="H38" t="n">
-        <v>79.2</v>
+        <v>37.4</v>
       </c>
       <c r="I38" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>162.99</v>
+        <v>233.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-100.63</v>
+        <v>188.71</v>
       </c>
       <c r="L38" t="n">
-        <v>191.55</v>
+        <v>300.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:39:03</t>
+          <t>05:41:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="F39" t="n">
-        <v>11.45</v>
+        <v>13.22</v>
       </c>
       <c r="G39" t="n">
-        <v>299.3</v>
+        <v>301.2</v>
       </c>
       <c r="H39" t="n">
-        <v>17.4</v>
+        <v>40.8</v>
       </c>
       <c r="I39" t="n">
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-64.58</v>
+        <v>257.08</v>
       </c>
       <c r="K39" t="n">
-        <v>-261.06</v>
+        <v>-49.82</v>
       </c>
       <c r="L39" t="n">
-        <v>268.93</v>
+        <v>261.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:40:44</t>
+          <t>05:43:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.45</v>
+        <v>4.16</v>
       </c>
       <c r="F40" t="n">
-        <v>12.41</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>313.1</v>
+        <v>290.4</v>
       </c>
       <c r="H40" t="n">
-        <v>32.2</v>
+        <v>61.1</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>187.1</v>
+        <v>229.56</v>
       </c>
       <c r="K40" t="n">
-        <v>181.35</v>
+        <v>97.03</v>
       </c>
       <c r="L40" t="n">
-        <v>260.57</v>
+        <v>249.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:44:55</t>
+          <t>05:47:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.79</v>
+        <v>4.03</v>
       </c>
       <c r="F41" t="n">
-        <v>14.79</v>
+        <v>11.14</v>
       </c>
       <c r="G41" t="n">
-        <v>294.2</v>
+        <v>308.7</v>
       </c>
       <c r="H41" t="n">
-        <v>20.2</v>
+        <v>86.8</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>325.7</v>
+        <v>-369.47</v>
       </c>
       <c r="K41" t="n">
-        <v>-266.63</v>
+        <v>67.38</v>
       </c>
       <c r="L41" t="n">
-        <v>420.92</v>
+        <v>375.57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:46:20</t>
+          <t>05:50:03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.28</v>
+        <v>4.63</v>
       </c>
       <c r="F42" t="n">
-        <v>15.98</v>
+        <v>13.83</v>
       </c>
       <c r="G42" t="n">
-        <v>305.9</v>
+        <v>300.2</v>
       </c>
       <c r="H42" t="n">
-        <v>52.7</v>
+        <v>35.3</v>
       </c>
       <c r="I42" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-335.58</v>
+        <v>-278.78</v>
       </c>
       <c r="K42" t="n">
-        <v>88.15000000000001</v>
+        <v>272.83</v>
       </c>
       <c r="L42" t="n">
-        <v>346.97</v>
+        <v>390.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:47:22</t>
+          <t>05:52:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.15</v>
+        <v>4.89</v>
       </c>
       <c r="F43" t="n">
         <v>16.21</v>
       </c>
       <c r="G43" t="n">
-        <v>303.8</v>
+        <v>298.4</v>
       </c>
       <c r="H43" t="n">
-        <v>73.3</v>
+        <v>25.9</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-426.92</v>
+        <v>-246.88</v>
       </c>
       <c r="K43" t="n">
-        <v>50.56</v>
+        <v>248.98</v>
       </c>
       <c r="L43" t="n">
-        <v>429.9</v>
+        <v>350.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:54:50</t>
+          <t>06:03:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.21</v>
+        <v>4.94</v>
       </c>
       <c r="F44" t="n">
-        <v>11.69</v>
+        <v>15.23</v>
       </c>
       <c r="G44" t="n">
-        <v>286.4</v>
+        <v>298.4</v>
       </c>
       <c r="H44" t="n">
-        <v>48.6</v>
+        <v>32.3</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>76.41</v>
+        <v>110.69</v>
       </c>
       <c r="K44" t="n">
-        <v>0.16</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>76.41</v>
+        <v>134.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05:55:55</t>
+          <t>06:04:51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.77</v>
+        <v>5.05</v>
       </c>
       <c r="F45" t="n">
         <v>16.21</v>
       </c>
       <c r="G45" t="n">
-        <v>289.5</v>
+        <v>306.1</v>
       </c>
       <c r="H45" t="n">
-        <v>17.1</v>
+        <v>38.2</v>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.25</v>
+        <v>114.21</v>
       </c>
       <c r="K45" t="n">
-        <v>170.22</v>
+        <v>90.09</v>
       </c>
       <c r="L45" t="n">
-        <v>172.71</v>
+        <v>145.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05:58:19</t>
+          <t>06:05:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1972,31 +1972,31 @@
         <v>4.43</v>
       </c>
       <c r="F46" t="n">
-        <v>11.53</v>
+        <v>14.87</v>
       </c>
       <c r="G46" t="n">
-        <v>303.7</v>
+        <v>281.2</v>
       </c>
       <c r="H46" t="n">
-        <v>50.1</v>
+        <v>26.8</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.79</v>
+        <v>27.16</v>
       </c>
       <c r="K46" t="n">
-        <v>-107.56</v>
+        <v>-79.61</v>
       </c>
       <c r="L46" t="n">
-        <v>107.63</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:02:56</t>
+          <t>06:11:06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="F47" t="n">
-        <v>10.49</v>
+        <v>9.84</v>
       </c>
       <c r="G47" t="n">
-        <v>311.3</v>
+        <v>307.6</v>
       </c>
       <c r="H47" t="n">
-        <v>60.2</v>
+        <v>32.6</v>
       </c>
       <c r="I47" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-100.98</v>
+        <v>57.21</v>
       </c>
       <c r="K47" t="n">
-        <v>4.02</v>
+        <v>72.95</v>
       </c>
       <c r="L47" t="n">
-        <v>101.06</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:03:49</t>
+          <t>06:13:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.97</v>
+        <v>4.84</v>
       </c>
       <c r="F48" t="n">
-        <v>16.21</v>
+        <v>12.18</v>
       </c>
       <c r="G48" t="n">
-        <v>301.9</v>
+        <v>316</v>
       </c>
       <c r="H48" t="n">
-        <v>49.4</v>
+        <v>43.2</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-140.85</v>
+        <v>-30.9</v>
       </c>
       <c r="K48" t="n">
-        <v>-11.36</v>
+        <v>113.96</v>
       </c>
       <c r="L48" t="n">
-        <v>141.31</v>
+        <v>118.07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:05:58</t>
+          <t>06:14:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.27</v>
+        <v>4.37</v>
       </c>
       <c r="F49" t="n">
-        <v>13.37</v>
+        <v>10.02</v>
       </c>
       <c r="G49" t="n">
-        <v>296</v>
+        <v>291.2</v>
       </c>
       <c r="H49" t="n">
-        <v>35.4</v>
+        <v>54.6</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-59.89</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-38.69</v>
+        <v>-77.73999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>71.3</v>
+        <v>108.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:11:30</t>
+          <t>06:19:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>5.32</v>
       </c>
       <c r="F50" t="n">
-        <v>10.89</v>
+        <v>15.29</v>
       </c>
       <c r="G50" t="n">
-        <v>300.2</v>
+        <v>313.1</v>
       </c>
       <c r="H50" t="n">
-        <v>43.1</v>
+        <v>32.2</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-155.45</v>
+        <v>190.35</v>
       </c>
       <c r="K50" t="n">
-        <v>51.33</v>
+        <v>109.46</v>
       </c>
       <c r="L50" t="n">
-        <v>163.7</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:13:00</t>
+          <t>06:21:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.18</v>
+        <v>4.93</v>
       </c>
       <c r="F51" t="n">
-        <v>12.41</v>
+        <v>15.5</v>
       </c>
       <c r="G51" t="n">
-        <v>311.8</v>
+        <v>294.2</v>
       </c>
       <c r="H51" t="n">
-        <v>58.5</v>
+        <v>20.2</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>132.47</v>
+        <v>189.93</v>
       </c>
       <c r="K51" t="n">
-        <v>105.63</v>
+        <v>-134.92</v>
       </c>
       <c r="L51" t="n">
-        <v>169.43</v>
+        <v>232.97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:14:10</t>
+          <t>06:23:57</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.72</v>
+        <v>5.42</v>
       </c>
       <c r="F52" t="n">
-        <v>14.84</v>
+        <v>16.21</v>
       </c>
       <c r="G52" t="n">
-        <v>301</v>
+        <v>305.9</v>
       </c>
       <c r="H52" t="n">
-        <v>15.1</v>
+        <v>52.7</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>221.77</v>
+        <v>-191.61</v>
       </c>
       <c r="K52" t="n">
-        <v>-68.39</v>
+        <v>23.76</v>
       </c>
       <c r="L52" t="n">
-        <v>232.08</v>
+        <v>193.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:19:21</t>
+          <t>06:28:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.36</v>
+        <v>5.31</v>
       </c>
       <c r="F53" t="n">
-        <v>12.22</v>
+        <v>16.21</v>
       </c>
       <c r="G53" t="n">
-        <v>310.9</v>
+        <v>303.8</v>
       </c>
       <c r="H53" t="n">
-        <v>65.8</v>
+        <v>73.3</v>
       </c>
       <c r="I53" t="n">
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-319.01</v>
+        <v>-354.82</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.48</v>
+        <v>-16.24</v>
       </c>
       <c r="L53" t="n">
-        <v>319.07</v>
+        <v>355.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:20:30</t>
+          <t>06:29:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.23</v>
+        <v>4.34</v>
       </c>
       <c r="F54" t="n">
-        <v>10.64</v>
+        <v>12.32</v>
       </c>
       <c r="G54" t="n">
-        <v>308.9</v>
+        <v>286.4</v>
       </c>
       <c r="H54" t="n">
-        <v>44.8</v>
+        <v>48.6</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-177.36</v>
+        <v>248.42</v>
       </c>
       <c r="K54" t="n">
-        <v>-178.17</v>
+        <v>-16.94</v>
       </c>
       <c r="L54" t="n">
-        <v>251.4</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:21:51</t>
+          <t>06:30:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.74</v>
+        <v>5.9</v>
       </c>
       <c r="F55" t="n">
-        <v>14.83</v>
+        <v>16.21</v>
       </c>
       <c r="G55" t="n">
-        <v>295.4</v>
+        <v>289.5</v>
       </c>
       <c r="H55" t="n">
-        <v>56.6</v>
+        <v>17.1</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-15.85</v>
+        <v>58.3</v>
       </c>
       <c r="K55" t="n">
-        <v>267.77</v>
+        <v>414.64</v>
       </c>
       <c r="L55" t="n">
-        <v>268.24</v>
+        <v>418.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:26:56</t>
+          <t>06:34:42</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.13</v>
+        <v>4.57</v>
       </c>
       <c r="F56" t="n">
-        <v>12.43</v>
+        <v>12.21</v>
       </c>
       <c r="G56" t="n">
-        <v>297.8</v>
+        <v>303.7</v>
       </c>
       <c r="H56" t="n">
-        <v>34.4</v>
+        <v>50.1</v>
       </c>
       <c r="I56" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-129.09</v>
+        <v>78.5</v>
       </c>
       <c r="K56" t="n">
-        <v>320.47</v>
+        <v>-404.6</v>
       </c>
       <c r="L56" t="n">
-        <v>345.49</v>
+        <v>412.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:28:22</t>
+          <t>06:36:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.94</v>
+        <v>4.22</v>
       </c>
       <c r="F57" t="n">
-        <v>16.21</v>
+        <v>11.07</v>
       </c>
       <c r="G57" t="n">
-        <v>300.3</v>
+        <v>311.3</v>
       </c>
       <c r="H57" t="n">
-        <v>32.9</v>
+        <v>60.2</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>417.6</v>
+        <v>-302.54</v>
       </c>
       <c r="K57" t="n">
-        <v>-135.68</v>
+        <v>-47.12</v>
       </c>
       <c r="L57" t="n">
-        <v>439.09</v>
+        <v>306.19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:30:46</t>
+          <t>06:37:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.59</v>
+        <v>5.09</v>
       </c>
       <c r="F58" t="n">
-        <v>13.19</v>
+        <v>16.21</v>
       </c>
       <c r="G58" t="n">
-        <v>313</v>
+        <v>301.9</v>
       </c>
       <c r="H58" t="n">
-        <v>77</v>
+        <v>49.4</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-251.61</v>
+        <v>-347.28</v>
       </c>
       <c r="K58" t="n">
-        <v>62.95</v>
+        <v>-103.01</v>
       </c>
       <c r="L58" t="n">
-        <v>259.37</v>
+        <v>362.23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:42:36</t>
+          <t>06:49:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="F59" t="n">
-        <v>14.82</v>
+        <v>14.15</v>
       </c>
       <c r="G59" t="n">
-        <v>293.6</v>
+        <v>296</v>
       </c>
       <c r="H59" t="n">
-        <v>30</v>
+        <v>35.4</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>72.52</v>
+        <v>-21.98</v>
       </c>
       <c r="K59" t="n">
-        <v>-120.06</v>
+        <v>-43.33</v>
       </c>
       <c r="L59" t="n">
-        <v>140.26</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:44:49</t>
+          <t>06:51:27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="F60" t="n">
-        <v>13.32</v>
+        <v>11.6</v>
       </c>
       <c r="G60" t="n">
-        <v>305.5</v>
+        <v>300.2</v>
       </c>
       <c r="H60" t="n">
-        <v>18.2</v>
+        <v>43.1</v>
       </c>
       <c r="I60" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-61.49</v>
+        <v>-86.27</v>
       </c>
       <c r="K60" t="n">
-        <v>43.39</v>
+        <v>22.44</v>
       </c>
       <c r="L60" t="n">
-        <v>75.26000000000001</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:46:51</t>
+          <t>06:53:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="F61" t="n">
-        <v>16.21</v>
+        <v>13.11</v>
       </c>
       <c r="G61" t="n">
-        <v>300.2</v>
+        <v>311.8</v>
       </c>
       <c r="H61" t="n">
-        <v>51.7</v>
+        <v>58.5</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-85.28</v>
+        <v>86.39</v>
       </c>
       <c r="K61" t="n">
-        <v>-62.99</v>
+        <v>37.18</v>
       </c>
       <c r="L61" t="n">
-        <v>106.02</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:50:40</t>
+          <t>06:57:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.76</v>
+        <v>4.88</v>
       </c>
       <c r="F62" t="n">
-        <v>12.91</v>
+        <v>15.65</v>
       </c>
       <c r="G62" t="n">
-        <v>299.3</v>
+        <v>301</v>
       </c>
       <c r="H62" t="n">
-        <v>38.8</v>
+        <v>15.1</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>112.87</v>
+        <v>169.76</v>
       </c>
       <c r="K62" t="n">
-        <v>36.66</v>
+        <v>-64.15000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>118.67</v>
+        <v>181.47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:53:00</t>
+          <t>06:59:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.17</v>
+        <v>4.51</v>
       </c>
       <c r="F63" t="n">
-        <v>14.97</v>
+        <v>12.95</v>
       </c>
       <c r="G63" t="n">
-        <v>307.1</v>
+        <v>310.9</v>
       </c>
       <c r="H63" t="n">
-        <v>39.6</v>
+        <v>65.8</v>
       </c>
       <c r="I63" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>29.82</v>
+        <v>-152.79</v>
       </c>
       <c r="K63" t="n">
-        <v>105.19</v>
+        <v>-36.24</v>
       </c>
       <c r="L63" t="n">
-        <v>109.34</v>
+        <v>157.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:55:22</t>
+          <t>07:00:20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.45</v>
+        <v>4.38</v>
       </c>
       <c r="F64" t="n">
-        <v>13.95</v>
+        <v>11.36</v>
       </c>
       <c r="G64" t="n">
-        <v>302.8</v>
+        <v>308.9</v>
       </c>
       <c r="H64" t="n">
-        <v>49.5</v>
+        <v>44.8</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-43.6</v>
+        <v>-58.13</v>
       </c>
       <c r="K64" t="n">
-        <v>-109.74</v>
+        <v>-105.77</v>
       </c>
       <c r="L64" t="n">
-        <v>118.09</v>
+        <v>120.69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:00:09</t>
+          <t>07:04:11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.31</v>
+        <v>4.9</v>
       </c>
       <c r="F65" t="n">
-        <v>13.26</v>
+        <v>15.63</v>
       </c>
       <c r="G65" t="n">
-        <v>300.9</v>
+        <v>295.4</v>
       </c>
       <c r="H65" t="n">
-        <v>54.1</v>
+        <v>56.6</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-166.79</v>
+        <v>41.38</v>
       </c>
       <c r="K65" t="n">
-        <v>181.12</v>
+        <v>184.85</v>
       </c>
       <c r="L65" t="n">
-        <v>246.22</v>
+        <v>189.42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:02:37</t>
+          <t>07:06:04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.58</v>
+        <v>4.27</v>
       </c>
       <c r="F66" t="n">
-        <v>16.21</v>
+        <v>13.11</v>
       </c>
       <c r="G66" t="n">
-        <v>283.2</v>
+        <v>297.8</v>
       </c>
       <c r="H66" t="n">
-        <v>67.7</v>
+        <v>34.4</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>208.16</v>
+        <v>-33</v>
       </c>
       <c r="K66" t="n">
-        <v>-7.19</v>
+        <v>177.5</v>
       </c>
       <c r="L66" t="n">
-        <v>208.28</v>
+        <v>180.54</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:03:19</t>
+          <t>07:08:08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.59</v>
+        <v>5.08</v>
       </c>
       <c r="F67" t="n">
-        <v>13.4</v>
+        <v>16.21</v>
       </c>
       <c r="G67" t="n">
-        <v>288.1</v>
+        <v>300.3</v>
       </c>
       <c r="H67" t="n">
-        <v>20.2</v>
+        <v>32.9</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-69.14</v>
+        <v>222.46</v>
       </c>
       <c r="K67" t="n">
-        <v>-140.7</v>
+        <v>-86.47</v>
       </c>
       <c r="L67" t="n">
-        <v>156.78</v>
+        <v>238.68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:08:37</t>
+          <t>07:13:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.98</v>
+        <v>3.74</v>
       </c>
       <c r="F68" t="n">
-        <v>14.71</v>
+        <v>13.89</v>
       </c>
       <c r="G68" t="n">
-        <v>311.5</v>
+        <v>313</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2</v>
+        <v>77</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-63.86</v>
+        <v>-231.76</v>
       </c>
       <c r="K68" t="n">
-        <v>-285.88</v>
+        <v>25.1</v>
       </c>
       <c r="L68" t="n">
-        <v>292.93</v>
+        <v>233.11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:10:02</t>
+          <t>07:15:34</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.32</v>
+        <v>4.78</v>
       </c>
       <c r="F69" t="n">
-        <v>13.06</v>
+        <v>15.42</v>
       </c>
       <c r="G69" t="n">
-        <v>305.1</v>
+        <v>293.6</v>
       </c>
       <c r="H69" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-199.02</v>
+        <v>325.77</v>
       </c>
       <c r="K69" t="n">
-        <v>130.97</v>
+        <v>-426.9</v>
       </c>
       <c r="L69" t="n">
-        <v>238.25</v>
+        <v>537</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:11:45</t>
+          <t>07:16:48</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.59</v>
+        <v>4.51</v>
       </c>
       <c r="F70" t="n">
-        <v>13.42</v>
+        <v>13.87</v>
       </c>
       <c r="G70" t="n">
-        <v>301.7</v>
+        <v>305.5</v>
       </c>
       <c r="H70" t="n">
-        <v>69.3</v>
+        <v>18.2</v>
       </c>
       <c r="I70" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-123.48</v>
+        <v>-209.76</v>
       </c>
       <c r="K70" t="n">
-        <v>261.59</v>
+        <v>147.47</v>
       </c>
       <c r="L70" t="n">
-        <v>289.27</v>
+        <v>256.42</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:15:06</t>
+          <t>07:21:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.89</v>
+        <v>5.01</v>
       </c>
       <c r="F71" t="n">
-        <v>12.51</v>
+        <v>16.21</v>
       </c>
       <c r="G71" t="n">
-        <v>286.1</v>
+        <v>300.2</v>
       </c>
       <c r="H71" t="n">
-        <v>28.7</v>
+        <v>51.7</v>
       </c>
       <c r="I71" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>253.45</v>
+        <v>-249.52</v>
       </c>
       <c r="K71" t="n">
-        <v>134.87</v>
+        <v>-335.81</v>
       </c>
       <c r="L71" t="n">
-        <v>287.1</v>
+        <v>418.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:17:22</t>
+          <t>07:21:55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.79</v>
+        <v>4.87</v>
       </c>
       <c r="F72" t="n">
-        <v>16.21</v>
+        <v>13.48</v>
       </c>
       <c r="G72" t="n">
-        <v>304.3</v>
+        <v>299.3</v>
       </c>
       <c r="H72" t="n">
-        <v>26.7</v>
+        <v>38.8</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>53.2</v>
+        <v>444.35</v>
       </c>
       <c r="K72" t="n">
-        <v>356.39</v>
+        <v>43.23</v>
       </c>
       <c r="L72" t="n">
-        <v>360.34</v>
+        <v>446.45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:18:24</t>
+          <t>07:24:20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.44</v>
+        <v>4.28</v>
       </c>
       <c r="F73" t="n">
-        <v>16.21</v>
+        <v>15.5</v>
       </c>
       <c r="G73" t="n">
-        <v>292.8</v>
+        <v>307.1</v>
       </c>
       <c r="H73" t="n">
-        <v>1.9</v>
+        <v>39.6</v>
       </c>
       <c r="I73" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-171.13</v>
+        <v>187.52</v>
       </c>
       <c r="K73" t="n">
-        <v>-247.92</v>
+        <v>306.45</v>
       </c>
       <c r="L73" t="n">
-        <v>301.25</v>
+        <v>359.27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:29:00</t>
+          <t>07:36:57</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="F74" t="n">
-        <v>13.24</v>
+        <v>14.66</v>
       </c>
       <c r="G74" t="n">
-        <v>308.7</v>
+        <v>302.8</v>
       </c>
       <c r="H74" t="n">
-        <v>39.7</v>
+        <v>49.5</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-99.23999999999999</v>
+        <v>-10.03</v>
       </c>
       <c r="K74" t="n">
-        <v>18.32</v>
+        <v>-95.81</v>
       </c>
       <c r="L74" t="n">
-        <v>100.92</v>
+        <v>96.33</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:30:40</t>
+          <t>07:39:23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.09</v>
+        <v>5.45</v>
       </c>
       <c r="F75" t="n">
-        <v>14.57</v>
+        <v>14</v>
       </c>
       <c r="G75" t="n">
-        <v>300.8</v>
+        <v>300.9</v>
       </c>
       <c r="H75" t="n">
-        <v>46.8</v>
+        <v>54.1</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>108.02</v>
+        <v>-90.84999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>30.29</v>
+        <v>122.36</v>
       </c>
       <c r="L75" t="n">
-        <v>112.19</v>
+        <v>152.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:32:37</t>
+          <t>07:40:45</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.36</v>
+        <v>5.7</v>
       </c>
       <c r="F76" t="n">
         <v>16.21</v>
       </c>
       <c r="G76" t="n">
-        <v>309.4</v>
+        <v>283.2</v>
       </c>
       <c r="H76" t="n">
-        <v>64.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="I76" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.98</v>
+        <v>131.6</v>
       </c>
       <c r="K76" t="n">
-        <v>136.83</v>
+        <v>-11.75</v>
       </c>
       <c r="L76" t="n">
-        <v>139.87</v>
+        <v>132.12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:37:55</t>
+          <t>07:45:38</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.95</v>
+        <v>4.73</v>
       </c>
       <c r="F77" t="n">
-        <v>10.4</v>
+        <v>14.11</v>
       </c>
       <c r="G77" t="n">
-        <v>307.1</v>
+        <v>288.1</v>
       </c>
       <c r="H77" t="n">
-        <v>16.1</v>
+        <v>20.2</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>56.79</v>
+        <v>-20.08</v>
       </c>
       <c r="K77" t="n">
-        <v>-80.06</v>
+        <v>-122.86</v>
       </c>
       <c r="L77" t="n">
-        <v>98.15000000000001</v>
+        <v>124.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:38:33</t>
+          <t>07:46:38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="F78" t="n">
-        <v>14.39</v>
+        <v>15.35</v>
       </c>
       <c r="G78" t="n">
-        <v>306.4</v>
+        <v>311.5</v>
       </c>
       <c r="H78" t="n">
-        <v>45</v>
+        <v>0.2</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-124.13</v>
+        <v>4.71</v>
       </c>
       <c r="K78" t="n">
-        <v>84.65000000000001</v>
+        <v>-159.1</v>
       </c>
       <c r="L78" t="n">
-        <v>150.25</v>
+        <v>159.17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:41:05</t>
+          <t>07:48:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.96</v>
+        <v>4.45</v>
       </c>
       <c r="F79" t="n">
-        <v>13.05</v>
+        <v>13.7</v>
       </c>
       <c r="G79" t="n">
-        <v>304.9</v>
+        <v>305.1</v>
       </c>
       <c r="H79" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="I79" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-57.63</v>
+        <v>-1</v>
       </c>
       <c r="K79" t="n">
-        <v>-126.07</v>
+        <v>-121.41</v>
       </c>
       <c r="L79" t="n">
-        <v>138.61</v>
+        <v>121.42</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:46:28</t>
+          <t>07:52:20</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.78</v>
+        <v>4.26</v>
       </c>
       <c r="F80" t="n">
-        <v>12.37</v>
+        <v>12.64</v>
       </c>
       <c r="G80" t="n">
-        <v>290.8</v>
+        <v>299.2</v>
       </c>
       <c r="H80" t="n">
-        <v>24.3</v>
+        <v>55.7</v>
       </c>
       <c r="I80" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>125.94</v>
+        <v>-77.39</v>
       </c>
       <c r="K80" t="n">
-        <v>105.76</v>
+        <v>-167.62</v>
       </c>
       <c r="L80" t="n">
-        <v>164.46</v>
+        <v>184.63</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:48:12</t>
+          <t>07:53:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.27</v>
+        <v>4.9</v>
       </c>
       <c r="F81" t="n">
-        <v>16.21</v>
+        <v>15.82</v>
       </c>
       <c r="G81" t="n">
-        <v>309.1</v>
+        <v>317.5</v>
       </c>
       <c r="H81" t="n">
-        <v>70.3</v>
+        <v>16.8</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-222.88</v>
+        <v>83.97</v>
       </c>
       <c r="K81" t="n">
-        <v>21.08</v>
+        <v>154.69</v>
       </c>
       <c r="L81" t="n">
-        <v>223.87</v>
+        <v>176.01</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:50:01</t>
+          <t>07:55:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.01</v>
+        <v>4.73</v>
       </c>
       <c r="F82" t="n">
-        <v>11.29</v>
+        <v>14.85</v>
       </c>
       <c r="G82" t="n">
-        <v>292.1</v>
+        <v>309</v>
       </c>
       <c r="H82" t="n">
-        <v>41.1</v>
+        <v>26.6</v>
       </c>
       <c r="I82" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>106.34</v>
+        <v>117.47</v>
       </c>
       <c r="K82" t="n">
-        <v>107.42</v>
+        <v>-89.36</v>
       </c>
       <c r="L82" t="n">
-        <v>151.15</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:55:31</t>
+          <t>08:00:25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.35</v>
+        <v>4.78</v>
       </c>
       <c r="F83" t="n">
-        <v>13.75</v>
+        <v>13.61</v>
       </c>
       <c r="G83" t="n">
-        <v>303.3</v>
+        <v>297.7</v>
       </c>
       <c r="H83" t="n">
-        <v>25.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-268.05</v>
+        <v>100.76</v>
       </c>
       <c r="K83" t="n">
-        <v>-54.48</v>
+        <v>304.29</v>
       </c>
       <c r="L83" t="n">
-        <v>273.53</v>
+        <v>320.54</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:56:31</t>
+          <t>08:02:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>4.57</v>
       </c>
       <c r="F84" t="n">
-        <v>11.54</v>
+        <v>13.13</v>
       </c>
       <c r="G84" t="n">
-        <v>299.3</v>
+        <v>299</v>
       </c>
       <c r="H84" t="n">
-        <v>33.8</v>
+        <v>56</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.78</v>
+        <v>123.45</v>
       </c>
       <c r="K84" t="n">
-        <v>-213.64</v>
+        <v>190.15</v>
       </c>
       <c r="L84" t="n">
-        <v>213.68</v>
+        <v>226.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:58:39</t>
+          <t>08:03:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.76</v>
+        <v>4.85</v>
       </c>
       <c r="F85" t="n">
         <v>16.21</v>
       </c>
       <c r="G85" t="n">
-        <v>309.6</v>
+        <v>296.9</v>
       </c>
       <c r="H85" t="n">
-        <v>53.1</v>
+        <v>36.7</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>160.79</v>
+        <v>-246.14</v>
       </c>
       <c r="K85" t="n">
-        <v>277.2</v>
+        <v>-132.8</v>
       </c>
       <c r="L85" t="n">
-        <v>320.45</v>
+        <v>279.68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:03:14</t>
+          <t>08:08:12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.77</v>
+        <v>5.48</v>
       </c>
       <c r="F86" t="n">
-        <v>13.71</v>
+        <v>16.21</v>
       </c>
       <c r="G86" t="n">
-        <v>291</v>
+        <v>302.2</v>
       </c>
       <c r="H86" t="n">
-        <v>68.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>252.54</v>
+        <v>463.01</v>
       </c>
       <c r="K86" t="n">
-        <v>168.22</v>
+        <v>40.54</v>
       </c>
       <c r="L86" t="n">
-        <v>303.44</v>
+        <v>464.78</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:05:25</t>
+          <t>08:10:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="F87" t="n">
-        <v>16.21</v>
+        <v>14.41</v>
       </c>
       <c r="G87" t="n">
-        <v>303.9</v>
+        <v>313.1</v>
       </c>
       <c r="H87" t="n">
-        <v>47.5</v>
+        <v>4.7</v>
       </c>
       <c r="I87" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>0.55</v>
+        <v>-448.64</v>
       </c>
       <c r="K87" t="n">
-        <v>-360.71</v>
+        <v>224.82</v>
       </c>
       <c r="L87" t="n">
-        <v>360.71</v>
+        <v>501.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:07:28</t>
+          <t>08:12:16</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.06</v>
+        <v>4.6</v>
       </c>
       <c r="F88" t="n">
-        <v>16.21</v>
+        <v>14.85</v>
       </c>
       <c r="G88" t="n">
-        <v>296</v>
+        <v>297.5</v>
       </c>
       <c r="H88" t="n">
-        <v>60.7</v>
+        <v>30.5</v>
       </c>
       <c r="I88" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-214.77</v>
+        <v>235.73</v>
       </c>
       <c r="K88" t="n">
-        <v>434.29</v>
+        <v>173.97</v>
       </c>
       <c r="L88" t="n">
-        <v>484.5</v>
+        <v>292.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.31</v>
+        <v>-23.07</v>
       </c>
       <c r="K14" t="n">
-        <v>-81.77</v>
+        <v>-77.59</v>
       </c>
       <c r="L14" t="n">
-        <v>85.31</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>31.6</v>
+        <v>34.32</v>
       </c>
       <c r="K15" t="n">
-        <v>-25.64</v>
+        <v>-27.85</v>
       </c>
       <c r="L15" t="n">
-        <v>40.69</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.64</v>
+        <v>-4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>-49.02</v>
+        <v>-51.77</v>
       </c>
       <c r="L16" t="n">
-        <v>49.24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>60.2</v>
+        <v>64.08</v>
       </c>
       <c r="K17" t="n">
-        <v>-16.66</v>
+        <v>-17.74</v>
       </c>
       <c r="L17" t="n">
-        <v>62.46</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
-        <v>25.3</v>
+        <v>29.89</v>
       </c>
       <c r="L18" t="n">
-        <v>25.34</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.23</v>
+        <v>-47.41</v>
       </c>
       <c r="K19" t="n">
-        <v>-37.74</v>
+        <v>-41.39</v>
       </c>
       <c r="L19" t="n">
-        <v>57.38</v>
+        <v>62.94</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>123.04</v>
+        <v>132.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-45.49</v>
+        <v>-49</v>
       </c>
       <c r="L20" t="n">
-        <v>131.18</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-81.89</v>
+        <v>-89.25</v>
       </c>
       <c r="K21" t="n">
-        <v>50.85</v>
+        <v>55.43</v>
       </c>
       <c r="L21" t="n">
-        <v>96.39</v>
+        <v>105.06</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-14.84</v>
+        <v>-16.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-113.96</v>
+        <v>-125.9</v>
       </c>
       <c r="L22" t="n">
-        <v>114.92</v>
+        <v>126.96</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>15.2</v>
+        <v>18.95</v>
       </c>
       <c r="K23" t="n">
-        <v>-162.92</v>
+        <v>-203.15</v>
       </c>
       <c r="L23" t="n">
-        <v>163.63</v>
+        <v>204.04</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-21.21</v>
+        <v>-24.01</v>
       </c>
       <c r="K24" t="n">
-        <v>-125.1</v>
+        <v>-141.59</v>
       </c>
       <c r="L24" t="n">
-        <v>126.89</v>
+        <v>143.61</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>66.7</v>
+        <v>80.5</v>
       </c>
       <c r="K25" t="n">
-        <v>133.66</v>
+        <v>161.32</v>
       </c>
       <c r="L25" t="n">
-        <v>149.38</v>
+        <v>180.29</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-298.51</v>
+        <v>-358.88</v>
       </c>
       <c r="K26" t="n">
-        <v>66.08</v>
+        <v>79.44</v>
       </c>
       <c r="L26" t="n">
-        <v>305.74</v>
+        <v>367.56</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-126.47</v>
+        <v>-145.42</v>
       </c>
       <c r="K27" t="n">
-        <v>119.09</v>
+        <v>136.93</v>
       </c>
       <c r="L27" t="n">
-        <v>173.72</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-171.47</v>
+        <v>-211.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-77.06</v>
+        <v>-95.19</v>
       </c>
       <c r="L28" t="n">
-        <v>188</v>
+        <v>232.21</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.4</v>
+        <v>-11.99</v>
       </c>
       <c r="K29" t="n">
-        <v>50.27</v>
+        <v>52.86</v>
       </c>
       <c r="L29" t="n">
-        <v>51.54</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="K30" t="n">
-        <v>53.96</v>
+        <v>55.61</v>
       </c>
       <c r="L30" t="n">
-        <v>53.97</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>59.6</v>
+        <v>61.38</v>
       </c>
       <c r="K31" t="n">
-        <v>22.18</v>
+        <v>22.84</v>
       </c>
       <c r="L31" t="n">
-        <v>63.6</v>
+        <v>65.48999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>32.57</v>
+        <v>33.29</v>
       </c>
       <c r="K32" t="n">
-        <v>57.7</v>
+        <v>58.98</v>
       </c>
       <c r="L32" t="n">
-        <v>66.26000000000001</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>27.61</v>
+        <v>32.36</v>
       </c>
       <c r="K33" t="n">
-        <v>4.23</v>
+        <v>4.96</v>
       </c>
       <c r="L33" t="n">
-        <v>27.93</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>9.359999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="K34" t="n">
-        <v>96.52</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>96.97</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.95</v>
+        <v>-24.4</v>
       </c>
       <c r="K35" t="n">
-        <v>-104.34</v>
+        <v>-116.03</v>
       </c>
       <c r="L35" t="n">
-        <v>106.62</v>
+        <v>118.57</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>83.7</v>
+        <v>98.23</v>
       </c>
       <c r="K36" t="n">
-        <v>62.04</v>
+        <v>72.8</v>
       </c>
       <c r="L36" t="n">
-        <v>104.19</v>
+        <v>122.26</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-85.86</v>
+        <v>-91.62</v>
       </c>
       <c r="K37" t="n">
-        <v>-14.51</v>
+        <v>-15.48</v>
       </c>
       <c r="L37" t="n">
-        <v>87.06999999999999</v>
+        <v>92.92</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-103.86</v>
+        <v>-118.62</v>
       </c>
       <c r="K38" t="n">
-        <v>-112.42</v>
+        <v>-128.4</v>
       </c>
       <c r="L38" t="n">
-        <v>153.05</v>
+        <v>174.81</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.7</v>
+        <v>-20.42</v>
       </c>
       <c r="K39" t="n">
-        <v>123.25</v>
+        <v>150.67</v>
       </c>
       <c r="L39" t="n">
-        <v>124.38</v>
+        <v>152.05</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>91.89</v>
+        <v>112.39</v>
       </c>
       <c r="K40" t="n">
-        <v>82.15000000000001</v>
+        <v>100.48</v>
       </c>
       <c r="L40" t="n">
-        <v>123.26</v>
+        <v>150.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>173.24</v>
+        <v>199.87</v>
       </c>
       <c r="K41" t="n">
-        <v>251.69</v>
+        <v>290.39</v>
       </c>
       <c r="L41" t="n">
-        <v>305.55</v>
+        <v>352.52</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-68.13</v>
+        <v>-82.83</v>
       </c>
       <c r="K42" t="n">
-        <v>-252.06</v>
+        <v>-306.45</v>
       </c>
       <c r="L42" t="n">
-        <v>261.11</v>
+        <v>317.45</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>316.72</v>
+        <v>387.39</v>
       </c>
       <c r="K43" t="n">
-        <v>-35.88</v>
+        <v>-43.88</v>
       </c>
       <c r="L43" t="n">
-        <v>318.74</v>
+        <v>389.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="K44" t="n">
-        <v>55.1</v>
+        <v>58.44</v>
       </c>
       <c r="L44" t="n">
-        <v>55.14</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.57</v>
+        <v>-14.87</v>
       </c>
       <c r="K45" t="n">
-        <v>-71.52</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>72.98999999999999</v>
+        <v>74.48999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>27.74</v>
+        <v>31.84</v>
       </c>
       <c r="K46" t="n">
-        <v>14.64</v>
+        <v>16.8</v>
       </c>
       <c r="L46" t="n">
-        <v>31.37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>35.05</v>
+        <v>41.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.26</v>
+        <v>-26.27</v>
       </c>
       <c r="L47" t="n">
-        <v>41.52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>44.25</v>
+        <v>50.75</v>
       </c>
       <c r="K48" t="n">
-        <v>-46.08</v>
+        <v>-52.84</v>
       </c>
       <c r="L48" t="n">
-        <v>63.88</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>69.43000000000001</v>
+        <v>70.56</v>
       </c>
       <c r="K49" t="n">
-        <v>35.58</v>
+        <v>36.16</v>
       </c>
       <c r="L49" t="n">
-        <v>78.01000000000001</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.43</v>
+        <v>-17.48</v>
       </c>
       <c r="K50" t="n">
-        <v>-87.14</v>
+        <v>-105.59</v>
       </c>
       <c r="L50" t="n">
-        <v>88.33</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>12.21</v>
+        <v>15.25</v>
       </c>
       <c r="K51" t="n">
-        <v>-81.03</v>
+        <v>-101.15</v>
       </c>
       <c r="L51" t="n">
-        <v>81.94</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-103.69</v>
+        <v>-121.33</v>
       </c>
       <c r="K52" t="n">
-        <v>43.48</v>
+        <v>50.87</v>
       </c>
       <c r="L52" t="n">
-        <v>112.44</v>
+        <v>131.56</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>126.84</v>
+        <v>157.88</v>
       </c>
       <c r="K53" t="n">
-        <v>21.06</v>
+        <v>26.21</v>
       </c>
       <c r="L53" t="n">
-        <v>128.58</v>
+        <v>160.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>128.41</v>
+        <v>143.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-113.97</v>
+        <v>-127.31</v>
       </c>
       <c r="L54" t="n">
-        <v>171.69</v>
+        <v>191.78</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-38.2</v>
+        <v>-47.06</v>
       </c>
       <c r="K55" t="n">
-        <v>-133.3</v>
+        <v>-164.21</v>
       </c>
       <c r="L55" t="n">
-        <v>138.66</v>
+        <v>170.82</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-206.06</v>
+        <v>-253.31</v>
       </c>
       <c r="K56" t="n">
-        <v>-228.54</v>
+        <v>-280.95</v>
       </c>
       <c r="L56" t="n">
-        <v>307.72</v>
+        <v>378.28</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>169.24</v>
+        <v>215.81</v>
       </c>
       <c r="K57" t="n">
-        <v>-110.37</v>
+        <v>-140.74</v>
       </c>
       <c r="L57" t="n">
-        <v>202.05</v>
+        <v>257.65</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-122.97</v>
+        <v>-167.49</v>
       </c>
       <c r="K58" t="n">
-        <v>176.97</v>
+        <v>241.04</v>
       </c>
       <c r="L58" t="n">
-        <v>215.5</v>
+        <v>293.52</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>22.74</v>
+        <v>24.17</v>
       </c>
       <c r="K59" t="n">
-        <v>45.78</v>
+        <v>48.65</v>
       </c>
       <c r="L59" t="n">
-        <v>51.11</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>42.68</v>
+        <v>46.22</v>
       </c>
       <c r="K60" t="n">
-        <v>29.56</v>
+        <v>32.01</v>
       </c>
       <c r="L60" t="n">
-        <v>51.91</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-36.57</v>
+        <v>-39.74</v>
       </c>
       <c r="K61" t="n">
-        <v>36.94</v>
+        <v>40.14</v>
       </c>
       <c r="L61" t="n">
-        <v>51.98</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>63.8</v>
+        <v>69.34</v>
       </c>
       <c r="K62" t="n">
-        <v>12.34</v>
+        <v>13.42</v>
       </c>
       <c r="L62" t="n">
-        <v>64.98</v>
+        <v>70.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.93</v>
+        <v>-26.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-44.66</v>
+        <v>-51.14</v>
       </c>
       <c r="L63" t="n">
-        <v>50.2</v>
+        <v>57.49</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>47.6</v>
+        <v>48.01</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.31999999999999</v>
+        <v>-66.89</v>
       </c>
       <c r="L64" t="n">
-        <v>81.63</v>
+        <v>82.34</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>44.99</v>
+        <v>47.16</v>
       </c>
       <c r="K65" t="n">
-        <v>153.01</v>
+        <v>160.39</v>
       </c>
       <c r="L65" t="n">
-        <v>159.49</v>
+        <v>167.18</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-52.21</v>
+        <v>-59.88</v>
       </c>
       <c r="K66" t="n">
-        <v>-118.58</v>
+        <v>-136.02</v>
       </c>
       <c r="L66" t="n">
-        <v>129.57</v>
+        <v>148.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-86.31</v>
+        <v>-102.5</v>
       </c>
       <c r="K67" t="n">
-        <v>-55</v>
+        <v>-65.31</v>
       </c>
       <c r="L67" t="n">
-        <v>102.35</v>
+        <v>121.54</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-54.2</v>
+        <v>-73.08</v>
       </c>
       <c r="K68" t="n">
-        <v>19.45</v>
+        <v>26.23</v>
       </c>
       <c r="L68" t="n">
-        <v>57.58</v>
+        <v>77.65000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>157.69</v>
+        <v>170.43</v>
       </c>
       <c r="K69" t="n">
-        <v>109.1</v>
+        <v>117.91</v>
       </c>
       <c r="L69" t="n">
-        <v>191.75</v>
+        <v>207.25</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-59.14</v>
+        <v>-69.42</v>
       </c>
       <c r="K70" t="n">
-        <v>101.33</v>
+        <v>118.95</v>
       </c>
       <c r="L70" t="n">
-        <v>117.33</v>
+        <v>137.72</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>265.17</v>
+        <v>325.74</v>
       </c>
       <c r="K71" t="n">
-        <v>48.83</v>
+        <v>59.98</v>
       </c>
       <c r="L71" t="n">
-        <v>269.63</v>
+        <v>331.22</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-92.84999999999999</v>
+        <v>-121.71</v>
       </c>
       <c r="K72" t="n">
-        <v>-178.19</v>
+        <v>-233.57</v>
       </c>
       <c r="L72" t="n">
-        <v>200.93</v>
+        <v>263.38</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>112.59</v>
+        <v>139.35</v>
       </c>
       <c r="K73" t="n">
-        <v>-242.72</v>
+        <v>-300.4</v>
       </c>
       <c r="L73" t="n">
-        <v>267.56</v>
+        <v>331.15</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-46.79</v>
+        <v>-50.34</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.42</v>
+        <v>-6.9</v>
       </c>
       <c r="L74" t="n">
-        <v>47.23</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.09</v>
+        <v>-66.87</v>
       </c>
       <c r="K75" t="n">
-        <v>7.19</v>
+        <v>7.5</v>
       </c>
       <c r="L75" t="n">
-        <v>64.48999999999999</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>28.42</v>
+        <v>30.4</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.57</v>
+        <v>-46.6</v>
       </c>
       <c r="L76" t="n">
-        <v>52.02</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-31.78</v>
+        <v>-33.46</v>
       </c>
       <c r="K77" t="n">
-        <v>-63.25</v>
+        <v>-66.59</v>
       </c>
       <c r="L77" t="n">
-        <v>70.78</v>
+        <v>74.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>76.7</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>34.13</v>
+        <v>36.64</v>
       </c>
       <c r="L78" t="n">
-        <v>83.95</v>
+        <v>90.13</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>30.31</v>
+        <v>29.83</v>
       </c>
       <c r="K79" t="n">
-        <v>91.11</v>
+        <v>89.69</v>
       </c>
       <c r="L79" t="n">
-        <v>96.02</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.19</v>
+        <v>-4.51</v>
       </c>
       <c r="K80" t="n">
-        <v>141.58</v>
+        <v>152.27</v>
       </c>
       <c r="L80" t="n">
-        <v>141.64</v>
+        <v>152.33</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-129.48</v>
+        <v>-137.68</v>
       </c>
       <c r="K81" t="n">
-        <v>-39.15</v>
+        <v>-41.62</v>
       </c>
       <c r="L81" t="n">
-        <v>135.27</v>
+        <v>143.83</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-51.44</v>
+        <v>-57.18</v>
       </c>
       <c r="K82" t="n">
-        <v>-83.19</v>
+        <v>-92.47</v>
       </c>
       <c r="L82" t="n">
-        <v>97.81</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-79.3</v>
+        <v>-98.76000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-119.68</v>
+        <v>-149.05</v>
       </c>
       <c r="L83" t="n">
-        <v>143.57</v>
+        <v>178.8</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-78.81</v>
+        <v>-97.36</v>
       </c>
       <c r="K84" t="n">
-        <v>116.89</v>
+        <v>144.4</v>
       </c>
       <c r="L84" t="n">
-        <v>140.98</v>
+        <v>174.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.22</v>
+        <v>-49.5</v>
       </c>
       <c r="K85" t="n">
-        <v>153.74</v>
+        <v>184.62</v>
       </c>
       <c r="L85" t="n">
-        <v>159.17</v>
+        <v>191.14</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>166.62</v>
+        <v>218.88</v>
       </c>
       <c r="K86" t="n">
-        <v>123.13</v>
+        <v>161.74</v>
       </c>
       <c r="L86" t="n">
-        <v>207.18</v>
+        <v>272.16</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-63.14</v>
+        <v>-87.47</v>
       </c>
       <c r="K87" t="n">
-        <v>93.31999999999999</v>
+        <v>129.27</v>
       </c>
       <c r="L87" t="n">
-        <v>112.68</v>
+        <v>156.08</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-46.99</v>
+        <v>-64.69</v>
       </c>
       <c r="K88" t="n">
-        <v>-47.53</v>
+        <v>-65.44</v>
       </c>
       <c r="L88" t="n">
-        <v>66.84</v>
+        <v>92.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-21.xlsx
+++ b/output/2024-06-21.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-23.07</v>
+        <v>-28.22</v>
       </c>
       <c r="K14" t="n">
-        <v>-77.59</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>80.94</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>34.32</v>
+        <v>38.61</v>
       </c>
       <c r="K15" t="n">
-        <v>-27.85</v>
+        <v>-31.33</v>
       </c>
       <c r="L15" t="n">
-        <v>44.2</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.9</v>
+        <v>-5.74</v>
       </c>
       <c r="K16" t="n">
-        <v>-51.77</v>
+        <v>-60.66</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>60.94</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>64.08</v>
+        <v>71.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-17.74</v>
+        <v>-19.82</v>
       </c>
       <c r="L17" t="n">
-        <v>66.48999999999999</v>
+        <v>74.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="K18" t="n">
-        <v>29.89</v>
+        <v>34.65</v>
       </c>
       <c r="L18" t="n">
-        <v>29.94</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-47.41</v>
+        <v>-52.75</v>
       </c>
       <c r="K19" t="n">
-        <v>-41.39</v>
+        <v>-46.05</v>
       </c>
       <c r="L19" t="n">
-        <v>62.94</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.99</v>
+        <v>-14.11</v>
       </c>
       <c r="K29" t="n">
-        <v>52.86</v>
+        <v>62.19</v>
       </c>
       <c r="L29" t="n">
-        <v>54.21</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="K30" t="n">
-        <v>55.61</v>
+        <v>67.75</v>
       </c>
       <c r="L30" t="n">
-        <v>55.63</v>
+        <v>67.76000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>61.38</v>
+        <v>89.19</v>
       </c>
       <c r="K31" t="n">
-        <v>22.84</v>
+        <v>33.18</v>
       </c>
       <c r="L31" t="n">
-        <v>65.48999999999999</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>33.29</v>
+        <v>37.95</v>
       </c>
       <c r="K32" t="n">
-        <v>58.98</v>
+        <v>67.23</v>
       </c>
       <c r="L32" t="n">
-        <v>67.72</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>32.36</v>
+        <v>39.12</v>
       </c>
       <c r="K33" t="n">
-        <v>4.96</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>32.74</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>9.06</v>
+        <v>11.14</v>
       </c>
       <c r="K34" t="n">
-        <v>93.45999999999999</v>
+        <v>114.92</v>
       </c>
       <c r="L34" t="n">
-        <v>93.90000000000001</v>
+        <v>115.46</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="K44" t="n">
-        <v>58.44</v>
+        <v>74.62</v>
       </c>
       <c r="L44" t="n">
-        <v>58.48</v>
+        <v>74.67</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.87</v>
+        <v>-18.42</v>
       </c>
       <c r="K45" t="n">
-        <v>-72.98999999999999</v>
+        <v>-90.39</v>
       </c>
       <c r="L45" t="n">
-        <v>74.48999999999999</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>31.84</v>
+        <v>41.57</v>
       </c>
       <c r="K46" t="n">
-        <v>16.8</v>
+        <v>21.93</v>
       </c>
       <c r="L46" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>41.37</v>
+        <v>49.93</v>
       </c>
       <c r="K47" t="n">
-        <v>-26.27</v>
+        <v>-31.7</v>
       </c>
       <c r="L47" t="n">
-        <v>49</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>50.75</v>
+        <v>74.44</v>
       </c>
       <c r="K48" t="n">
-        <v>-52.84</v>
+        <v>-77.52</v>
       </c>
       <c r="L48" t="n">
-        <v>73.26000000000001</v>
+        <v>107.47</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>70.56</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>36.16</v>
+        <v>43.31</v>
       </c>
       <c r="L49" t="n">
-        <v>79.29000000000001</v>
+        <v>94.95999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>24.17</v>
+        <v>28.26</v>
       </c>
       <c r="K59" t="n">
-        <v>48.65</v>
+        <v>56.89</v>
       </c>
       <c r="L59" t="n">
-        <v>54.32</v>
+        <v>63.52</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>46.22</v>
+        <v>61.81</v>
       </c>
       <c r="K60" t="n">
-        <v>32.01</v>
+        <v>42.81</v>
       </c>
       <c r="L60" t="n">
-        <v>56.22</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-39.74</v>
+        <v>-58.3</v>
       </c>
       <c r="K61" t="n">
-        <v>40.14</v>
+        <v>58.89</v>
       </c>
       <c r="L61" t="n">
-        <v>56.48</v>
+        <v>82.87</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>69.34</v>
+        <v>90.39</v>
       </c>
       <c r="K62" t="n">
-        <v>13.42</v>
+        <v>17.49</v>
       </c>
       <c r="L62" t="n">
-        <v>70.63</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-26.26</v>
+        <v>-30.68</v>
       </c>
       <c r="K63" t="n">
-        <v>-51.14</v>
+        <v>-59.75</v>
       </c>
       <c r="L63" t="n">
-        <v>57.49</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>48.01</v>
+        <v>60.23</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.89</v>
+        <v>-83.92</v>
       </c>
       <c r="L64" t="n">
-        <v>82.34</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-50.34</v>
+        <v>-78.34</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.9</v>
+        <v>-10.75</v>
       </c>
       <c r="L74" t="n">
-        <v>50.81</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-66.87</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>7.5</v>
+        <v>10.23</v>
       </c>
       <c r="L75" t="n">
-        <v>67.29000000000001</v>
+        <v>91.81</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>30.4</v>
+        <v>41.15</v>
       </c>
       <c r="K76" t="n">
-        <v>-46.6</v>
+        <v>-63.08</v>
       </c>
       <c r="L76" t="n">
-        <v>55.64</v>
+        <v>75.31</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-33.46</v>
+        <v>-43.41</v>
       </c>
       <c r="K77" t="n">
-        <v>-66.59</v>
+        <v>-86.41</v>
       </c>
       <c r="L77" t="n">
-        <v>74.53</v>
+        <v>96.70999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>82.34999999999999</v>
+        <v>117.83</v>
       </c>
       <c r="K78" t="n">
-        <v>36.64</v>
+        <v>52.42</v>
       </c>
       <c r="L78" t="n">
-        <v>90.13</v>
+        <v>128.96</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>29.83</v>
+        <v>39.85</v>
       </c>
       <c r="K79" t="n">
-        <v>89.69</v>
+        <v>119.8</v>
       </c>
       <c r="L79" t="n">
-        <v>94.52</v>
+        <v>126.25</v>
       </c>
     </row>
     <row r="80">
